--- a/templates/FlexiTog_data_request_pack.xlsx
+++ b/templates/FlexiTog_data_request_pack.xlsx
@@ -276,67 +276,73 @@
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
+        <t>Brand, e.g. FlexiTog, RefrigiWear, Gold Freeze
+Type: str</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
         <t>product_family
 Type: str</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>unit_weight_kg
 Type: float
 Required</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>length_cm
 Type: float</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>width_cm
 Type: float</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>height_cm
 Type: float</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>unit_price_eur
 Type: float
 Required</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Customs tariff code. Drives duty rate
 Type: str</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Manufacturing origin (ISO2). Decides EU-preferential duty
 Type: str</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Units on one full pallet. Used to suggest pallet count
 Type: float</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>SKU needs a product conformity certificate (e.g. SASO/SABER PCoC)
 Type: bool</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>notes
 Type: str</t>
@@ -493,6 +499,18 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
+        <t>Optional. For the dashboard map. Blank = city lookup
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. For the dashboard map. Blank = city lookup
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
         <t>notes
 Type: str</t>
       </text>
@@ -599,6 +617,18 @@
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. For the dashboard map
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. For the dashboard map
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
       <text>
         <t>notes
 Type: str</t>
@@ -739,6 +769,31 @@
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Brands this supplier makes, separated by ;
+Type: str</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Main transport mode to Helmond
+Allowed: road, sea, air, multimodal
+Type: str</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. For the dashboard map. Blank = city lookup
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. For the dashboard map. Blank = city lookup
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>notes
 Type: str</t>
@@ -1416,11 +1471,11 @@
         </is>
       </c>
       <c r="J15" s="5">
-        <f>COUNTA('Freight rates'!A2:A80)</f>
+        <f>COUNTA('Freight rates'!A2:A81)</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>COUNTIF('Freight rates'!I2:I80,"real")</f>
+        <f>COUNTIF('Freight rates'!I2:I81,"real")</f>
         <v/>
       </c>
     </row>
@@ -1795,19 +1850,19 @@
           <t>Suppliers</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>Low</t>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Only needed to simulate orders that start at a supplier instead of Helmond stock.</t>
+          <t>Real supplier list per brand (FlexiTog, RefrigiWear, Gold Freeze) with city, SKUs, lead time, Incoterm and inbound mode. Places the supply base on the map and sets inbound freight for orders that start at a supplier. Confirm the origin per SKU: Albanian and Serbian origin may qualify for Pan-Euro-Med preference.</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Purchasing.</t>
+          <t>Purchasing, supplier contracts, supplier origin declarations.</t>
         </is>
       </c>
       <c r="F24" s="8" t="n"/>
@@ -3083,7 +3138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J202"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3095,6 +3150,10 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3140,6 +3199,26 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>brands</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>inbound_mode</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -3147,44 +3226,60 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>SUP-PK1</t>
+          <t>SUP-AL1</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
         <is>
-          <t>Placeholder Supplier Pakistan</t>
+          <t>Placeholder garment maker Albania</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>Sialkot</t>
+          <t>Durrës</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>FT-GLV-100;FT-GLV-200</t>
+          <t>FT-JKT-100;FT-JKT-200;FT-TRS-100;FT-OVR-100</t>
         </is>
       </c>
       <c r="F2" s="12" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
-          <t>FOB</t>
+          <t>DAP</t>
         </is>
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="n"/>
-      <c r="J2" s="13" t="inlineStr">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>FlexiTog</t>
+        </is>
+      </c>
+      <c r="J2" s="12" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="K2" s="12" t="n"/>
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="inlineStr">
+        <is>
+          <t>Cut-make-trim for the FlexiTog line. Road via Montenegro and Croatia, or ferry to Bari</t>
+        </is>
+      </c>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>EXAMPLE ROW: delete before upload</t>
         </is>
@@ -3200,6 +3295,10 @@
       <c r="G3" s="14" t="n"/>
       <c r="H3" s="14" t="n"/>
       <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n"/>
@@ -3211,6 +3310,10 @@
       <c r="G4" s="14" t="n"/>
       <c r="H4" s="14" t="n"/>
       <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n"/>
@@ -3222,6 +3325,10 @@
       <c r="G5" s="14" t="n"/>
       <c r="H5" s="14" t="n"/>
       <c r="I5" s="14" t="n"/>
+      <c r="J5" s="14" t="n"/>
+      <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n"/>
@@ -3233,6 +3340,10 @@
       <c r="G6" s="14" t="n"/>
       <c r="H6" s="14" t="n"/>
       <c r="I6" s="14" t="n"/>
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n"/>
@@ -3244,6 +3355,10 @@
       <c r="G7" s="14" t="n"/>
       <c r="H7" s="14" t="n"/>
       <c r="I7" s="14" t="n"/>
+      <c r="J7" s="14" t="n"/>
+      <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
@@ -3255,6 +3370,10 @@
       <c r="G8" s="14" t="n"/>
       <c r="H8" s="14" t="n"/>
       <c r="I8" s="14" t="n"/>
+      <c r="J8" s="14" t="n"/>
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n"/>
@@ -3266,6 +3385,10 @@
       <c r="G9" s="14" t="n"/>
       <c r="H9" s="14" t="n"/>
       <c r="I9" s="14" t="n"/>
+      <c r="J9" s="14" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n"/>
@@ -3277,6 +3400,10 @@
       <c r="G10" s="14" t="n"/>
       <c r="H10" s="14" t="n"/>
       <c r="I10" s="14" t="n"/>
+      <c r="J10" s="14" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n"/>
@@ -3288,6 +3415,10 @@
       <c r="G11" s="14" t="n"/>
       <c r="H11" s="14" t="n"/>
       <c r="I11" s="14" t="n"/>
+      <c r="J11" s="14" t="n"/>
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n"/>
@@ -3299,6 +3430,10 @@
       <c r="G12" s="14" t="n"/>
       <c r="H12" s="14" t="n"/>
       <c r="I12" s="14" t="n"/>
+      <c r="J12" s="14" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n"/>
@@ -3310,6 +3445,10 @@
       <c r="G13" s="14" t="n"/>
       <c r="H13" s="14" t="n"/>
       <c r="I13" s="14" t="n"/>
+      <c r="J13" s="14" t="n"/>
+      <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n"/>
@@ -3321,6 +3460,10 @@
       <c r="G14" s="14" t="n"/>
       <c r="H14" s="14" t="n"/>
       <c r="I14" s="14" t="n"/>
+      <c r="J14" s="14" t="n"/>
+      <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n"/>
@@ -3332,6 +3475,10 @@
       <c r="G15" s="14" t="n"/>
       <c r="H15" s="14" t="n"/>
       <c r="I15" s="14" t="n"/>
+      <c r="J15" s="14" t="n"/>
+      <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n"/>
@@ -3343,6 +3490,10 @@
       <c r="G16" s="14" t="n"/>
       <c r="H16" s="14" t="n"/>
       <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n"/>
@@ -3354,6 +3505,10 @@
       <c r="G17" s="14" t="n"/>
       <c r="H17" s="14" t="n"/>
       <c r="I17" s="14" t="n"/>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n"/>
@@ -3365,6 +3520,10 @@
       <c r="G18" s="14" t="n"/>
       <c r="H18" s="14" t="n"/>
       <c r="I18" s="14" t="n"/>
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n"/>
@@ -3376,6 +3535,10 @@
       <c r="G19" s="14" t="n"/>
       <c r="H19" s="14" t="n"/>
       <c r="I19" s="14" t="n"/>
+      <c r="J19" s="14" t="n"/>
+      <c r="K19" s="14" t="n"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n"/>
@@ -3387,6 +3550,10 @@
       <c r="G20" s="14" t="n"/>
       <c r="H20" s="14" t="n"/>
       <c r="I20" s="14" t="n"/>
+      <c r="J20" s="14" t="n"/>
+      <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
@@ -3398,6 +3565,10 @@
       <c r="G21" s="14" t="n"/>
       <c r="H21" s="14" t="n"/>
       <c r="I21" s="14" t="n"/>
+      <c r="J21" s="14" t="n"/>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n"/>
@@ -3409,6 +3580,10 @@
       <c r="G22" s="14" t="n"/>
       <c r="H22" s="14" t="n"/>
       <c r="I22" s="14" t="n"/>
+      <c r="J22" s="14" t="n"/>
+      <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n"/>
@@ -3420,6 +3595,10 @@
       <c r="G23" s="14" t="n"/>
       <c r="H23" s="14" t="n"/>
       <c r="I23" s="14" t="n"/>
+      <c r="J23" s="14" t="n"/>
+      <c r="K23" s="14" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n"/>
@@ -3431,6 +3610,10 @@
       <c r="G24" s="14" t="n"/>
       <c r="H24" s="14" t="n"/>
       <c r="I24" s="14" t="n"/>
+      <c r="J24" s="14" t="n"/>
+      <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n"/>
@@ -3442,6 +3625,10 @@
       <c r="G25" s="14" t="n"/>
       <c r="H25" s="14" t="n"/>
       <c r="I25" s="14" t="n"/>
+      <c r="J25" s="14" t="n"/>
+      <c r="K25" s="14" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n"/>
@@ -3453,6 +3640,10 @@
       <c r="G26" s="14" t="n"/>
       <c r="H26" s="14" t="n"/>
       <c r="I26" s="14" t="n"/>
+      <c r="J26" s="14" t="n"/>
+      <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n"/>
@@ -3464,6 +3655,10 @@
       <c r="G27" s="14" t="n"/>
       <c r="H27" s="14" t="n"/>
       <c r="I27" s="14" t="n"/>
+      <c r="J27" s="14" t="n"/>
+      <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n"/>
@@ -3475,6 +3670,10 @@
       <c r="G28" s="14" t="n"/>
       <c r="H28" s="14" t="n"/>
       <c r="I28" s="14" t="n"/>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n"/>
@@ -3486,6 +3685,10 @@
       <c r="G29" s="14" t="n"/>
       <c r="H29" s="14" t="n"/>
       <c r="I29" s="14" t="n"/>
+      <c r="J29" s="14" t="n"/>
+      <c r="K29" s="14" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n"/>
@@ -3497,6 +3700,10 @@
       <c r="G30" s="14" t="n"/>
       <c r="H30" s="14" t="n"/>
       <c r="I30" s="14" t="n"/>
+      <c r="J30" s="14" t="n"/>
+      <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n"/>
@@ -3508,6 +3715,10 @@
       <c r="G31" s="14" t="n"/>
       <c r="H31" s="14" t="n"/>
       <c r="I31" s="14" t="n"/>
+      <c r="J31" s="14" t="n"/>
+      <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n"/>
@@ -3519,6 +3730,10 @@
       <c r="G32" s="14" t="n"/>
       <c r="H32" s="14" t="n"/>
       <c r="I32" s="14" t="n"/>
+      <c r="J32" s="14" t="n"/>
+      <c r="K32" s="14" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n"/>
@@ -3530,6 +3745,10 @@
       <c r="G33" s="14" t="n"/>
       <c r="H33" s="14" t="n"/>
       <c r="I33" s="14" t="n"/>
+      <c r="J33" s="14" t="n"/>
+      <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n"/>
@@ -3541,6 +3760,10 @@
       <c r="G34" s="14" t="n"/>
       <c r="H34" s="14" t="n"/>
       <c r="I34" s="14" t="n"/>
+      <c r="J34" s="14" t="n"/>
+      <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n"/>
@@ -3552,6 +3775,10 @@
       <c r="G35" s="14" t="n"/>
       <c r="H35" s="14" t="n"/>
       <c r="I35" s="14" t="n"/>
+      <c r="J35" s="14" t="n"/>
+      <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n"/>
@@ -3563,6 +3790,10 @@
       <c r="G36" s="14" t="n"/>
       <c r="H36" s="14" t="n"/>
       <c r="I36" s="14" t="n"/>
+      <c r="J36" s="14" t="n"/>
+      <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n"/>
@@ -3574,6 +3805,10 @@
       <c r="G37" s="14" t="n"/>
       <c r="H37" s="14" t="n"/>
       <c r="I37" s="14" t="n"/>
+      <c r="J37" s="14" t="n"/>
+      <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n"/>
@@ -3585,6 +3820,10 @@
       <c r="G38" s="14" t="n"/>
       <c r="H38" s="14" t="n"/>
       <c r="I38" s="14" t="n"/>
+      <c r="J38" s="14" t="n"/>
+      <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n"/>
@@ -3596,6 +3835,10 @@
       <c r="G39" s="14" t="n"/>
       <c r="H39" s="14" t="n"/>
       <c r="I39" s="14" t="n"/>
+      <c r="J39" s="14" t="n"/>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n"/>
@@ -3607,6 +3850,10 @@
       <c r="G40" s="14" t="n"/>
       <c r="H40" s="14" t="n"/>
       <c r="I40" s="14" t="n"/>
+      <c r="J40" s="14" t="n"/>
+      <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n"/>
@@ -3618,6 +3865,10 @@
       <c r="G41" s="14" t="n"/>
       <c r="H41" s="14" t="n"/>
       <c r="I41" s="14" t="n"/>
+      <c r="J41" s="14" t="n"/>
+      <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n"/>
@@ -3629,6 +3880,10 @@
       <c r="G42" s="14" t="n"/>
       <c r="H42" s="14" t="n"/>
       <c r="I42" s="14" t="n"/>
+      <c r="J42" s="14" t="n"/>
+      <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n"/>
@@ -3640,6 +3895,10 @@
       <c r="G43" s="14" t="n"/>
       <c r="H43" s="14" t="n"/>
       <c r="I43" s="14" t="n"/>
+      <c r="J43" s="14" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n"/>
@@ -3651,6 +3910,10 @@
       <c r="G44" s="14" t="n"/>
       <c r="H44" s="14" t="n"/>
       <c r="I44" s="14" t="n"/>
+      <c r="J44" s="14" t="n"/>
+      <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n"/>
@@ -3662,6 +3925,10 @@
       <c r="G45" s="14" t="n"/>
       <c r="H45" s="14" t="n"/>
       <c r="I45" s="14" t="n"/>
+      <c r="J45" s="14" t="n"/>
+      <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n"/>
@@ -3673,6 +3940,10 @@
       <c r="G46" s="14" t="n"/>
       <c r="H46" s="14" t="n"/>
       <c r="I46" s="14" t="n"/>
+      <c r="J46" s="14" t="n"/>
+      <c r="K46" s="14" t="n"/>
+      <c r="L46" s="14" t="n"/>
+      <c r="M46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n"/>
@@ -3684,6 +3955,10 @@
       <c r="G47" s="14" t="n"/>
       <c r="H47" s="14" t="n"/>
       <c r="I47" s="14" t="n"/>
+      <c r="J47" s="14" t="n"/>
+      <c r="K47" s="14" t="n"/>
+      <c r="L47" s="14" t="n"/>
+      <c r="M47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n"/>
@@ -3695,6 +3970,10 @@
       <c r="G48" s="14" t="n"/>
       <c r="H48" s="14" t="n"/>
       <c r="I48" s="14" t="n"/>
+      <c r="J48" s="14" t="n"/>
+      <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n"/>
@@ -3706,6 +3985,10 @@
       <c r="G49" s="14" t="n"/>
       <c r="H49" s="14" t="n"/>
       <c r="I49" s="14" t="n"/>
+      <c r="J49" s="14" t="n"/>
+      <c r="K49" s="14" t="n"/>
+      <c r="L49" s="14" t="n"/>
+      <c r="M49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n"/>
@@ -3717,6 +4000,10 @@
       <c r="G50" s="14" t="n"/>
       <c r="H50" s="14" t="n"/>
       <c r="I50" s="14" t="n"/>
+      <c r="J50" s="14" t="n"/>
+      <c r="K50" s="14" t="n"/>
+      <c r="L50" s="14" t="n"/>
+      <c r="M50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n"/>
@@ -3728,6 +4015,10 @@
       <c r="G51" s="14" t="n"/>
       <c r="H51" s="14" t="n"/>
       <c r="I51" s="14" t="n"/>
+      <c r="J51" s="14" t="n"/>
+      <c r="K51" s="14" t="n"/>
+      <c r="L51" s="14" t="n"/>
+      <c r="M51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n"/>
@@ -3739,6 +4030,10 @@
       <c r="G52" s="14" t="n"/>
       <c r="H52" s="14" t="n"/>
       <c r="I52" s="14" t="n"/>
+      <c r="J52" s="14" t="n"/>
+      <c r="K52" s="14" t="n"/>
+      <c r="L52" s="14" t="n"/>
+      <c r="M52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n"/>
@@ -3750,6 +4045,10 @@
       <c r="G53" s="14" t="n"/>
       <c r="H53" s="14" t="n"/>
       <c r="I53" s="14" t="n"/>
+      <c r="J53" s="14" t="n"/>
+      <c r="K53" s="14" t="n"/>
+      <c r="L53" s="14" t="n"/>
+      <c r="M53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n"/>
@@ -3761,6 +4060,10 @@
       <c r="G54" s="14" t="n"/>
       <c r="H54" s="14" t="n"/>
       <c r="I54" s="14" t="n"/>
+      <c r="J54" s="14" t="n"/>
+      <c r="K54" s="14" t="n"/>
+      <c r="L54" s="14" t="n"/>
+      <c r="M54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n"/>
@@ -3772,6 +4075,10 @@
       <c r="G55" s="14" t="n"/>
       <c r="H55" s="14" t="n"/>
       <c r="I55" s="14" t="n"/>
+      <c r="J55" s="14" t="n"/>
+      <c r="K55" s="14" t="n"/>
+      <c r="L55" s="14" t="n"/>
+      <c r="M55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n"/>
@@ -3783,6 +4090,10 @@
       <c r="G56" s="14" t="n"/>
       <c r="H56" s="14" t="n"/>
       <c r="I56" s="14" t="n"/>
+      <c r="J56" s="14" t="n"/>
+      <c r="K56" s="14" t="n"/>
+      <c r="L56" s="14" t="n"/>
+      <c r="M56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n"/>
@@ -3794,6 +4105,10 @@
       <c r="G57" s="14" t="n"/>
       <c r="H57" s="14" t="n"/>
       <c r="I57" s="14" t="n"/>
+      <c r="J57" s="14" t="n"/>
+      <c r="K57" s="14" t="n"/>
+      <c r="L57" s="14" t="n"/>
+      <c r="M57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n"/>
@@ -3805,6 +4120,10 @@
       <c r="G58" s="14" t="n"/>
       <c r="H58" s="14" t="n"/>
       <c r="I58" s="14" t="n"/>
+      <c r="J58" s="14" t="n"/>
+      <c r="K58" s="14" t="n"/>
+      <c r="L58" s="14" t="n"/>
+      <c r="M58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n"/>
@@ -3816,6 +4135,10 @@
       <c r="G59" s="14" t="n"/>
       <c r="H59" s="14" t="n"/>
       <c r="I59" s="14" t="n"/>
+      <c r="J59" s="14" t="n"/>
+      <c r="K59" s="14" t="n"/>
+      <c r="L59" s="14" t="n"/>
+      <c r="M59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n"/>
@@ -3827,6 +4150,10 @@
       <c r="G60" s="14" t="n"/>
       <c r="H60" s="14" t="n"/>
       <c r="I60" s="14" t="n"/>
+      <c r="J60" s="14" t="n"/>
+      <c r="K60" s="14" t="n"/>
+      <c r="L60" s="14" t="n"/>
+      <c r="M60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n"/>
@@ -3838,6 +4165,10 @@
       <c r="G61" s="14" t="n"/>
       <c r="H61" s="14" t="n"/>
       <c r="I61" s="14" t="n"/>
+      <c r="J61" s="14" t="n"/>
+      <c r="K61" s="14" t="n"/>
+      <c r="L61" s="14" t="n"/>
+      <c r="M61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n"/>
@@ -3849,6 +4180,10 @@
       <c r="G62" s="14" t="n"/>
       <c r="H62" s="14" t="n"/>
       <c r="I62" s="14" t="n"/>
+      <c r="J62" s="14" t="n"/>
+      <c r="K62" s="14" t="n"/>
+      <c r="L62" s="14" t="n"/>
+      <c r="M62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n"/>
@@ -3860,6 +4195,10 @@
       <c r="G63" s="14" t="n"/>
       <c r="H63" s="14" t="n"/>
       <c r="I63" s="14" t="n"/>
+      <c r="J63" s="14" t="n"/>
+      <c r="K63" s="14" t="n"/>
+      <c r="L63" s="14" t="n"/>
+      <c r="M63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n"/>
@@ -3871,6 +4210,10 @@
       <c r="G64" s="14" t="n"/>
       <c r="H64" s="14" t="n"/>
       <c r="I64" s="14" t="n"/>
+      <c r="J64" s="14" t="n"/>
+      <c r="K64" s="14" t="n"/>
+      <c r="L64" s="14" t="n"/>
+      <c r="M64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n"/>
@@ -3882,6 +4225,10 @@
       <c r="G65" s="14" t="n"/>
       <c r="H65" s="14" t="n"/>
       <c r="I65" s="14" t="n"/>
+      <c r="J65" s="14" t="n"/>
+      <c r="K65" s="14" t="n"/>
+      <c r="L65" s="14" t="n"/>
+      <c r="M65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n"/>
@@ -3893,6 +4240,10 @@
       <c r="G66" s="14" t="n"/>
       <c r="H66" s="14" t="n"/>
       <c r="I66" s="14" t="n"/>
+      <c r="J66" s="14" t="n"/>
+      <c r="K66" s="14" t="n"/>
+      <c r="L66" s="14" t="n"/>
+      <c r="M66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n"/>
@@ -3904,6 +4255,10 @@
       <c r="G67" s="14" t="n"/>
       <c r="H67" s="14" t="n"/>
       <c r="I67" s="14" t="n"/>
+      <c r="J67" s="14" t="n"/>
+      <c r="K67" s="14" t="n"/>
+      <c r="L67" s="14" t="n"/>
+      <c r="M67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n"/>
@@ -3915,6 +4270,10 @@
       <c r="G68" s="14" t="n"/>
       <c r="H68" s="14" t="n"/>
       <c r="I68" s="14" t="n"/>
+      <c r="J68" s="14" t="n"/>
+      <c r="K68" s="14" t="n"/>
+      <c r="L68" s="14" t="n"/>
+      <c r="M68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n"/>
@@ -3926,6 +4285,10 @@
       <c r="G69" s="14" t="n"/>
       <c r="H69" s="14" t="n"/>
       <c r="I69" s="14" t="n"/>
+      <c r="J69" s="14" t="n"/>
+      <c r="K69" s="14" t="n"/>
+      <c r="L69" s="14" t="n"/>
+      <c r="M69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n"/>
@@ -3937,6 +4300,10 @@
       <c r="G70" s="14" t="n"/>
       <c r="H70" s="14" t="n"/>
       <c r="I70" s="14" t="n"/>
+      <c r="J70" s="14" t="n"/>
+      <c r="K70" s="14" t="n"/>
+      <c r="L70" s="14" t="n"/>
+      <c r="M70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n"/>
@@ -3948,6 +4315,10 @@
       <c r="G71" s="14" t="n"/>
       <c r="H71" s="14" t="n"/>
       <c r="I71" s="14" t="n"/>
+      <c r="J71" s="14" t="n"/>
+      <c r="K71" s="14" t="n"/>
+      <c r="L71" s="14" t="n"/>
+      <c r="M71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n"/>
@@ -3959,6 +4330,10 @@
       <c r="G72" s="14" t="n"/>
       <c r="H72" s="14" t="n"/>
       <c r="I72" s="14" t="n"/>
+      <c r="J72" s="14" t="n"/>
+      <c r="K72" s="14" t="n"/>
+      <c r="L72" s="14" t="n"/>
+      <c r="M72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n"/>
@@ -3970,6 +4345,10 @@
       <c r="G73" s="14" t="n"/>
       <c r="H73" s="14" t="n"/>
       <c r="I73" s="14" t="n"/>
+      <c r="J73" s="14" t="n"/>
+      <c r="K73" s="14" t="n"/>
+      <c r="L73" s="14" t="n"/>
+      <c r="M73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n"/>
@@ -3981,6 +4360,10 @@
       <c r="G74" s="14" t="n"/>
       <c r="H74" s="14" t="n"/>
       <c r="I74" s="14" t="n"/>
+      <c r="J74" s="14" t="n"/>
+      <c r="K74" s="14" t="n"/>
+      <c r="L74" s="14" t="n"/>
+      <c r="M74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n"/>
@@ -3992,6 +4375,10 @@
       <c r="G75" s="14" t="n"/>
       <c r="H75" s="14" t="n"/>
       <c r="I75" s="14" t="n"/>
+      <c r="J75" s="14" t="n"/>
+      <c r="K75" s="14" t="n"/>
+      <c r="L75" s="14" t="n"/>
+      <c r="M75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n"/>
@@ -4003,6 +4390,10 @@
       <c r="G76" s="14" t="n"/>
       <c r="H76" s="14" t="n"/>
       <c r="I76" s="14" t="n"/>
+      <c r="J76" s="14" t="n"/>
+      <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n"/>
@@ -4014,6 +4405,10 @@
       <c r="G77" s="14" t="n"/>
       <c r="H77" s="14" t="n"/>
       <c r="I77" s="14" t="n"/>
+      <c r="J77" s="14" t="n"/>
+      <c r="K77" s="14" t="n"/>
+      <c r="L77" s="14" t="n"/>
+      <c r="M77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n"/>
@@ -4025,6 +4420,10 @@
       <c r="G78" s="14" t="n"/>
       <c r="H78" s="14" t="n"/>
       <c r="I78" s="14" t="n"/>
+      <c r="J78" s="14" t="n"/>
+      <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n"/>
@@ -4036,6 +4435,10 @@
       <c r="G79" s="14" t="n"/>
       <c r="H79" s="14" t="n"/>
       <c r="I79" s="14" t="n"/>
+      <c r="J79" s="14" t="n"/>
+      <c r="K79" s="14" t="n"/>
+      <c r="L79" s="14" t="n"/>
+      <c r="M79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n"/>
@@ -4047,6 +4450,10 @@
       <c r="G80" s="14" t="n"/>
       <c r="H80" s="14" t="n"/>
       <c r="I80" s="14" t="n"/>
+      <c r="J80" s="14" t="n"/>
+      <c r="K80" s="14" t="n"/>
+      <c r="L80" s="14" t="n"/>
+      <c r="M80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n"/>
@@ -4058,6 +4465,10 @@
       <c r="G81" s="14" t="n"/>
       <c r="H81" s="14" t="n"/>
       <c r="I81" s="14" t="n"/>
+      <c r="J81" s="14" t="n"/>
+      <c r="K81" s="14" t="n"/>
+      <c r="L81" s="14" t="n"/>
+      <c r="M81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n"/>
@@ -4069,6 +4480,10 @@
       <c r="G82" s="14" t="n"/>
       <c r="H82" s="14" t="n"/>
       <c r="I82" s="14" t="n"/>
+      <c r="J82" s="14" t="n"/>
+      <c r="K82" s="14" t="n"/>
+      <c r="L82" s="14" t="n"/>
+      <c r="M82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n"/>
@@ -4080,6 +4495,10 @@
       <c r="G83" s="14" t="n"/>
       <c r="H83" s="14" t="n"/>
       <c r="I83" s="14" t="n"/>
+      <c r="J83" s="14" t="n"/>
+      <c r="K83" s="14" t="n"/>
+      <c r="L83" s="14" t="n"/>
+      <c r="M83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n"/>
@@ -4091,6 +4510,10 @@
       <c r="G84" s="14" t="n"/>
       <c r="H84" s="14" t="n"/>
       <c r="I84" s="14" t="n"/>
+      <c r="J84" s="14" t="n"/>
+      <c r="K84" s="14" t="n"/>
+      <c r="L84" s="14" t="n"/>
+      <c r="M84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n"/>
@@ -4102,6 +4525,10 @@
       <c r="G85" s="14" t="n"/>
       <c r="H85" s="14" t="n"/>
       <c r="I85" s="14" t="n"/>
+      <c r="J85" s="14" t="n"/>
+      <c r="K85" s="14" t="n"/>
+      <c r="L85" s="14" t="n"/>
+      <c r="M85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n"/>
@@ -4113,6 +4540,10 @@
       <c r="G86" s="14" t="n"/>
       <c r="H86" s="14" t="n"/>
       <c r="I86" s="14" t="n"/>
+      <c r="J86" s="14" t="n"/>
+      <c r="K86" s="14" t="n"/>
+      <c r="L86" s="14" t="n"/>
+      <c r="M86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n"/>
@@ -4124,6 +4555,10 @@
       <c r="G87" s="14" t="n"/>
       <c r="H87" s="14" t="n"/>
       <c r="I87" s="14" t="n"/>
+      <c r="J87" s="14" t="n"/>
+      <c r="K87" s="14" t="n"/>
+      <c r="L87" s="14" t="n"/>
+      <c r="M87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n"/>
@@ -4135,6 +4570,10 @@
       <c r="G88" s="14" t="n"/>
       <c r="H88" s="14" t="n"/>
       <c r="I88" s="14" t="n"/>
+      <c r="J88" s="14" t="n"/>
+      <c r="K88" s="14" t="n"/>
+      <c r="L88" s="14" t="n"/>
+      <c r="M88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n"/>
@@ -4146,6 +4585,10 @@
       <c r="G89" s="14" t="n"/>
       <c r="H89" s="14" t="n"/>
       <c r="I89" s="14" t="n"/>
+      <c r="J89" s="14" t="n"/>
+      <c r="K89" s="14" t="n"/>
+      <c r="L89" s="14" t="n"/>
+      <c r="M89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n"/>
@@ -4157,6 +4600,10 @@
       <c r="G90" s="14" t="n"/>
       <c r="H90" s="14" t="n"/>
       <c r="I90" s="14" t="n"/>
+      <c r="J90" s="14" t="n"/>
+      <c r="K90" s="14" t="n"/>
+      <c r="L90" s="14" t="n"/>
+      <c r="M90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n"/>
@@ -4168,6 +4615,10 @@
       <c r="G91" s="14" t="n"/>
       <c r="H91" s="14" t="n"/>
       <c r="I91" s="14" t="n"/>
+      <c r="J91" s="14" t="n"/>
+      <c r="K91" s="14" t="n"/>
+      <c r="L91" s="14" t="n"/>
+      <c r="M91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n"/>
@@ -4179,6 +4630,10 @@
       <c r="G92" s="14" t="n"/>
       <c r="H92" s="14" t="n"/>
       <c r="I92" s="14" t="n"/>
+      <c r="J92" s="14" t="n"/>
+      <c r="K92" s="14" t="n"/>
+      <c r="L92" s="14" t="n"/>
+      <c r="M92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n"/>
@@ -4190,6 +4645,10 @@
       <c r="G93" s="14" t="n"/>
       <c r="H93" s="14" t="n"/>
       <c r="I93" s="14" t="n"/>
+      <c r="J93" s="14" t="n"/>
+      <c r="K93" s="14" t="n"/>
+      <c r="L93" s="14" t="n"/>
+      <c r="M93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n"/>
@@ -4201,6 +4660,10 @@
       <c r="G94" s="14" t="n"/>
       <c r="H94" s="14" t="n"/>
       <c r="I94" s="14" t="n"/>
+      <c r="J94" s="14" t="n"/>
+      <c r="K94" s="14" t="n"/>
+      <c r="L94" s="14" t="n"/>
+      <c r="M94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n"/>
@@ -4212,6 +4675,10 @@
       <c r="G95" s="14" t="n"/>
       <c r="H95" s="14" t="n"/>
       <c r="I95" s="14" t="n"/>
+      <c r="J95" s="14" t="n"/>
+      <c r="K95" s="14" t="n"/>
+      <c r="L95" s="14" t="n"/>
+      <c r="M95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n"/>
@@ -4223,6 +4690,10 @@
       <c r="G96" s="14" t="n"/>
       <c r="H96" s="14" t="n"/>
       <c r="I96" s="14" t="n"/>
+      <c r="J96" s="14" t="n"/>
+      <c r="K96" s="14" t="n"/>
+      <c r="L96" s="14" t="n"/>
+      <c r="M96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n"/>
@@ -4234,6 +4705,10 @@
       <c r="G97" s="14" t="n"/>
       <c r="H97" s="14" t="n"/>
       <c r="I97" s="14" t="n"/>
+      <c r="J97" s="14" t="n"/>
+      <c r="K97" s="14" t="n"/>
+      <c r="L97" s="14" t="n"/>
+      <c r="M97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n"/>
@@ -4245,6 +4720,10 @@
       <c r="G98" s="14" t="n"/>
       <c r="H98" s="14" t="n"/>
       <c r="I98" s="14" t="n"/>
+      <c r="J98" s="14" t="n"/>
+      <c r="K98" s="14" t="n"/>
+      <c r="L98" s="14" t="n"/>
+      <c r="M98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n"/>
@@ -4256,6 +4735,10 @@
       <c r="G99" s="14" t="n"/>
       <c r="H99" s="14" t="n"/>
       <c r="I99" s="14" t="n"/>
+      <c r="J99" s="14" t="n"/>
+      <c r="K99" s="14" t="n"/>
+      <c r="L99" s="14" t="n"/>
+      <c r="M99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n"/>
@@ -4267,6 +4750,10 @@
       <c r="G100" s="14" t="n"/>
       <c r="H100" s="14" t="n"/>
       <c r="I100" s="14" t="n"/>
+      <c r="J100" s="14" t="n"/>
+      <c r="K100" s="14" t="n"/>
+      <c r="L100" s="14" t="n"/>
+      <c r="M100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n"/>
@@ -4278,6 +4765,10 @@
       <c r="G101" s="14" t="n"/>
       <c r="H101" s="14" t="n"/>
       <c r="I101" s="14" t="n"/>
+      <c r="J101" s="14" t="n"/>
+      <c r="K101" s="14" t="n"/>
+      <c r="L101" s="14" t="n"/>
+      <c r="M101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n"/>
@@ -4289,6 +4780,10 @@
       <c r="G102" s="14" t="n"/>
       <c r="H102" s="14" t="n"/>
       <c r="I102" s="14" t="n"/>
+      <c r="J102" s="14" t="n"/>
+      <c r="K102" s="14" t="n"/>
+      <c r="L102" s="14" t="n"/>
+      <c r="M102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n"/>
@@ -4300,6 +4795,10 @@
       <c r="G103" s="14" t="n"/>
       <c r="H103" s="14" t="n"/>
       <c r="I103" s="14" t="n"/>
+      <c r="J103" s="14" t="n"/>
+      <c r="K103" s="14" t="n"/>
+      <c r="L103" s="14" t="n"/>
+      <c r="M103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n"/>
@@ -4311,6 +4810,10 @@
       <c r="G104" s="14" t="n"/>
       <c r="H104" s="14" t="n"/>
       <c r="I104" s="14" t="n"/>
+      <c r="J104" s="14" t="n"/>
+      <c r="K104" s="14" t="n"/>
+      <c r="L104" s="14" t="n"/>
+      <c r="M104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n"/>
@@ -4322,6 +4825,10 @@
       <c r="G105" s="14" t="n"/>
       <c r="H105" s="14" t="n"/>
       <c r="I105" s="14" t="n"/>
+      <c r="J105" s="14" t="n"/>
+      <c r="K105" s="14" t="n"/>
+      <c r="L105" s="14" t="n"/>
+      <c r="M105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n"/>
@@ -4333,6 +4840,10 @@
       <c r="G106" s="14" t="n"/>
       <c r="H106" s="14" t="n"/>
       <c r="I106" s="14" t="n"/>
+      <c r="J106" s="14" t="n"/>
+      <c r="K106" s="14" t="n"/>
+      <c r="L106" s="14" t="n"/>
+      <c r="M106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n"/>
@@ -4344,6 +4855,10 @@
       <c r="G107" s="14" t="n"/>
       <c r="H107" s="14" t="n"/>
       <c r="I107" s="14" t="n"/>
+      <c r="J107" s="14" t="n"/>
+      <c r="K107" s="14" t="n"/>
+      <c r="L107" s="14" t="n"/>
+      <c r="M107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n"/>
@@ -4355,6 +4870,10 @@
       <c r="G108" s="14" t="n"/>
       <c r="H108" s="14" t="n"/>
       <c r="I108" s="14" t="n"/>
+      <c r="J108" s="14" t="n"/>
+      <c r="K108" s="14" t="n"/>
+      <c r="L108" s="14" t="n"/>
+      <c r="M108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n"/>
@@ -4366,6 +4885,10 @@
       <c r="G109" s="14" t="n"/>
       <c r="H109" s="14" t="n"/>
       <c r="I109" s="14" t="n"/>
+      <c r="J109" s="14" t="n"/>
+      <c r="K109" s="14" t="n"/>
+      <c r="L109" s="14" t="n"/>
+      <c r="M109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n"/>
@@ -4377,6 +4900,10 @@
       <c r="G110" s="14" t="n"/>
       <c r="H110" s="14" t="n"/>
       <c r="I110" s="14" t="n"/>
+      <c r="J110" s="14" t="n"/>
+      <c r="K110" s="14" t="n"/>
+      <c r="L110" s="14" t="n"/>
+      <c r="M110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n"/>
@@ -4388,6 +4915,10 @@
       <c r="G111" s="14" t="n"/>
       <c r="H111" s="14" t="n"/>
       <c r="I111" s="14" t="n"/>
+      <c r="J111" s="14" t="n"/>
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n"/>
+      <c r="M111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n"/>
@@ -4399,6 +4930,10 @@
       <c r="G112" s="14" t="n"/>
       <c r="H112" s="14" t="n"/>
       <c r="I112" s="14" t="n"/>
+      <c r="J112" s="14" t="n"/>
+      <c r="K112" s="14" t="n"/>
+      <c r="L112" s="14" t="n"/>
+      <c r="M112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n"/>
@@ -4410,6 +4945,10 @@
       <c r="G113" s="14" t="n"/>
       <c r="H113" s="14" t="n"/>
       <c r="I113" s="14" t="n"/>
+      <c r="J113" s="14" t="n"/>
+      <c r="K113" s="14" t="n"/>
+      <c r="L113" s="14" t="n"/>
+      <c r="M113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n"/>
@@ -4421,6 +4960,10 @@
       <c r="G114" s="14" t="n"/>
       <c r="H114" s="14" t="n"/>
       <c r="I114" s="14" t="n"/>
+      <c r="J114" s="14" t="n"/>
+      <c r="K114" s="14" t="n"/>
+      <c r="L114" s="14" t="n"/>
+      <c r="M114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n"/>
@@ -4432,6 +4975,10 @@
       <c r="G115" s="14" t="n"/>
       <c r="H115" s="14" t="n"/>
       <c r="I115" s="14" t="n"/>
+      <c r="J115" s="14" t="n"/>
+      <c r="K115" s="14" t="n"/>
+      <c r="L115" s="14" t="n"/>
+      <c r="M115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n"/>
@@ -4443,6 +4990,10 @@
       <c r="G116" s="14" t="n"/>
       <c r="H116" s="14" t="n"/>
       <c r="I116" s="14" t="n"/>
+      <c r="J116" s="14" t="n"/>
+      <c r="K116" s="14" t="n"/>
+      <c r="L116" s="14" t="n"/>
+      <c r="M116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n"/>
@@ -4454,6 +5005,10 @@
       <c r="G117" s="14" t="n"/>
       <c r="H117" s="14" t="n"/>
       <c r="I117" s="14" t="n"/>
+      <c r="J117" s="14" t="n"/>
+      <c r="K117" s="14" t="n"/>
+      <c r="L117" s="14" t="n"/>
+      <c r="M117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n"/>
@@ -4465,6 +5020,10 @@
       <c r="G118" s="14" t="n"/>
       <c r="H118" s="14" t="n"/>
       <c r="I118" s="14" t="n"/>
+      <c r="J118" s="14" t="n"/>
+      <c r="K118" s="14" t="n"/>
+      <c r="L118" s="14" t="n"/>
+      <c r="M118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n"/>
@@ -4476,6 +5035,10 @@
       <c r="G119" s="14" t="n"/>
       <c r="H119" s="14" t="n"/>
       <c r="I119" s="14" t="n"/>
+      <c r="J119" s="14" t="n"/>
+      <c r="K119" s="14" t="n"/>
+      <c r="L119" s="14" t="n"/>
+      <c r="M119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n"/>
@@ -4487,6 +5050,10 @@
       <c r="G120" s="14" t="n"/>
       <c r="H120" s="14" t="n"/>
       <c r="I120" s="14" t="n"/>
+      <c r="J120" s="14" t="n"/>
+      <c r="K120" s="14" t="n"/>
+      <c r="L120" s="14" t="n"/>
+      <c r="M120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n"/>
@@ -4498,6 +5065,10 @@
       <c r="G121" s="14" t="n"/>
       <c r="H121" s="14" t="n"/>
       <c r="I121" s="14" t="n"/>
+      <c r="J121" s="14" t="n"/>
+      <c r="K121" s="14" t="n"/>
+      <c r="L121" s="14" t="n"/>
+      <c r="M121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n"/>
@@ -4509,6 +5080,10 @@
       <c r="G122" s="14" t="n"/>
       <c r="H122" s="14" t="n"/>
       <c r="I122" s="14" t="n"/>
+      <c r="J122" s="14" t="n"/>
+      <c r="K122" s="14" t="n"/>
+      <c r="L122" s="14" t="n"/>
+      <c r="M122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n"/>
@@ -4520,6 +5095,10 @@
       <c r="G123" s="14" t="n"/>
       <c r="H123" s="14" t="n"/>
       <c r="I123" s="14" t="n"/>
+      <c r="J123" s="14" t="n"/>
+      <c r="K123" s="14" t="n"/>
+      <c r="L123" s="14" t="n"/>
+      <c r="M123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n"/>
@@ -4531,6 +5110,10 @@
       <c r="G124" s="14" t="n"/>
       <c r="H124" s="14" t="n"/>
       <c r="I124" s="14" t="n"/>
+      <c r="J124" s="14" t="n"/>
+      <c r="K124" s="14" t="n"/>
+      <c r="L124" s="14" t="n"/>
+      <c r="M124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n"/>
@@ -4542,6 +5125,10 @@
       <c r="G125" s="14" t="n"/>
       <c r="H125" s="14" t="n"/>
       <c r="I125" s="14" t="n"/>
+      <c r="J125" s="14" t="n"/>
+      <c r="K125" s="14" t="n"/>
+      <c r="L125" s="14" t="n"/>
+      <c r="M125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n"/>
@@ -4553,6 +5140,10 @@
       <c r="G126" s="14" t="n"/>
       <c r="H126" s="14" t="n"/>
       <c r="I126" s="14" t="n"/>
+      <c r="J126" s="14" t="n"/>
+      <c r="K126" s="14" t="n"/>
+      <c r="L126" s="14" t="n"/>
+      <c r="M126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n"/>
@@ -4564,6 +5155,10 @@
       <c r="G127" s="14" t="n"/>
       <c r="H127" s="14" t="n"/>
       <c r="I127" s="14" t="n"/>
+      <c r="J127" s="14" t="n"/>
+      <c r="K127" s="14" t="n"/>
+      <c r="L127" s="14" t="n"/>
+      <c r="M127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n"/>
@@ -4575,6 +5170,10 @@
       <c r="G128" s="14" t="n"/>
       <c r="H128" s="14" t="n"/>
       <c r="I128" s="14" t="n"/>
+      <c r="J128" s="14" t="n"/>
+      <c r="K128" s="14" t="n"/>
+      <c r="L128" s="14" t="n"/>
+      <c r="M128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n"/>
@@ -4586,6 +5185,10 @@
       <c r="G129" s="14" t="n"/>
       <c r="H129" s="14" t="n"/>
       <c r="I129" s="14" t="n"/>
+      <c r="J129" s="14" t="n"/>
+      <c r="K129" s="14" t="n"/>
+      <c r="L129" s="14" t="n"/>
+      <c r="M129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n"/>
@@ -4597,6 +5200,10 @@
       <c r="G130" s="14" t="n"/>
       <c r="H130" s="14" t="n"/>
       <c r="I130" s="14" t="n"/>
+      <c r="J130" s="14" t="n"/>
+      <c r="K130" s="14" t="n"/>
+      <c r="L130" s="14" t="n"/>
+      <c r="M130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n"/>
@@ -4608,6 +5215,10 @@
       <c r="G131" s="14" t="n"/>
       <c r="H131" s="14" t="n"/>
       <c r="I131" s="14" t="n"/>
+      <c r="J131" s="14" t="n"/>
+      <c r="K131" s="14" t="n"/>
+      <c r="L131" s="14" t="n"/>
+      <c r="M131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="14" t="n"/>
@@ -4619,6 +5230,10 @@
       <c r="G132" s="14" t="n"/>
       <c r="H132" s="14" t="n"/>
       <c r="I132" s="14" t="n"/>
+      <c r="J132" s="14" t="n"/>
+      <c r="K132" s="14" t="n"/>
+      <c r="L132" s="14" t="n"/>
+      <c r="M132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n"/>
@@ -4630,6 +5245,10 @@
       <c r="G133" s="14" t="n"/>
       <c r="H133" s="14" t="n"/>
       <c r="I133" s="14" t="n"/>
+      <c r="J133" s="14" t="n"/>
+      <c r="K133" s="14" t="n"/>
+      <c r="L133" s="14" t="n"/>
+      <c r="M133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="14" t="n"/>
@@ -4641,6 +5260,10 @@
       <c r="G134" s="14" t="n"/>
       <c r="H134" s="14" t="n"/>
       <c r="I134" s="14" t="n"/>
+      <c r="J134" s="14" t="n"/>
+      <c r="K134" s="14" t="n"/>
+      <c r="L134" s="14" t="n"/>
+      <c r="M134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n"/>
@@ -4652,6 +5275,10 @@
       <c r="G135" s="14" t="n"/>
       <c r="H135" s="14" t="n"/>
       <c r="I135" s="14" t="n"/>
+      <c r="J135" s="14" t="n"/>
+      <c r="K135" s="14" t="n"/>
+      <c r="L135" s="14" t="n"/>
+      <c r="M135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="14" t="n"/>
@@ -4663,6 +5290,10 @@
       <c r="G136" s="14" t="n"/>
       <c r="H136" s="14" t="n"/>
       <c r="I136" s="14" t="n"/>
+      <c r="J136" s="14" t="n"/>
+      <c r="K136" s="14" t="n"/>
+      <c r="L136" s="14" t="n"/>
+      <c r="M136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n"/>
@@ -4674,6 +5305,10 @@
       <c r="G137" s="14" t="n"/>
       <c r="H137" s="14" t="n"/>
       <c r="I137" s="14" t="n"/>
+      <c r="J137" s="14" t="n"/>
+      <c r="K137" s="14" t="n"/>
+      <c r="L137" s="14" t="n"/>
+      <c r="M137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="14" t="n"/>
@@ -4685,6 +5320,10 @@
       <c r="G138" s="14" t="n"/>
       <c r="H138" s="14" t="n"/>
       <c r="I138" s="14" t="n"/>
+      <c r="J138" s="14" t="n"/>
+      <c r="K138" s="14" t="n"/>
+      <c r="L138" s="14" t="n"/>
+      <c r="M138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n"/>
@@ -4696,6 +5335,10 @@
       <c r="G139" s="14" t="n"/>
       <c r="H139" s="14" t="n"/>
       <c r="I139" s="14" t="n"/>
+      <c r="J139" s="14" t="n"/>
+      <c r="K139" s="14" t="n"/>
+      <c r="L139" s="14" t="n"/>
+      <c r="M139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="14" t="n"/>
@@ -4707,6 +5350,10 @@
       <c r="G140" s="14" t="n"/>
       <c r="H140" s="14" t="n"/>
       <c r="I140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="14" t="n"/>
+      <c r="L140" s="14" t="n"/>
+      <c r="M140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n"/>
@@ -4718,6 +5365,10 @@
       <c r="G141" s="14" t="n"/>
       <c r="H141" s="14" t="n"/>
       <c r="I141" s="14" t="n"/>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="14" t="n"/>
+      <c r="L141" s="14" t="n"/>
+      <c r="M141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="14" t="n"/>
@@ -4729,6 +5380,10 @@
       <c r="G142" s="14" t="n"/>
       <c r="H142" s="14" t="n"/>
       <c r="I142" s="14" t="n"/>
+      <c r="J142" s="14" t="n"/>
+      <c r="K142" s="14" t="n"/>
+      <c r="L142" s="14" t="n"/>
+      <c r="M142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n"/>
@@ -4740,6 +5395,10 @@
       <c r="G143" s="14" t="n"/>
       <c r="H143" s="14" t="n"/>
       <c r="I143" s="14" t="n"/>
+      <c r="J143" s="14" t="n"/>
+      <c r="K143" s="14" t="n"/>
+      <c r="L143" s="14" t="n"/>
+      <c r="M143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n"/>
@@ -4751,6 +5410,10 @@
       <c r="G144" s="14" t="n"/>
       <c r="H144" s="14" t="n"/>
       <c r="I144" s="14" t="n"/>
+      <c r="J144" s="14" t="n"/>
+      <c r="K144" s="14" t="n"/>
+      <c r="L144" s="14" t="n"/>
+      <c r="M144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n"/>
@@ -4762,6 +5425,10 @@
       <c r="G145" s="14" t="n"/>
       <c r="H145" s="14" t="n"/>
       <c r="I145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="14" t="n"/>
+      <c r="L145" s="14" t="n"/>
+      <c r="M145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="14" t="n"/>
@@ -4773,6 +5440,10 @@
       <c r="G146" s="14" t="n"/>
       <c r="H146" s="14" t="n"/>
       <c r="I146" s="14" t="n"/>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="14" t="n"/>
+      <c r="L146" s="14" t="n"/>
+      <c r="M146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n"/>
@@ -4784,6 +5455,10 @@
       <c r="G147" s="14" t="n"/>
       <c r="H147" s="14" t="n"/>
       <c r="I147" s="14" t="n"/>
+      <c r="J147" s="14" t="n"/>
+      <c r="K147" s="14" t="n"/>
+      <c r="L147" s="14" t="n"/>
+      <c r="M147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="14" t="n"/>
@@ -4795,6 +5470,10 @@
       <c r="G148" s="14" t="n"/>
       <c r="H148" s="14" t="n"/>
       <c r="I148" s="14" t="n"/>
+      <c r="J148" s="14" t="n"/>
+      <c r="K148" s="14" t="n"/>
+      <c r="L148" s="14" t="n"/>
+      <c r="M148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n"/>
@@ -4806,6 +5485,10 @@
       <c r="G149" s="14" t="n"/>
       <c r="H149" s="14" t="n"/>
       <c r="I149" s="14" t="n"/>
+      <c r="J149" s="14" t="n"/>
+      <c r="K149" s="14" t="n"/>
+      <c r="L149" s="14" t="n"/>
+      <c r="M149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="14" t="n"/>
@@ -4817,6 +5500,10 @@
       <c r="G150" s="14" t="n"/>
       <c r="H150" s="14" t="n"/>
       <c r="I150" s="14" t="n"/>
+      <c r="J150" s="14" t="n"/>
+      <c r="K150" s="14" t="n"/>
+      <c r="L150" s="14" t="n"/>
+      <c r="M150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n"/>
@@ -4828,6 +5515,10 @@
       <c r="G151" s="14" t="n"/>
       <c r="H151" s="14" t="n"/>
       <c r="I151" s="14" t="n"/>
+      <c r="J151" s="14" t="n"/>
+      <c r="K151" s="14" t="n"/>
+      <c r="L151" s="14" t="n"/>
+      <c r="M151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="14" t="n"/>
@@ -4839,6 +5530,10 @@
       <c r="G152" s="14" t="n"/>
       <c r="H152" s="14" t="n"/>
       <c r="I152" s="14" t="n"/>
+      <c r="J152" s="14" t="n"/>
+      <c r="K152" s="14" t="n"/>
+      <c r="L152" s="14" t="n"/>
+      <c r="M152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n"/>
@@ -4850,6 +5545,10 @@
       <c r="G153" s="14" t="n"/>
       <c r="H153" s="14" t="n"/>
       <c r="I153" s="14" t="n"/>
+      <c r="J153" s="14" t="n"/>
+      <c r="K153" s="14" t="n"/>
+      <c r="L153" s="14" t="n"/>
+      <c r="M153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="14" t="n"/>
@@ -4861,6 +5560,10 @@
       <c r="G154" s="14" t="n"/>
       <c r="H154" s="14" t="n"/>
       <c r="I154" s="14" t="n"/>
+      <c r="J154" s="14" t="n"/>
+      <c r="K154" s="14" t="n"/>
+      <c r="L154" s="14" t="n"/>
+      <c r="M154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n"/>
@@ -4872,6 +5575,10 @@
       <c r="G155" s="14" t="n"/>
       <c r="H155" s="14" t="n"/>
       <c r="I155" s="14" t="n"/>
+      <c r="J155" s="14" t="n"/>
+      <c r="K155" s="14" t="n"/>
+      <c r="L155" s="14" t="n"/>
+      <c r="M155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n"/>
@@ -4883,6 +5590,10 @@
       <c r="G156" s="14" t="n"/>
       <c r="H156" s="14" t="n"/>
       <c r="I156" s="14" t="n"/>
+      <c r="J156" s="14" t="n"/>
+      <c r="K156" s="14" t="n"/>
+      <c r="L156" s="14" t="n"/>
+      <c r="M156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n"/>
@@ -4894,6 +5605,10 @@
       <c r="G157" s="14" t="n"/>
       <c r="H157" s="14" t="n"/>
       <c r="I157" s="14" t="n"/>
+      <c r="J157" s="14" t="n"/>
+      <c r="K157" s="14" t="n"/>
+      <c r="L157" s="14" t="n"/>
+      <c r="M157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="14" t="n"/>
@@ -4905,6 +5620,10 @@
       <c r="G158" s="14" t="n"/>
       <c r="H158" s="14" t="n"/>
       <c r="I158" s="14" t="n"/>
+      <c r="J158" s="14" t="n"/>
+      <c r="K158" s="14" t="n"/>
+      <c r="L158" s="14" t="n"/>
+      <c r="M158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n"/>
@@ -4916,6 +5635,10 @@
       <c r="G159" s="14" t="n"/>
       <c r="H159" s="14" t="n"/>
       <c r="I159" s="14" t="n"/>
+      <c r="J159" s="14" t="n"/>
+      <c r="K159" s="14" t="n"/>
+      <c r="L159" s="14" t="n"/>
+      <c r="M159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="14" t="n"/>
@@ -4927,6 +5650,10 @@
       <c r="G160" s="14" t="n"/>
       <c r="H160" s="14" t="n"/>
       <c r="I160" s="14" t="n"/>
+      <c r="J160" s="14" t="n"/>
+      <c r="K160" s="14" t="n"/>
+      <c r="L160" s="14" t="n"/>
+      <c r="M160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n"/>
@@ -4938,6 +5665,10 @@
       <c r="G161" s="14" t="n"/>
       <c r="H161" s="14" t="n"/>
       <c r="I161" s="14" t="n"/>
+      <c r="J161" s="14" t="n"/>
+      <c r="K161" s="14" t="n"/>
+      <c r="L161" s="14" t="n"/>
+      <c r="M161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="14" t="n"/>
@@ -4949,6 +5680,10 @@
       <c r="G162" s="14" t="n"/>
       <c r="H162" s="14" t="n"/>
       <c r="I162" s="14" t="n"/>
+      <c r="J162" s="14" t="n"/>
+      <c r="K162" s="14" t="n"/>
+      <c r="L162" s="14" t="n"/>
+      <c r="M162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n"/>
@@ -4960,6 +5695,10 @@
       <c r="G163" s="14" t="n"/>
       <c r="H163" s="14" t="n"/>
       <c r="I163" s="14" t="n"/>
+      <c r="J163" s="14" t="n"/>
+      <c r="K163" s="14" t="n"/>
+      <c r="L163" s="14" t="n"/>
+      <c r="M163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n"/>
@@ -4971,6 +5710,10 @@
       <c r="G164" s="14" t="n"/>
       <c r="H164" s="14" t="n"/>
       <c r="I164" s="14" t="n"/>
+      <c r="J164" s="14" t="n"/>
+      <c r="K164" s="14" t="n"/>
+      <c r="L164" s="14" t="n"/>
+      <c r="M164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n"/>
@@ -4982,6 +5725,10 @@
       <c r="G165" s="14" t="n"/>
       <c r="H165" s="14" t="n"/>
       <c r="I165" s="14" t="n"/>
+      <c r="J165" s="14" t="n"/>
+      <c r="K165" s="14" t="n"/>
+      <c r="L165" s="14" t="n"/>
+      <c r="M165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n"/>
@@ -4993,6 +5740,10 @@
       <c r="G166" s="14" t="n"/>
       <c r="H166" s="14" t="n"/>
       <c r="I166" s="14" t="n"/>
+      <c r="J166" s="14" t="n"/>
+      <c r="K166" s="14" t="n"/>
+      <c r="L166" s="14" t="n"/>
+      <c r="M166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n"/>
@@ -5004,6 +5755,10 @@
       <c r="G167" s="14" t="n"/>
       <c r="H167" s="14" t="n"/>
       <c r="I167" s="14" t="n"/>
+      <c r="J167" s="14" t="n"/>
+      <c r="K167" s="14" t="n"/>
+      <c r="L167" s="14" t="n"/>
+      <c r="M167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="14" t="n"/>
@@ -5015,6 +5770,10 @@
       <c r="G168" s="14" t="n"/>
       <c r="H168" s="14" t="n"/>
       <c r="I168" s="14" t="n"/>
+      <c r="J168" s="14" t="n"/>
+      <c r="K168" s="14" t="n"/>
+      <c r="L168" s="14" t="n"/>
+      <c r="M168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n"/>
@@ -5026,6 +5785,10 @@
       <c r="G169" s="14" t="n"/>
       <c r="H169" s="14" t="n"/>
       <c r="I169" s="14" t="n"/>
+      <c r="J169" s="14" t="n"/>
+      <c r="K169" s="14" t="n"/>
+      <c r="L169" s="14" t="n"/>
+      <c r="M169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="14" t="n"/>
@@ -5037,6 +5800,10 @@
       <c r="G170" s="14" t="n"/>
       <c r="H170" s="14" t="n"/>
       <c r="I170" s="14" t="n"/>
+      <c r="J170" s="14" t="n"/>
+      <c r="K170" s="14" t="n"/>
+      <c r="L170" s="14" t="n"/>
+      <c r="M170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n"/>
@@ -5048,6 +5815,10 @@
       <c r="G171" s="14" t="n"/>
       <c r="H171" s="14" t="n"/>
       <c r="I171" s="14" t="n"/>
+      <c r="J171" s="14" t="n"/>
+      <c r="K171" s="14" t="n"/>
+      <c r="L171" s="14" t="n"/>
+      <c r="M171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n"/>
@@ -5059,6 +5830,10 @@
       <c r="G172" s="14" t="n"/>
       <c r="H172" s="14" t="n"/>
       <c r="I172" s="14" t="n"/>
+      <c r="J172" s="14" t="n"/>
+      <c r="K172" s="14" t="n"/>
+      <c r="L172" s="14" t="n"/>
+      <c r="M172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n"/>
@@ -5070,6 +5845,10 @@
       <c r="G173" s="14" t="n"/>
       <c r="H173" s="14" t="n"/>
       <c r="I173" s="14" t="n"/>
+      <c r="J173" s="14" t="n"/>
+      <c r="K173" s="14" t="n"/>
+      <c r="L173" s="14" t="n"/>
+      <c r="M173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n"/>
@@ -5081,6 +5860,10 @@
       <c r="G174" s="14" t="n"/>
       <c r="H174" s="14" t="n"/>
       <c r="I174" s="14" t="n"/>
+      <c r="J174" s="14" t="n"/>
+      <c r="K174" s="14" t="n"/>
+      <c r="L174" s="14" t="n"/>
+      <c r="M174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n"/>
@@ -5092,6 +5875,10 @@
       <c r="G175" s="14" t="n"/>
       <c r="H175" s="14" t="n"/>
       <c r="I175" s="14" t="n"/>
+      <c r="J175" s="14" t="n"/>
+      <c r="K175" s="14" t="n"/>
+      <c r="L175" s="14" t="n"/>
+      <c r="M175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n"/>
@@ -5103,6 +5890,10 @@
       <c r="G176" s="14" t="n"/>
       <c r="H176" s="14" t="n"/>
       <c r="I176" s="14" t="n"/>
+      <c r="J176" s="14" t="n"/>
+      <c r="K176" s="14" t="n"/>
+      <c r="L176" s="14" t="n"/>
+      <c r="M176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n"/>
@@ -5114,6 +5905,10 @@
       <c r="G177" s="14" t="n"/>
       <c r="H177" s="14" t="n"/>
       <c r="I177" s="14" t="n"/>
+      <c r="J177" s="14" t="n"/>
+      <c r="K177" s="14" t="n"/>
+      <c r="L177" s="14" t="n"/>
+      <c r="M177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n"/>
@@ -5125,6 +5920,10 @@
       <c r="G178" s="14" t="n"/>
       <c r="H178" s="14" t="n"/>
       <c r="I178" s="14" t="n"/>
+      <c r="J178" s="14" t="n"/>
+      <c r="K178" s="14" t="n"/>
+      <c r="L178" s="14" t="n"/>
+      <c r="M178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n"/>
@@ -5136,6 +5935,10 @@
       <c r="G179" s="14" t="n"/>
       <c r="H179" s="14" t="n"/>
       <c r="I179" s="14" t="n"/>
+      <c r="J179" s="14" t="n"/>
+      <c r="K179" s="14" t="n"/>
+      <c r="L179" s="14" t="n"/>
+      <c r="M179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n"/>
@@ -5147,6 +5950,10 @@
       <c r="G180" s="14" t="n"/>
       <c r="H180" s="14" t="n"/>
       <c r="I180" s="14" t="n"/>
+      <c r="J180" s="14" t="n"/>
+      <c r="K180" s="14" t="n"/>
+      <c r="L180" s="14" t="n"/>
+      <c r="M180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n"/>
@@ -5158,6 +5965,10 @@
       <c r="G181" s="14" t="n"/>
       <c r="H181" s="14" t="n"/>
       <c r="I181" s="14" t="n"/>
+      <c r="J181" s="14" t="n"/>
+      <c r="K181" s="14" t="n"/>
+      <c r="L181" s="14" t="n"/>
+      <c r="M181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n"/>
@@ -5169,6 +5980,10 @@
       <c r="G182" s="14" t="n"/>
       <c r="H182" s="14" t="n"/>
       <c r="I182" s="14" t="n"/>
+      <c r="J182" s="14" t="n"/>
+      <c r="K182" s="14" t="n"/>
+      <c r="L182" s="14" t="n"/>
+      <c r="M182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n"/>
@@ -5180,6 +5995,10 @@
       <c r="G183" s="14" t="n"/>
       <c r="H183" s="14" t="n"/>
       <c r="I183" s="14" t="n"/>
+      <c r="J183" s="14" t="n"/>
+      <c r="K183" s="14" t="n"/>
+      <c r="L183" s="14" t="n"/>
+      <c r="M183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n"/>
@@ -5191,6 +6010,10 @@
       <c r="G184" s="14" t="n"/>
       <c r="H184" s="14" t="n"/>
       <c r="I184" s="14" t="n"/>
+      <c r="J184" s="14" t="n"/>
+      <c r="K184" s="14" t="n"/>
+      <c r="L184" s="14" t="n"/>
+      <c r="M184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n"/>
@@ -5202,6 +6025,10 @@
       <c r="G185" s="14" t="n"/>
       <c r="H185" s="14" t="n"/>
       <c r="I185" s="14" t="n"/>
+      <c r="J185" s="14" t="n"/>
+      <c r="K185" s="14" t="n"/>
+      <c r="L185" s="14" t="n"/>
+      <c r="M185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n"/>
@@ -5213,6 +6040,10 @@
       <c r="G186" s="14" t="n"/>
       <c r="H186" s="14" t="n"/>
       <c r="I186" s="14" t="n"/>
+      <c r="J186" s="14" t="n"/>
+      <c r="K186" s="14" t="n"/>
+      <c r="L186" s="14" t="n"/>
+      <c r="M186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n"/>
@@ -5224,6 +6055,10 @@
       <c r="G187" s="14" t="n"/>
       <c r="H187" s="14" t="n"/>
       <c r="I187" s="14" t="n"/>
+      <c r="J187" s="14" t="n"/>
+      <c r="K187" s="14" t="n"/>
+      <c r="L187" s="14" t="n"/>
+      <c r="M187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n"/>
@@ -5235,6 +6070,10 @@
       <c r="G188" s="14" t="n"/>
       <c r="H188" s="14" t="n"/>
       <c r="I188" s="14" t="n"/>
+      <c r="J188" s="14" t="n"/>
+      <c r="K188" s="14" t="n"/>
+      <c r="L188" s="14" t="n"/>
+      <c r="M188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n"/>
@@ -5246,6 +6085,10 @@
       <c r="G189" s="14" t="n"/>
       <c r="H189" s="14" t="n"/>
       <c r="I189" s="14" t="n"/>
+      <c r="J189" s="14" t="n"/>
+      <c r="K189" s="14" t="n"/>
+      <c r="L189" s="14" t="n"/>
+      <c r="M189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n"/>
@@ -5257,6 +6100,10 @@
       <c r="G190" s="14" t="n"/>
       <c r="H190" s="14" t="n"/>
       <c r="I190" s="14" t="n"/>
+      <c r="J190" s="14" t="n"/>
+      <c r="K190" s="14" t="n"/>
+      <c r="L190" s="14" t="n"/>
+      <c r="M190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n"/>
@@ -5268,6 +6115,10 @@
       <c r="G191" s="14" t="n"/>
       <c r="H191" s="14" t="n"/>
       <c r="I191" s="14" t="n"/>
+      <c r="J191" s="14" t="n"/>
+      <c r="K191" s="14" t="n"/>
+      <c r="L191" s="14" t="n"/>
+      <c r="M191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n"/>
@@ -5279,6 +6130,10 @@
       <c r="G192" s="14" t="n"/>
       <c r="H192" s="14" t="n"/>
       <c r="I192" s="14" t="n"/>
+      <c r="J192" s="14" t="n"/>
+      <c r="K192" s="14" t="n"/>
+      <c r="L192" s="14" t="n"/>
+      <c r="M192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n"/>
@@ -5290,6 +6145,10 @@
       <c r="G193" s="14" t="n"/>
       <c r="H193" s="14" t="n"/>
       <c r="I193" s="14" t="n"/>
+      <c r="J193" s="14" t="n"/>
+      <c r="K193" s="14" t="n"/>
+      <c r="L193" s="14" t="n"/>
+      <c r="M193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n"/>
@@ -5301,6 +6160,10 @@
       <c r="G194" s="14" t="n"/>
       <c r="H194" s="14" t="n"/>
       <c r="I194" s="14" t="n"/>
+      <c r="J194" s="14" t="n"/>
+      <c r="K194" s="14" t="n"/>
+      <c r="L194" s="14" t="n"/>
+      <c r="M194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n"/>
@@ -5312,6 +6175,10 @@
       <c r="G195" s="14" t="n"/>
       <c r="H195" s="14" t="n"/>
       <c r="I195" s="14" t="n"/>
+      <c r="J195" s="14" t="n"/>
+      <c r="K195" s="14" t="n"/>
+      <c r="L195" s="14" t="n"/>
+      <c r="M195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n"/>
@@ -5323,6 +6190,10 @@
       <c r="G196" s="14" t="n"/>
       <c r="H196" s="14" t="n"/>
       <c r="I196" s="14" t="n"/>
+      <c r="J196" s="14" t="n"/>
+      <c r="K196" s="14" t="n"/>
+      <c r="L196" s="14" t="n"/>
+      <c r="M196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n"/>
@@ -5334,6 +6205,10 @@
       <c r="G197" s="14" t="n"/>
       <c r="H197" s="14" t="n"/>
       <c r="I197" s="14" t="n"/>
+      <c r="J197" s="14" t="n"/>
+      <c r="K197" s="14" t="n"/>
+      <c r="L197" s="14" t="n"/>
+      <c r="M197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n"/>
@@ -5345,6 +6220,10 @@
       <c r="G198" s="14" t="n"/>
       <c r="H198" s="14" t="n"/>
       <c r="I198" s="14" t="n"/>
+      <c r="J198" s="14" t="n"/>
+      <c r="K198" s="14" t="n"/>
+      <c r="L198" s="14" t="n"/>
+      <c r="M198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n"/>
@@ -5356,6 +6235,10 @@
       <c r="G199" s="14" t="n"/>
       <c r="H199" s="14" t="n"/>
       <c r="I199" s="14" t="n"/>
+      <c r="J199" s="14" t="n"/>
+      <c r="K199" s="14" t="n"/>
+      <c r="L199" s="14" t="n"/>
+      <c r="M199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n"/>
@@ -5367,6 +6250,10 @@
       <c r="G200" s="14" t="n"/>
       <c r="H200" s="14" t="n"/>
       <c r="I200" s="14" t="n"/>
+      <c r="J200" s="14" t="n"/>
+      <c r="K200" s="14" t="n"/>
+      <c r="L200" s="14" t="n"/>
+      <c r="M200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n"/>
@@ -5378,6 +6265,10 @@
       <c r="G201" s="14" t="n"/>
       <c r="H201" s="14" t="n"/>
       <c r="I201" s="14" t="n"/>
+      <c r="J201" s="14" t="n"/>
+      <c r="K201" s="14" t="n"/>
+      <c r="L201" s="14" t="n"/>
+      <c r="M201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n"/>
@@ -5389,8 +6280,17 @@
       <c r="G202" s="14" t="n"/>
       <c r="H202" s="14" t="n"/>
       <c r="I202" s="14" t="n"/>
+      <c r="J202" s="14" t="n"/>
+      <c r="K202" s="14" t="n"/>
+      <c r="L202" s="14" t="n"/>
+      <c r="M202" s="14" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="J3:J202" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"road,sea,air,multimodal"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7070,22 +7970,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7101,55 +8002,60 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>brand</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>product_family</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>unit_weight_kg</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>length_cm</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>width_cm</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>height_cm</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>unit_price_eur</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>hs_code</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>country_of_origin</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>units_per_pallet</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>requires_conformity_cert</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -7168,42 +8074,47 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
+          <t>FlexiTog</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
           <t>Jackets</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="E2" s="12" t="n">
         <v>2.1</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="F2" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="G2" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="H2" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="I2" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>6201.40</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="L2" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="L2" s="12" t="b">
+      <c r="M2" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="12" t="n"/>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="N2" s="12" t="n"/>
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>EXAMPLE ROW: delete before upload</t>
         </is>
@@ -7223,6 +8134,7 @@
       <c r="K3" s="14" t="n"/>
       <c r="L3" s="14" t="n"/>
       <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n"/>
@@ -7238,6 +8150,7 @@
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
       <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n"/>
@@ -7253,6 +8166,7 @@
       <c r="K5" s="14" t="n"/>
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n"/>
@@ -7268,6 +8182,7 @@
       <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n"/>
@@ -7283,6 +8198,7 @@
       <c r="K7" s="14" t="n"/>
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="14" t="n"/>
+      <c r="N7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
@@ -7298,6 +8214,7 @@
       <c r="K8" s="14" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n"/>
@@ -7313,6 +8230,7 @@
       <c r="K9" s="14" t="n"/>
       <c r="L9" s="14" t="n"/>
       <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n"/>
@@ -7328,6 +8246,7 @@
       <c r="K10" s="14" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n"/>
@@ -7343,6 +8262,7 @@
       <c r="K11" s="14" t="n"/>
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n"/>
@@ -7358,6 +8278,7 @@
       <c r="K12" s="14" t="n"/>
       <c r="L12" s="14" t="n"/>
       <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n"/>
@@ -7373,6 +8294,7 @@
       <c r="K13" s="14" t="n"/>
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n"/>
@@ -7388,6 +8310,7 @@
       <c r="K14" s="14" t="n"/>
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n"/>
@@ -7403,6 +8326,7 @@
       <c r="K15" s="14" t="n"/>
       <c r="L15" s="14" t="n"/>
       <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n"/>
@@ -7418,6 +8342,7 @@
       <c r="K16" s="14" t="n"/>
       <c r="L16" s="14" t="n"/>
       <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n"/>
@@ -7433,6 +8358,7 @@
       <c r="K17" s="14" t="n"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n"/>
@@ -7448,6 +8374,7 @@
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="14" t="n"/>
       <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n"/>
@@ -7463,6 +8390,7 @@
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n"/>
@@ -7478,6 +8406,7 @@
       <c r="K20" s="14" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
@@ -7493,6 +8422,7 @@
       <c r="K21" s="14" t="n"/>
       <c r="L21" s="14" t="n"/>
       <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n"/>
@@ -7508,6 +8438,7 @@
       <c r="K22" s="14" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n"/>
@@ -7523,6 +8454,7 @@
       <c r="K23" s="14" t="n"/>
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="14" t="n"/>
+      <c r="N23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n"/>
@@ -7538,6 +8470,7 @@
       <c r="K24" s="14" t="n"/>
       <c r="L24" s="14" t="n"/>
       <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n"/>
@@ -7553,6 +8486,7 @@
       <c r="K25" s="14" t="n"/>
       <c r="L25" s="14" t="n"/>
       <c r="M25" s="14" t="n"/>
+      <c r="N25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n"/>
@@ -7568,6 +8502,7 @@
       <c r="K26" s="14" t="n"/>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n"/>
@@ -7583,6 +8518,7 @@
       <c r="K27" s="14" t="n"/>
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="14" t="n"/>
+      <c r="N27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n"/>
@@ -7598,6 +8534,7 @@
       <c r="K28" s="14" t="n"/>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n"/>
@@ -7613,6 +8550,7 @@
       <c r="K29" s="14" t="n"/>
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="14" t="n"/>
+      <c r="N29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n"/>
@@ -7628,6 +8566,7 @@
       <c r="K30" s="14" t="n"/>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n"/>
@@ -7643,6 +8582,7 @@
       <c r="K31" s="14" t="n"/>
       <c r="L31" s="14" t="n"/>
       <c r="M31" s="14" t="n"/>
+      <c r="N31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n"/>
@@ -7658,6 +8598,7 @@
       <c r="K32" s="14" t="n"/>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n"/>
@@ -7673,6 +8614,7 @@
       <c r="K33" s="14" t="n"/>
       <c r="L33" s="14" t="n"/>
       <c r="M33" s="14" t="n"/>
+      <c r="N33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n"/>
@@ -7688,6 +8630,7 @@
       <c r="K34" s="14" t="n"/>
       <c r="L34" s="14" t="n"/>
       <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n"/>
@@ -7703,6 +8646,7 @@
       <c r="K35" s="14" t="n"/>
       <c r="L35" s="14" t="n"/>
       <c r="M35" s="14" t="n"/>
+      <c r="N35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n"/>
@@ -7718,6 +8662,7 @@
       <c r="K36" s="14" t="n"/>
       <c r="L36" s="14" t="n"/>
       <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n"/>
@@ -7733,6 +8678,7 @@
       <c r="K37" s="14" t="n"/>
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n"/>
@@ -7748,6 +8694,7 @@
       <c r="K38" s="14" t="n"/>
       <c r="L38" s="14" t="n"/>
       <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n"/>
@@ -7763,6 +8710,7 @@
       <c r="K39" s="14" t="n"/>
       <c r="L39" s="14" t="n"/>
       <c r="M39" s="14" t="n"/>
+      <c r="N39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n"/>
@@ -7778,6 +8726,7 @@
       <c r="K40" s="14" t="n"/>
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="14" t="n"/>
+      <c r="N40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n"/>
@@ -7793,6 +8742,7 @@
       <c r="K41" s="14" t="n"/>
       <c r="L41" s="14" t="n"/>
       <c r="M41" s="14" t="n"/>
+      <c r="N41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n"/>
@@ -7808,6 +8758,7 @@
       <c r="K42" s="14" t="n"/>
       <c r="L42" s="14" t="n"/>
       <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n"/>
@@ -7823,6 +8774,7 @@
       <c r="K43" s="14" t="n"/>
       <c r="L43" s="14" t="n"/>
       <c r="M43" s="14" t="n"/>
+      <c r="N43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n"/>
@@ -7838,6 +8790,7 @@
       <c r="K44" s="14" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n"/>
@@ -7853,6 +8806,7 @@
       <c r="K45" s="14" t="n"/>
       <c r="L45" s="14" t="n"/>
       <c r="M45" s="14" t="n"/>
+      <c r="N45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n"/>
@@ -7868,6 +8822,7 @@
       <c r="K46" s="14" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="14" t="n"/>
+      <c r="N46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n"/>
@@ -7883,6 +8838,7 @@
       <c r="K47" s="14" t="n"/>
       <c r="L47" s="14" t="n"/>
       <c r="M47" s="14" t="n"/>
+      <c r="N47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n"/>
@@ -7898,6 +8854,7 @@
       <c r="K48" s="14" t="n"/>
       <c r="L48" s="14" t="n"/>
       <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n"/>
@@ -7913,6 +8870,7 @@
       <c r="K49" s="14" t="n"/>
       <c r="L49" s="14" t="n"/>
       <c r="M49" s="14" t="n"/>
+      <c r="N49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n"/>
@@ -7928,6 +8886,7 @@
       <c r="K50" s="14" t="n"/>
       <c r="L50" s="14" t="n"/>
       <c r="M50" s="14" t="n"/>
+      <c r="N50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n"/>
@@ -7943,6 +8902,7 @@
       <c r="K51" s="14" t="n"/>
       <c r="L51" s="14" t="n"/>
       <c r="M51" s="14" t="n"/>
+      <c r="N51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n"/>
@@ -7958,6 +8918,7 @@
       <c r="K52" s="14" t="n"/>
       <c r="L52" s="14" t="n"/>
       <c r="M52" s="14" t="n"/>
+      <c r="N52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n"/>
@@ -7973,6 +8934,7 @@
       <c r="K53" s="14" t="n"/>
       <c r="L53" s="14" t="n"/>
       <c r="M53" s="14" t="n"/>
+      <c r="N53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n"/>
@@ -7988,6 +8950,7 @@
       <c r="K54" s="14" t="n"/>
       <c r="L54" s="14" t="n"/>
       <c r="M54" s="14" t="n"/>
+      <c r="N54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n"/>
@@ -8003,6 +8966,7 @@
       <c r="K55" s="14" t="n"/>
       <c r="L55" s="14" t="n"/>
       <c r="M55" s="14" t="n"/>
+      <c r="N55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n"/>
@@ -8018,6 +8982,7 @@
       <c r="K56" s="14" t="n"/>
       <c r="L56" s="14" t="n"/>
       <c r="M56" s="14" t="n"/>
+      <c r="N56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n"/>
@@ -8033,6 +8998,7 @@
       <c r="K57" s="14" t="n"/>
       <c r="L57" s="14" t="n"/>
       <c r="M57" s="14" t="n"/>
+      <c r="N57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n"/>
@@ -8048,6 +9014,7 @@
       <c r="K58" s="14" t="n"/>
       <c r="L58" s="14" t="n"/>
       <c r="M58" s="14" t="n"/>
+      <c r="N58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n"/>
@@ -8063,6 +9030,7 @@
       <c r="K59" s="14" t="n"/>
       <c r="L59" s="14" t="n"/>
       <c r="M59" s="14" t="n"/>
+      <c r="N59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n"/>
@@ -8078,6 +9046,7 @@
       <c r="K60" s="14" t="n"/>
       <c r="L60" s="14" t="n"/>
       <c r="M60" s="14" t="n"/>
+      <c r="N60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n"/>
@@ -8093,6 +9062,7 @@
       <c r="K61" s="14" t="n"/>
       <c r="L61" s="14" t="n"/>
       <c r="M61" s="14" t="n"/>
+      <c r="N61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n"/>
@@ -8108,6 +9078,7 @@
       <c r="K62" s="14" t="n"/>
       <c r="L62" s="14" t="n"/>
       <c r="M62" s="14" t="n"/>
+      <c r="N62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n"/>
@@ -8123,6 +9094,7 @@
       <c r="K63" s="14" t="n"/>
       <c r="L63" s="14" t="n"/>
       <c r="M63" s="14" t="n"/>
+      <c r="N63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n"/>
@@ -8138,6 +9110,7 @@
       <c r="K64" s="14" t="n"/>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="14" t="n"/>
+      <c r="N64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n"/>
@@ -8153,6 +9126,7 @@
       <c r="K65" s="14" t="n"/>
       <c r="L65" s="14" t="n"/>
       <c r="M65" s="14" t="n"/>
+      <c r="N65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n"/>
@@ -8168,6 +9142,7 @@
       <c r="K66" s="14" t="n"/>
       <c r="L66" s="14" t="n"/>
       <c r="M66" s="14" t="n"/>
+      <c r="N66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n"/>
@@ -8183,6 +9158,7 @@
       <c r="K67" s="14" t="n"/>
       <c r="L67" s="14" t="n"/>
       <c r="M67" s="14" t="n"/>
+      <c r="N67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n"/>
@@ -8198,6 +9174,7 @@
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n"/>
       <c r="M68" s="14" t="n"/>
+      <c r="N68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n"/>
@@ -8213,6 +9190,7 @@
       <c r="K69" s="14" t="n"/>
       <c r="L69" s="14" t="n"/>
       <c r="M69" s="14" t="n"/>
+      <c r="N69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n"/>
@@ -8228,6 +9206,7 @@
       <c r="K70" s="14" t="n"/>
       <c r="L70" s="14" t="n"/>
       <c r="M70" s="14" t="n"/>
+      <c r="N70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n"/>
@@ -8243,6 +9222,7 @@
       <c r="K71" s="14" t="n"/>
       <c r="L71" s="14" t="n"/>
       <c r="M71" s="14" t="n"/>
+      <c r="N71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n"/>
@@ -8258,6 +9238,7 @@
       <c r="K72" s="14" t="n"/>
       <c r="L72" s="14" t="n"/>
       <c r="M72" s="14" t="n"/>
+      <c r="N72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n"/>
@@ -8273,6 +9254,7 @@
       <c r="K73" s="14" t="n"/>
       <c r="L73" s="14" t="n"/>
       <c r="M73" s="14" t="n"/>
+      <c r="N73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n"/>
@@ -8288,6 +9270,7 @@
       <c r="K74" s="14" t="n"/>
       <c r="L74" s="14" t="n"/>
       <c r="M74" s="14" t="n"/>
+      <c r="N74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n"/>
@@ -8303,6 +9286,7 @@
       <c r="K75" s="14" t="n"/>
       <c r="L75" s="14" t="n"/>
       <c r="M75" s="14" t="n"/>
+      <c r="N75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n"/>
@@ -8318,6 +9302,7 @@
       <c r="K76" s="14" t="n"/>
       <c r="L76" s="14" t="n"/>
       <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n"/>
@@ -8333,6 +9318,7 @@
       <c r="K77" s="14" t="n"/>
       <c r="L77" s="14" t="n"/>
       <c r="M77" s="14" t="n"/>
+      <c r="N77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n"/>
@@ -8348,6 +9334,7 @@
       <c r="K78" s="14" t="n"/>
       <c r="L78" s="14" t="n"/>
       <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n"/>
@@ -8363,6 +9350,7 @@
       <c r="K79" s="14" t="n"/>
       <c r="L79" s="14" t="n"/>
       <c r="M79" s="14" t="n"/>
+      <c r="N79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n"/>
@@ -8378,6 +9366,7 @@
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="14" t="n"/>
       <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n"/>
@@ -8393,6 +9382,7 @@
       <c r="K81" s="14" t="n"/>
       <c r="L81" s="14" t="n"/>
       <c r="M81" s="14" t="n"/>
+      <c r="N81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n"/>
@@ -8408,6 +9398,7 @@
       <c r="K82" s="14" t="n"/>
       <c r="L82" s="14" t="n"/>
       <c r="M82" s="14" t="n"/>
+      <c r="N82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n"/>
@@ -8423,6 +9414,7 @@
       <c r="K83" s="14" t="n"/>
       <c r="L83" s="14" t="n"/>
       <c r="M83" s="14" t="n"/>
+      <c r="N83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n"/>
@@ -8438,6 +9430,7 @@
       <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
       <c r="M84" s="14" t="n"/>
+      <c r="N84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n"/>
@@ -8453,6 +9446,7 @@
       <c r="K85" s="14" t="n"/>
       <c r="L85" s="14" t="n"/>
       <c r="M85" s="14" t="n"/>
+      <c r="N85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n"/>
@@ -8468,6 +9462,7 @@
       <c r="K86" s="14" t="n"/>
       <c r="L86" s="14" t="n"/>
       <c r="M86" s="14" t="n"/>
+      <c r="N86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n"/>
@@ -8483,6 +9478,7 @@
       <c r="K87" s="14" t="n"/>
       <c r="L87" s="14" t="n"/>
       <c r="M87" s="14" t="n"/>
+      <c r="N87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n"/>
@@ -8498,6 +9494,7 @@
       <c r="K88" s="14" t="n"/>
       <c r="L88" s="14" t="n"/>
       <c r="M88" s="14" t="n"/>
+      <c r="N88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n"/>
@@ -8513,6 +9510,7 @@
       <c r="K89" s="14" t="n"/>
       <c r="L89" s="14" t="n"/>
       <c r="M89" s="14" t="n"/>
+      <c r="N89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n"/>
@@ -8528,6 +9526,7 @@
       <c r="K90" s="14" t="n"/>
       <c r="L90" s="14" t="n"/>
       <c r="M90" s="14" t="n"/>
+      <c r="N90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n"/>
@@ -8543,6 +9542,7 @@
       <c r="K91" s="14" t="n"/>
       <c r="L91" s="14" t="n"/>
       <c r="M91" s="14" t="n"/>
+      <c r="N91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n"/>
@@ -8558,6 +9558,7 @@
       <c r="K92" s="14" t="n"/>
       <c r="L92" s="14" t="n"/>
       <c r="M92" s="14" t="n"/>
+      <c r="N92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n"/>
@@ -8573,6 +9574,7 @@
       <c r="K93" s="14" t="n"/>
       <c r="L93" s="14" t="n"/>
       <c r="M93" s="14" t="n"/>
+      <c r="N93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n"/>
@@ -8588,6 +9590,7 @@
       <c r="K94" s="14" t="n"/>
       <c r="L94" s="14" t="n"/>
       <c r="M94" s="14" t="n"/>
+      <c r="N94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n"/>
@@ -8603,6 +9606,7 @@
       <c r="K95" s="14" t="n"/>
       <c r="L95" s="14" t="n"/>
       <c r="M95" s="14" t="n"/>
+      <c r="N95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n"/>
@@ -8618,6 +9622,7 @@
       <c r="K96" s="14" t="n"/>
       <c r="L96" s="14" t="n"/>
       <c r="M96" s="14" t="n"/>
+      <c r="N96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n"/>
@@ -8633,6 +9638,7 @@
       <c r="K97" s="14" t="n"/>
       <c r="L97" s="14" t="n"/>
       <c r="M97" s="14" t="n"/>
+      <c r="N97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n"/>
@@ -8648,6 +9654,7 @@
       <c r="K98" s="14" t="n"/>
       <c r="L98" s="14" t="n"/>
       <c r="M98" s="14" t="n"/>
+      <c r="N98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n"/>
@@ -8663,6 +9670,7 @@
       <c r="K99" s="14" t="n"/>
       <c r="L99" s="14" t="n"/>
       <c r="M99" s="14" t="n"/>
+      <c r="N99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n"/>
@@ -8678,6 +9686,7 @@
       <c r="K100" s="14" t="n"/>
       <c r="L100" s="14" t="n"/>
       <c r="M100" s="14" t="n"/>
+      <c r="N100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n"/>
@@ -8693,6 +9702,7 @@
       <c r="K101" s="14" t="n"/>
       <c r="L101" s="14" t="n"/>
       <c r="M101" s="14" t="n"/>
+      <c r="N101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n"/>
@@ -8708,6 +9718,7 @@
       <c r="K102" s="14" t="n"/>
       <c r="L102" s="14" t="n"/>
       <c r="M102" s="14" t="n"/>
+      <c r="N102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n"/>
@@ -8723,6 +9734,7 @@
       <c r="K103" s="14" t="n"/>
       <c r="L103" s="14" t="n"/>
       <c r="M103" s="14" t="n"/>
+      <c r="N103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n"/>
@@ -8738,6 +9750,7 @@
       <c r="K104" s="14" t="n"/>
       <c r="L104" s="14" t="n"/>
       <c r="M104" s="14" t="n"/>
+      <c r="N104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n"/>
@@ -8753,6 +9766,7 @@
       <c r="K105" s="14" t="n"/>
       <c r="L105" s="14" t="n"/>
       <c r="M105" s="14" t="n"/>
+      <c r="N105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n"/>
@@ -8768,6 +9782,7 @@
       <c r="K106" s="14" t="n"/>
       <c r="L106" s="14" t="n"/>
       <c r="M106" s="14" t="n"/>
+      <c r="N106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n"/>
@@ -8783,6 +9798,7 @@
       <c r="K107" s="14" t="n"/>
       <c r="L107" s="14" t="n"/>
       <c r="M107" s="14" t="n"/>
+      <c r="N107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n"/>
@@ -8798,6 +9814,7 @@
       <c r="K108" s="14" t="n"/>
       <c r="L108" s="14" t="n"/>
       <c r="M108" s="14" t="n"/>
+      <c r="N108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n"/>
@@ -8813,6 +9830,7 @@
       <c r="K109" s="14" t="n"/>
       <c r="L109" s="14" t="n"/>
       <c r="M109" s="14" t="n"/>
+      <c r="N109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n"/>
@@ -8828,6 +9846,7 @@
       <c r="K110" s="14" t="n"/>
       <c r="L110" s="14" t="n"/>
       <c r="M110" s="14" t="n"/>
+      <c r="N110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n"/>
@@ -8843,6 +9862,7 @@
       <c r="K111" s="14" t="n"/>
       <c r="L111" s="14" t="n"/>
       <c r="M111" s="14" t="n"/>
+      <c r="N111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n"/>
@@ -8858,6 +9878,7 @@
       <c r="K112" s="14" t="n"/>
       <c r="L112" s="14" t="n"/>
       <c r="M112" s="14" t="n"/>
+      <c r="N112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n"/>
@@ -8873,6 +9894,7 @@
       <c r="K113" s="14" t="n"/>
       <c r="L113" s="14" t="n"/>
       <c r="M113" s="14" t="n"/>
+      <c r="N113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n"/>
@@ -8888,6 +9910,7 @@
       <c r="K114" s="14" t="n"/>
       <c r="L114" s="14" t="n"/>
       <c r="M114" s="14" t="n"/>
+      <c r="N114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n"/>
@@ -8903,6 +9926,7 @@
       <c r="K115" s="14" t="n"/>
       <c r="L115" s="14" t="n"/>
       <c r="M115" s="14" t="n"/>
+      <c r="N115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n"/>
@@ -8918,6 +9942,7 @@
       <c r="K116" s="14" t="n"/>
       <c r="L116" s="14" t="n"/>
       <c r="M116" s="14" t="n"/>
+      <c r="N116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n"/>
@@ -8933,6 +9958,7 @@
       <c r="K117" s="14" t="n"/>
       <c r="L117" s="14" t="n"/>
       <c r="M117" s="14" t="n"/>
+      <c r="N117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n"/>
@@ -8948,6 +9974,7 @@
       <c r="K118" s="14" t="n"/>
       <c r="L118" s="14" t="n"/>
       <c r="M118" s="14" t="n"/>
+      <c r="N118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n"/>
@@ -8963,6 +9990,7 @@
       <c r="K119" s="14" t="n"/>
       <c r="L119" s="14" t="n"/>
       <c r="M119" s="14" t="n"/>
+      <c r="N119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n"/>
@@ -8978,6 +10006,7 @@
       <c r="K120" s="14" t="n"/>
       <c r="L120" s="14" t="n"/>
       <c r="M120" s="14" t="n"/>
+      <c r="N120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n"/>
@@ -8993,6 +10022,7 @@
       <c r="K121" s="14" t="n"/>
       <c r="L121" s="14" t="n"/>
       <c r="M121" s="14" t="n"/>
+      <c r="N121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n"/>
@@ -9008,6 +10038,7 @@
       <c r="K122" s="14" t="n"/>
       <c r="L122" s="14" t="n"/>
       <c r="M122" s="14" t="n"/>
+      <c r="N122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n"/>
@@ -9023,6 +10054,7 @@
       <c r="K123" s="14" t="n"/>
       <c r="L123" s="14" t="n"/>
       <c r="M123" s="14" t="n"/>
+      <c r="N123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n"/>
@@ -9038,6 +10070,7 @@
       <c r="K124" s="14" t="n"/>
       <c r="L124" s="14" t="n"/>
       <c r="M124" s="14" t="n"/>
+      <c r="N124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n"/>
@@ -9053,6 +10086,7 @@
       <c r="K125" s="14" t="n"/>
       <c r="L125" s="14" t="n"/>
       <c r="M125" s="14" t="n"/>
+      <c r="N125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n"/>
@@ -9068,6 +10102,7 @@
       <c r="K126" s="14" t="n"/>
       <c r="L126" s="14" t="n"/>
       <c r="M126" s="14" t="n"/>
+      <c r="N126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n"/>
@@ -9083,6 +10118,7 @@
       <c r="K127" s="14" t="n"/>
       <c r="L127" s="14" t="n"/>
       <c r="M127" s="14" t="n"/>
+      <c r="N127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n"/>
@@ -9098,6 +10134,7 @@
       <c r="K128" s="14" t="n"/>
       <c r="L128" s="14" t="n"/>
       <c r="M128" s="14" t="n"/>
+      <c r="N128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n"/>
@@ -9113,6 +10150,7 @@
       <c r="K129" s="14" t="n"/>
       <c r="L129" s="14" t="n"/>
       <c r="M129" s="14" t="n"/>
+      <c r="N129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n"/>
@@ -9128,6 +10166,7 @@
       <c r="K130" s="14" t="n"/>
       <c r="L130" s="14" t="n"/>
       <c r="M130" s="14" t="n"/>
+      <c r="N130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n"/>
@@ -9143,6 +10182,7 @@
       <c r="K131" s="14" t="n"/>
       <c r="L131" s="14" t="n"/>
       <c r="M131" s="14" t="n"/>
+      <c r="N131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="14" t="n"/>
@@ -9158,6 +10198,7 @@
       <c r="K132" s="14" t="n"/>
       <c r="L132" s="14" t="n"/>
       <c r="M132" s="14" t="n"/>
+      <c r="N132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n"/>
@@ -9173,6 +10214,7 @@
       <c r="K133" s="14" t="n"/>
       <c r="L133" s="14" t="n"/>
       <c r="M133" s="14" t="n"/>
+      <c r="N133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="14" t="n"/>
@@ -9188,6 +10230,7 @@
       <c r="K134" s="14" t="n"/>
       <c r="L134" s="14" t="n"/>
       <c r="M134" s="14" t="n"/>
+      <c r="N134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n"/>
@@ -9203,6 +10246,7 @@
       <c r="K135" s="14" t="n"/>
       <c r="L135" s="14" t="n"/>
       <c r="M135" s="14" t="n"/>
+      <c r="N135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="14" t="n"/>
@@ -9218,6 +10262,7 @@
       <c r="K136" s="14" t="n"/>
       <c r="L136" s="14" t="n"/>
       <c r="M136" s="14" t="n"/>
+      <c r="N136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n"/>
@@ -9233,6 +10278,7 @@
       <c r="K137" s="14" t="n"/>
       <c r="L137" s="14" t="n"/>
       <c r="M137" s="14" t="n"/>
+      <c r="N137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="14" t="n"/>
@@ -9248,6 +10294,7 @@
       <c r="K138" s="14" t="n"/>
       <c r="L138" s="14" t="n"/>
       <c r="M138" s="14" t="n"/>
+      <c r="N138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n"/>
@@ -9263,6 +10310,7 @@
       <c r="K139" s="14" t="n"/>
       <c r="L139" s="14" t="n"/>
       <c r="M139" s="14" t="n"/>
+      <c r="N139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="14" t="n"/>
@@ -9278,6 +10326,7 @@
       <c r="K140" s="14" t="n"/>
       <c r="L140" s="14" t="n"/>
       <c r="M140" s="14" t="n"/>
+      <c r="N140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n"/>
@@ -9293,6 +10342,7 @@
       <c r="K141" s="14" t="n"/>
       <c r="L141" s="14" t="n"/>
       <c r="M141" s="14" t="n"/>
+      <c r="N141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="14" t="n"/>
@@ -9308,6 +10358,7 @@
       <c r="K142" s="14" t="n"/>
       <c r="L142" s="14" t="n"/>
       <c r="M142" s="14" t="n"/>
+      <c r="N142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n"/>
@@ -9323,6 +10374,7 @@
       <c r="K143" s="14" t="n"/>
       <c r="L143" s="14" t="n"/>
       <c r="M143" s="14" t="n"/>
+      <c r="N143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n"/>
@@ -9338,6 +10390,7 @@
       <c r="K144" s="14" t="n"/>
       <c r="L144" s="14" t="n"/>
       <c r="M144" s="14" t="n"/>
+      <c r="N144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n"/>
@@ -9353,6 +10406,7 @@
       <c r="K145" s="14" t="n"/>
       <c r="L145" s="14" t="n"/>
       <c r="M145" s="14" t="n"/>
+      <c r="N145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="14" t="n"/>
@@ -9368,6 +10422,7 @@
       <c r="K146" s="14" t="n"/>
       <c r="L146" s="14" t="n"/>
       <c r="M146" s="14" t="n"/>
+      <c r="N146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n"/>
@@ -9383,6 +10438,7 @@
       <c r="K147" s="14" t="n"/>
       <c r="L147" s="14" t="n"/>
       <c r="M147" s="14" t="n"/>
+      <c r="N147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="14" t="n"/>
@@ -9398,6 +10454,7 @@
       <c r="K148" s="14" t="n"/>
       <c r="L148" s="14" t="n"/>
       <c r="M148" s="14" t="n"/>
+      <c r="N148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n"/>
@@ -9413,6 +10470,7 @@
       <c r="K149" s="14" t="n"/>
       <c r="L149" s="14" t="n"/>
       <c r="M149" s="14" t="n"/>
+      <c r="N149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="14" t="n"/>
@@ -9428,6 +10486,7 @@
       <c r="K150" s="14" t="n"/>
       <c r="L150" s="14" t="n"/>
       <c r="M150" s="14" t="n"/>
+      <c r="N150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n"/>
@@ -9443,6 +10502,7 @@
       <c r="K151" s="14" t="n"/>
       <c r="L151" s="14" t="n"/>
       <c r="M151" s="14" t="n"/>
+      <c r="N151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="14" t="n"/>
@@ -9458,6 +10518,7 @@
       <c r="K152" s="14" t="n"/>
       <c r="L152" s="14" t="n"/>
       <c r="M152" s="14" t="n"/>
+      <c r="N152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n"/>
@@ -9473,6 +10534,7 @@
       <c r="K153" s="14" t="n"/>
       <c r="L153" s="14" t="n"/>
       <c r="M153" s="14" t="n"/>
+      <c r="N153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="14" t="n"/>
@@ -9488,6 +10550,7 @@
       <c r="K154" s="14" t="n"/>
       <c r="L154" s="14" t="n"/>
       <c r="M154" s="14" t="n"/>
+      <c r="N154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n"/>
@@ -9503,6 +10566,7 @@
       <c r="K155" s="14" t="n"/>
       <c r="L155" s="14" t="n"/>
       <c r="M155" s="14" t="n"/>
+      <c r="N155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n"/>
@@ -9518,6 +10582,7 @@
       <c r="K156" s="14" t="n"/>
       <c r="L156" s="14" t="n"/>
       <c r="M156" s="14" t="n"/>
+      <c r="N156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n"/>
@@ -9533,6 +10598,7 @@
       <c r="K157" s="14" t="n"/>
       <c r="L157" s="14" t="n"/>
       <c r="M157" s="14" t="n"/>
+      <c r="N157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="14" t="n"/>
@@ -9548,6 +10614,7 @@
       <c r="K158" s="14" t="n"/>
       <c r="L158" s="14" t="n"/>
       <c r="M158" s="14" t="n"/>
+      <c r="N158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n"/>
@@ -9563,6 +10630,7 @@
       <c r="K159" s="14" t="n"/>
       <c r="L159" s="14" t="n"/>
       <c r="M159" s="14" t="n"/>
+      <c r="N159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="14" t="n"/>
@@ -9578,6 +10646,7 @@
       <c r="K160" s="14" t="n"/>
       <c r="L160" s="14" t="n"/>
       <c r="M160" s="14" t="n"/>
+      <c r="N160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n"/>
@@ -9593,6 +10662,7 @@
       <c r="K161" s="14" t="n"/>
       <c r="L161" s="14" t="n"/>
       <c r="M161" s="14" t="n"/>
+      <c r="N161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="14" t="n"/>
@@ -9608,6 +10678,7 @@
       <c r="K162" s="14" t="n"/>
       <c r="L162" s="14" t="n"/>
       <c r="M162" s="14" t="n"/>
+      <c r="N162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n"/>
@@ -9623,6 +10694,7 @@
       <c r="K163" s="14" t="n"/>
       <c r="L163" s="14" t="n"/>
       <c r="M163" s="14" t="n"/>
+      <c r="N163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n"/>
@@ -9638,6 +10710,7 @@
       <c r="K164" s="14" t="n"/>
       <c r="L164" s="14" t="n"/>
       <c r="M164" s="14" t="n"/>
+      <c r="N164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n"/>
@@ -9653,6 +10726,7 @@
       <c r="K165" s="14" t="n"/>
       <c r="L165" s="14" t="n"/>
       <c r="M165" s="14" t="n"/>
+      <c r="N165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n"/>
@@ -9668,6 +10742,7 @@
       <c r="K166" s="14" t="n"/>
       <c r="L166" s="14" t="n"/>
       <c r="M166" s="14" t="n"/>
+      <c r="N166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n"/>
@@ -9683,6 +10758,7 @@
       <c r="K167" s="14" t="n"/>
       <c r="L167" s="14" t="n"/>
       <c r="M167" s="14" t="n"/>
+      <c r="N167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="14" t="n"/>
@@ -9698,6 +10774,7 @@
       <c r="K168" s="14" t="n"/>
       <c r="L168" s="14" t="n"/>
       <c r="M168" s="14" t="n"/>
+      <c r="N168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n"/>
@@ -9713,6 +10790,7 @@
       <c r="K169" s="14" t="n"/>
       <c r="L169" s="14" t="n"/>
       <c r="M169" s="14" t="n"/>
+      <c r="N169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="14" t="n"/>
@@ -9728,6 +10806,7 @@
       <c r="K170" s="14" t="n"/>
       <c r="L170" s="14" t="n"/>
       <c r="M170" s="14" t="n"/>
+      <c r="N170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n"/>
@@ -9743,6 +10822,7 @@
       <c r="K171" s="14" t="n"/>
       <c r="L171" s="14" t="n"/>
       <c r="M171" s="14" t="n"/>
+      <c r="N171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n"/>
@@ -9758,6 +10838,7 @@
       <c r="K172" s="14" t="n"/>
       <c r="L172" s="14" t="n"/>
       <c r="M172" s="14" t="n"/>
+      <c r="N172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n"/>
@@ -9773,6 +10854,7 @@
       <c r="K173" s="14" t="n"/>
       <c r="L173" s="14" t="n"/>
       <c r="M173" s="14" t="n"/>
+      <c r="N173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n"/>
@@ -9788,6 +10870,7 @@
       <c r="K174" s="14" t="n"/>
       <c r="L174" s="14" t="n"/>
       <c r="M174" s="14" t="n"/>
+      <c r="N174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n"/>
@@ -9803,6 +10886,7 @@
       <c r="K175" s="14" t="n"/>
       <c r="L175" s="14" t="n"/>
       <c r="M175" s="14" t="n"/>
+      <c r="N175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n"/>
@@ -9818,6 +10902,7 @@
       <c r="K176" s="14" t="n"/>
       <c r="L176" s="14" t="n"/>
       <c r="M176" s="14" t="n"/>
+      <c r="N176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n"/>
@@ -9833,6 +10918,7 @@
       <c r="K177" s="14" t="n"/>
       <c r="L177" s="14" t="n"/>
       <c r="M177" s="14" t="n"/>
+      <c r="N177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n"/>
@@ -9848,6 +10934,7 @@
       <c r="K178" s="14" t="n"/>
       <c r="L178" s="14" t="n"/>
       <c r="M178" s="14" t="n"/>
+      <c r="N178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n"/>
@@ -9863,6 +10950,7 @@
       <c r="K179" s="14" t="n"/>
       <c r="L179" s="14" t="n"/>
       <c r="M179" s="14" t="n"/>
+      <c r="N179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n"/>
@@ -9878,6 +10966,7 @@
       <c r="K180" s="14" t="n"/>
       <c r="L180" s="14" t="n"/>
       <c r="M180" s="14" t="n"/>
+      <c r="N180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n"/>
@@ -9893,6 +10982,7 @@
       <c r="K181" s="14" t="n"/>
       <c r="L181" s="14" t="n"/>
       <c r="M181" s="14" t="n"/>
+      <c r="N181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n"/>
@@ -9908,6 +10998,7 @@
       <c r="K182" s="14" t="n"/>
       <c r="L182" s="14" t="n"/>
       <c r="M182" s="14" t="n"/>
+      <c r="N182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n"/>
@@ -9923,6 +11014,7 @@
       <c r="K183" s="14" t="n"/>
       <c r="L183" s="14" t="n"/>
       <c r="M183" s="14" t="n"/>
+      <c r="N183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n"/>
@@ -9938,6 +11030,7 @@
       <c r="K184" s="14" t="n"/>
       <c r="L184" s="14" t="n"/>
       <c r="M184" s="14" t="n"/>
+      <c r="N184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n"/>
@@ -9953,6 +11046,7 @@
       <c r="K185" s="14" t="n"/>
       <c r="L185" s="14" t="n"/>
       <c r="M185" s="14" t="n"/>
+      <c r="N185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n"/>
@@ -9968,6 +11062,7 @@
       <c r="K186" s="14" t="n"/>
       <c r="L186" s="14" t="n"/>
       <c r="M186" s="14" t="n"/>
+      <c r="N186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n"/>
@@ -9983,6 +11078,7 @@
       <c r="K187" s="14" t="n"/>
       <c r="L187" s="14" t="n"/>
       <c r="M187" s="14" t="n"/>
+      <c r="N187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n"/>
@@ -9998,6 +11094,7 @@
       <c r="K188" s="14" t="n"/>
       <c r="L188" s="14" t="n"/>
       <c r="M188" s="14" t="n"/>
+      <c r="N188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n"/>
@@ -10013,6 +11110,7 @@
       <c r="K189" s="14" t="n"/>
       <c r="L189" s="14" t="n"/>
       <c r="M189" s="14" t="n"/>
+      <c r="N189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n"/>
@@ -10028,6 +11126,7 @@
       <c r="K190" s="14" t="n"/>
       <c r="L190" s="14" t="n"/>
       <c r="M190" s="14" t="n"/>
+      <c r="N190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n"/>
@@ -10043,6 +11142,7 @@
       <c r="K191" s="14" t="n"/>
       <c r="L191" s="14" t="n"/>
       <c r="M191" s="14" t="n"/>
+      <c r="N191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n"/>
@@ -10058,6 +11158,7 @@
       <c r="K192" s="14" t="n"/>
       <c r="L192" s="14" t="n"/>
       <c r="M192" s="14" t="n"/>
+      <c r="N192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n"/>
@@ -10073,6 +11174,7 @@
       <c r="K193" s="14" t="n"/>
       <c r="L193" s="14" t="n"/>
       <c r="M193" s="14" t="n"/>
+      <c r="N193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n"/>
@@ -10088,6 +11190,7 @@
       <c r="K194" s="14" t="n"/>
       <c r="L194" s="14" t="n"/>
       <c r="M194" s="14" t="n"/>
+      <c r="N194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n"/>
@@ -10103,6 +11206,7 @@
       <c r="K195" s="14" t="n"/>
       <c r="L195" s="14" t="n"/>
       <c r="M195" s="14" t="n"/>
+      <c r="N195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n"/>
@@ -10118,6 +11222,7 @@
       <c r="K196" s="14" t="n"/>
       <c r="L196" s="14" t="n"/>
       <c r="M196" s="14" t="n"/>
+      <c r="N196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n"/>
@@ -10133,6 +11238,7 @@
       <c r="K197" s="14" t="n"/>
       <c r="L197" s="14" t="n"/>
       <c r="M197" s="14" t="n"/>
+      <c r="N197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n"/>
@@ -10148,6 +11254,7 @@
       <c r="K198" s="14" t="n"/>
       <c r="L198" s="14" t="n"/>
       <c r="M198" s="14" t="n"/>
+      <c r="N198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n"/>
@@ -10163,6 +11270,7 @@
       <c r="K199" s="14" t="n"/>
       <c r="L199" s="14" t="n"/>
       <c r="M199" s="14" t="n"/>
+      <c r="N199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n"/>
@@ -10178,6 +11286,7 @@
       <c r="K200" s="14" t="n"/>
       <c r="L200" s="14" t="n"/>
       <c r="M200" s="14" t="n"/>
+      <c r="N200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n"/>
@@ -10193,6 +11302,7 @@
       <c r="K201" s="14" t="n"/>
       <c r="L201" s="14" t="n"/>
       <c r="M201" s="14" t="n"/>
+      <c r="N201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n"/>
@@ -10208,6 +11318,7 @@
       <c r="K202" s="14" t="n"/>
       <c r="L202" s="14" t="n"/>
       <c r="M202" s="14" t="n"/>
+      <c r="N202" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10306,14 +11417,14 @@
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>FT-GLV-200</t>
+          <t>GF-TRS-200</t>
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>1380</v>
+        <v>80</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>12420</v>
+        <v>6320</v>
       </c>
       <c r="G2" s="12" t="inlineStr">
         <is>
@@ -12749,7 +13860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L202"/>
+  <dimension ref="A1:N202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12763,6 +13874,8 @@
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12818,6 +13931,16 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
@@ -12862,7 +13985,9 @@
       </c>
       <c r="J2" s="12" t="n"/>
       <c r="K2" s="12" t="n"/>
-      <c r="L2" s="13" t="inlineStr">
+      <c r="L2" s="12" t="n"/>
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="13" t="inlineStr">
         <is>
           <t>EXAMPLE ROW: delete before upload</t>
         </is>
@@ -12880,6 +14005,8 @@
       <c r="I3" s="14" t="n"/>
       <c r="J3" s="14" t="n"/>
       <c r="K3" s="14" t="n"/>
+      <c r="L3" s="14" t="n"/>
+      <c r="M3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n"/>
@@ -12893,6 +14020,8 @@
       <c r="I4" s="14" t="n"/>
       <c r="J4" s="14" t="n"/>
       <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n"/>
@@ -12906,6 +14035,8 @@
       <c r="I5" s="14" t="n"/>
       <c r="J5" s="14" t="n"/>
       <c r="K5" s="14" t="n"/>
+      <c r="L5" s="14" t="n"/>
+      <c r="M5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n"/>
@@ -12919,6 +14050,8 @@
       <c r="I6" s="14" t="n"/>
       <c r="J6" s="14" t="n"/>
       <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n"/>
@@ -12932,6 +14065,8 @@
       <c r="I7" s="14" t="n"/>
       <c r="J7" s="14" t="n"/>
       <c r="K7" s="14" t="n"/>
+      <c r="L7" s="14" t="n"/>
+      <c r="M7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
@@ -12945,6 +14080,8 @@
       <c r="I8" s="14" t="n"/>
       <c r="J8" s="14" t="n"/>
       <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n"/>
@@ -12958,6 +14095,8 @@
       <c r="I9" s="14" t="n"/>
       <c r="J9" s="14" t="n"/>
       <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n"/>
@@ -12971,6 +14110,8 @@
       <c r="I10" s="14" t="n"/>
       <c r="J10" s="14" t="n"/>
       <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n"/>
@@ -12984,6 +14125,8 @@
       <c r="I11" s="14" t="n"/>
       <c r="J11" s="14" t="n"/>
       <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n"/>
@@ -12997,6 +14140,8 @@
       <c r="I12" s="14" t="n"/>
       <c r="J12" s="14" t="n"/>
       <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n"/>
@@ -13010,6 +14155,8 @@
       <c r="I13" s="14" t="n"/>
       <c r="J13" s="14" t="n"/>
       <c r="K13" s="14" t="n"/>
+      <c r="L13" s="14" t="n"/>
+      <c r="M13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n"/>
@@ -13023,6 +14170,8 @@
       <c r="I14" s="14" t="n"/>
       <c r="J14" s="14" t="n"/>
       <c r="K14" s="14" t="n"/>
+      <c r="L14" s="14" t="n"/>
+      <c r="M14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n"/>
@@ -13036,6 +14185,8 @@
       <c r="I15" s="14" t="n"/>
       <c r="J15" s="14" t="n"/>
       <c r="K15" s="14" t="n"/>
+      <c r="L15" s="14" t="n"/>
+      <c r="M15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n"/>
@@ -13049,6 +14200,8 @@
       <c r="I16" s="14" t="n"/>
       <c r="J16" s="14" t="n"/>
       <c r="K16" s="14" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n"/>
@@ -13062,6 +14215,8 @@
       <c r="I17" s="14" t="n"/>
       <c r="J17" s="14" t="n"/>
       <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n"/>
@@ -13075,6 +14230,8 @@
       <c r="I18" s="14" t="n"/>
       <c r="J18" s="14" t="n"/>
       <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n"/>
@@ -13088,6 +14245,8 @@
       <c r="I19" s="14" t="n"/>
       <c r="J19" s="14" t="n"/>
       <c r="K19" s="14" t="n"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n"/>
@@ -13101,6 +14260,8 @@
       <c r="I20" s="14" t="n"/>
       <c r="J20" s="14" t="n"/>
       <c r="K20" s="14" t="n"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
@@ -13114,6 +14275,8 @@
       <c r="I21" s="14" t="n"/>
       <c r="J21" s="14" t="n"/>
       <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n"/>
@@ -13127,6 +14290,8 @@
       <c r="I22" s="14" t="n"/>
       <c r="J22" s="14" t="n"/>
       <c r="K22" s="14" t="n"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n"/>
@@ -13140,6 +14305,8 @@
       <c r="I23" s="14" t="n"/>
       <c r="J23" s="14" t="n"/>
       <c r="K23" s="14" t="n"/>
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n"/>
@@ -13153,6 +14320,8 @@
       <c r="I24" s="14" t="n"/>
       <c r="J24" s="14" t="n"/>
       <c r="K24" s="14" t="n"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n"/>
@@ -13166,6 +14335,8 @@
       <c r="I25" s="14" t="n"/>
       <c r="J25" s="14" t="n"/>
       <c r="K25" s="14" t="n"/>
+      <c r="L25" s="14" t="n"/>
+      <c r="M25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n"/>
@@ -13179,6 +14350,8 @@
       <c r="I26" s="14" t="n"/>
       <c r="J26" s="14" t="n"/>
       <c r="K26" s="14" t="n"/>
+      <c r="L26" s="14" t="n"/>
+      <c r="M26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n"/>
@@ -13192,6 +14365,8 @@
       <c r="I27" s="14" t="n"/>
       <c r="J27" s="14" t="n"/>
       <c r="K27" s="14" t="n"/>
+      <c r="L27" s="14" t="n"/>
+      <c r="M27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n"/>
@@ -13205,6 +14380,8 @@
       <c r="I28" s="14" t="n"/>
       <c r="J28" s="14" t="n"/>
       <c r="K28" s="14" t="n"/>
+      <c r="L28" s="14" t="n"/>
+      <c r="M28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n"/>
@@ -13218,6 +14395,8 @@
       <c r="I29" s="14" t="n"/>
       <c r="J29" s="14" t="n"/>
       <c r="K29" s="14" t="n"/>
+      <c r="L29" s="14" t="n"/>
+      <c r="M29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n"/>
@@ -13231,6 +14410,8 @@
       <c r="I30" s="14" t="n"/>
       <c r="J30" s="14" t="n"/>
       <c r="K30" s="14" t="n"/>
+      <c r="L30" s="14" t="n"/>
+      <c r="M30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n"/>
@@ -13244,6 +14425,8 @@
       <c r="I31" s="14" t="n"/>
       <c r="J31" s="14" t="n"/>
       <c r="K31" s="14" t="n"/>
+      <c r="L31" s="14" t="n"/>
+      <c r="M31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n"/>
@@ -13257,6 +14440,8 @@
       <c r="I32" s="14" t="n"/>
       <c r="J32" s="14" t="n"/>
       <c r="K32" s="14" t="n"/>
+      <c r="L32" s="14" t="n"/>
+      <c r="M32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n"/>
@@ -13270,6 +14455,8 @@
       <c r="I33" s="14" t="n"/>
       <c r="J33" s="14" t="n"/>
       <c r="K33" s="14" t="n"/>
+      <c r="L33" s="14" t="n"/>
+      <c r="M33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n"/>
@@ -13283,6 +14470,8 @@
       <c r="I34" s="14" t="n"/>
       <c r="J34" s="14" t="n"/>
       <c r="K34" s="14" t="n"/>
+      <c r="L34" s="14" t="n"/>
+      <c r="M34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n"/>
@@ -13296,6 +14485,8 @@
       <c r="I35" s="14" t="n"/>
       <c r="J35" s="14" t="n"/>
       <c r="K35" s="14" t="n"/>
+      <c r="L35" s="14" t="n"/>
+      <c r="M35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n"/>
@@ -13309,6 +14500,8 @@
       <c r="I36" s="14" t="n"/>
       <c r="J36" s="14" t="n"/>
       <c r="K36" s="14" t="n"/>
+      <c r="L36" s="14" t="n"/>
+      <c r="M36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n"/>
@@ -13322,6 +14515,8 @@
       <c r="I37" s="14" t="n"/>
       <c r="J37" s="14" t="n"/>
       <c r="K37" s="14" t="n"/>
+      <c r="L37" s="14" t="n"/>
+      <c r="M37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n"/>
@@ -13335,6 +14530,8 @@
       <c r="I38" s="14" t="n"/>
       <c r="J38" s="14" t="n"/>
       <c r="K38" s="14" t="n"/>
+      <c r="L38" s="14" t="n"/>
+      <c r="M38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n"/>
@@ -13348,6 +14545,8 @@
       <c r="I39" s="14" t="n"/>
       <c r="J39" s="14" t="n"/>
       <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n"/>
@@ -13361,6 +14560,8 @@
       <c r="I40" s="14" t="n"/>
       <c r="J40" s="14" t="n"/>
       <c r="K40" s="14" t="n"/>
+      <c r="L40" s="14" t="n"/>
+      <c r="M40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n"/>
@@ -13374,6 +14575,8 @@
       <c r="I41" s="14" t="n"/>
       <c r="J41" s="14" t="n"/>
       <c r="K41" s="14" t="n"/>
+      <c r="L41" s="14" t="n"/>
+      <c r="M41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n"/>
@@ -13387,6 +14590,8 @@
       <c r="I42" s="14" t="n"/>
       <c r="J42" s="14" t="n"/>
       <c r="K42" s="14" t="n"/>
+      <c r="L42" s="14" t="n"/>
+      <c r="M42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n"/>
@@ -13400,6 +14605,8 @@
       <c r="I43" s="14" t="n"/>
       <c r="J43" s="14" t="n"/>
       <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n"/>
@@ -13413,6 +14620,8 @@
       <c r="I44" s="14" t="n"/>
       <c r="J44" s="14" t="n"/>
       <c r="K44" s="14" t="n"/>
+      <c r="L44" s="14" t="n"/>
+      <c r="M44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n"/>
@@ -13426,6 +14635,8 @@
       <c r="I45" s="14" t="n"/>
       <c r="J45" s="14" t="n"/>
       <c r="K45" s="14" t="n"/>
+      <c r="L45" s="14" t="n"/>
+      <c r="M45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n"/>
@@ -13439,6 +14650,8 @@
       <c r="I46" s="14" t="n"/>
       <c r="J46" s="14" t="n"/>
       <c r="K46" s="14" t="n"/>
+      <c r="L46" s="14" t="n"/>
+      <c r="M46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n"/>
@@ -13452,6 +14665,8 @@
       <c r="I47" s="14" t="n"/>
       <c r="J47" s="14" t="n"/>
       <c r="K47" s="14" t="n"/>
+      <c r="L47" s="14" t="n"/>
+      <c r="M47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n"/>
@@ -13465,6 +14680,8 @@
       <c r="I48" s="14" t="n"/>
       <c r="J48" s="14" t="n"/>
       <c r="K48" s="14" t="n"/>
+      <c r="L48" s="14" t="n"/>
+      <c r="M48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n"/>
@@ -13478,6 +14695,8 @@
       <c r="I49" s="14" t="n"/>
       <c r="J49" s="14" t="n"/>
       <c r="K49" s="14" t="n"/>
+      <c r="L49" s="14" t="n"/>
+      <c r="M49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n"/>
@@ -13491,6 +14710,8 @@
       <c r="I50" s="14" t="n"/>
       <c r="J50" s="14" t="n"/>
       <c r="K50" s="14" t="n"/>
+      <c r="L50" s="14" t="n"/>
+      <c r="M50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n"/>
@@ -13504,6 +14725,8 @@
       <c r="I51" s="14" t="n"/>
       <c r="J51" s="14" t="n"/>
       <c r="K51" s="14" t="n"/>
+      <c r="L51" s="14" t="n"/>
+      <c r="M51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n"/>
@@ -13517,6 +14740,8 @@
       <c r="I52" s="14" t="n"/>
       <c r="J52" s="14" t="n"/>
       <c r="K52" s="14" t="n"/>
+      <c r="L52" s="14" t="n"/>
+      <c r="M52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n"/>
@@ -13530,6 +14755,8 @@
       <c r="I53" s="14" t="n"/>
       <c r="J53" s="14" t="n"/>
       <c r="K53" s="14" t="n"/>
+      <c r="L53" s="14" t="n"/>
+      <c r="M53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n"/>
@@ -13543,6 +14770,8 @@
       <c r="I54" s="14" t="n"/>
       <c r="J54" s="14" t="n"/>
       <c r="K54" s="14" t="n"/>
+      <c r="L54" s="14" t="n"/>
+      <c r="M54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n"/>
@@ -13556,6 +14785,8 @@
       <c r="I55" s="14" t="n"/>
       <c r="J55" s="14" t="n"/>
       <c r="K55" s="14" t="n"/>
+      <c r="L55" s="14" t="n"/>
+      <c r="M55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n"/>
@@ -13569,6 +14800,8 @@
       <c r="I56" s="14" t="n"/>
       <c r="J56" s="14" t="n"/>
       <c r="K56" s="14" t="n"/>
+      <c r="L56" s="14" t="n"/>
+      <c r="M56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n"/>
@@ -13582,6 +14815,8 @@
       <c r="I57" s="14" t="n"/>
       <c r="J57" s="14" t="n"/>
       <c r="K57" s="14" t="n"/>
+      <c r="L57" s="14" t="n"/>
+      <c r="M57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n"/>
@@ -13595,6 +14830,8 @@
       <c r="I58" s="14" t="n"/>
       <c r="J58" s="14" t="n"/>
       <c r="K58" s="14" t="n"/>
+      <c r="L58" s="14" t="n"/>
+      <c r="M58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n"/>
@@ -13608,6 +14845,8 @@
       <c r="I59" s="14" t="n"/>
       <c r="J59" s="14" t="n"/>
       <c r="K59" s="14" t="n"/>
+      <c r="L59" s="14" t="n"/>
+      <c r="M59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n"/>
@@ -13621,6 +14860,8 @@
       <c r="I60" s="14" t="n"/>
       <c r="J60" s="14" t="n"/>
       <c r="K60" s="14" t="n"/>
+      <c r="L60" s="14" t="n"/>
+      <c r="M60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n"/>
@@ -13634,6 +14875,8 @@
       <c r="I61" s="14" t="n"/>
       <c r="J61" s="14" t="n"/>
       <c r="K61" s="14" t="n"/>
+      <c r="L61" s="14" t="n"/>
+      <c r="M61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n"/>
@@ -13647,6 +14890,8 @@
       <c r="I62" s="14" t="n"/>
       <c r="J62" s="14" t="n"/>
       <c r="K62" s="14" t="n"/>
+      <c r="L62" s="14" t="n"/>
+      <c r="M62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n"/>
@@ -13660,6 +14905,8 @@
       <c r="I63" s="14" t="n"/>
       <c r="J63" s="14" t="n"/>
       <c r="K63" s="14" t="n"/>
+      <c r="L63" s="14" t="n"/>
+      <c r="M63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n"/>
@@ -13673,6 +14920,8 @@
       <c r="I64" s="14" t="n"/>
       <c r="J64" s="14" t="n"/>
       <c r="K64" s="14" t="n"/>
+      <c r="L64" s="14" t="n"/>
+      <c r="M64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n"/>
@@ -13686,6 +14935,8 @@
       <c r="I65" s="14" t="n"/>
       <c r="J65" s="14" t="n"/>
       <c r="K65" s="14" t="n"/>
+      <c r="L65" s="14" t="n"/>
+      <c r="M65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n"/>
@@ -13699,6 +14950,8 @@
       <c r="I66" s="14" t="n"/>
       <c r="J66" s="14" t="n"/>
       <c r="K66" s="14" t="n"/>
+      <c r="L66" s="14" t="n"/>
+      <c r="M66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n"/>
@@ -13712,6 +14965,8 @@
       <c r="I67" s="14" t="n"/>
       <c r="J67" s="14" t="n"/>
       <c r="K67" s="14" t="n"/>
+      <c r="L67" s="14" t="n"/>
+      <c r="M67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n"/>
@@ -13725,6 +14980,8 @@
       <c r="I68" s="14" t="n"/>
       <c r="J68" s="14" t="n"/>
       <c r="K68" s="14" t="n"/>
+      <c r="L68" s="14" t="n"/>
+      <c r="M68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n"/>
@@ -13738,6 +14995,8 @@
       <c r="I69" s="14" t="n"/>
       <c r="J69" s="14" t="n"/>
       <c r="K69" s="14" t="n"/>
+      <c r="L69" s="14" t="n"/>
+      <c r="M69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n"/>
@@ -13751,6 +15010,8 @@
       <c r="I70" s="14" t="n"/>
       <c r="J70" s="14" t="n"/>
       <c r="K70" s="14" t="n"/>
+      <c r="L70" s="14" t="n"/>
+      <c r="M70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n"/>
@@ -13764,6 +15025,8 @@
       <c r="I71" s="14" t="n"/>
       <c r="J71" s="14" t="n"/>
       <c r="K71" s="14" t="n"/>
+      <c r="L71" s="14" t="n"/>
+      <c r="M71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n"/>
@@ -13777,6 +15040,8 @@
       <c r="I72" s="14" t="n"/>
       <c r="J72" s="14" t="n"/>
       <c r="K72" s="14" t="n"/>
+      <c r="L72" s="14" t="n"/>
+      <c r="M72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n"/>
@@ -13790,6 +15055,8 @@
       <c r="I73" s="14" t="n"/>
       <c r="J73" s="14" t="n"/>
       <c r="K73" s="14" t="n"/>
+      <c r="L73" s="14" t="n"/>
+      <c r="M73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n"/>
@@ -13803,6 +15070,8 @@
       <c r="I74" s="14" t="n"/>
       <c r="J74" s="14" t="n"/>
       <c r="K74" s="14" t="n"/>
+      <c r="L74" s="14" t="n"/>
+      <c r="M74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n"/>
@@ -13816,6 +15085,8 @@
       <c r="I75" s="14" t="n"/>
       <c r="J75" s="14" t="n"/>
       <c r="K75" s="14" t="n"/>
+      <c r="L75" s="14" t="n"/>
+      <c r="M75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n"/>
@@ -13829,6 +15100,8 @@
       <c r="I76" s="14" t="n"/>
       <c r="J76" s="14" t="n"/>
       <c r="K76" s="14" t="n"/>
+      <c r="L76" s="14" t="n"/>
+      <c r="M76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n"/>
@@ -13842,6 +15115,8 @@
       <c r="I77" s="14" t="n"/>
       <c r="J77" s="14" t="n"/>
       <c r="K77" s="14" t="n"/>
+      <c r="L77" s="14" t="n"/>
+      <c r="M77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n"/>
@@ -13855,6 +15130,8 @@
       <c r="I78" s="14" t="n"/>
       <c r="J78" s="14" t="n"/>
       <c r="K78" s="14" t="n"/>
+      <c r="L78" s="14" t="n"/>
+      <c r="M78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n"/>
@@ -13868,6 +15145,8 @@
       <c r="I79" s="14" t="n"/>
       <c r="J79" s="14" t="n"/>
       <c r="K79" s="14" t="n"/>
+      <c r="L79" s="14" t="n"/>
+      <c r="M79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n"/>
@@ -13881,6 +15160,8 @@
       <c r="I80" s="14" t="n"/>
       <c r="J80" s="14" t="n"/>
       <c r="K80" s="14" t="n"/>
+      <c r="L80" s="14" t="n"/>
+      <c r="M80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n"/>
@@ -13894,6 +15175,8 @@
       <c r="I81" s="14" t="n"/>
       <c r="J81" s="14" t="n"/>
       <c r="K81" s="14" t="n"/>
+      <c r="L81" s="14" t="n"/>
+      <c r="M81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n"/>
@@ -13907,6 +15190,8 @@
       <c r="I82" s="14" t="n"/>
       <c r="J82" s="14" t="n"/>
       <c r="K82" s="14" t="n"/>
+      <c r="L82" s="14" t="n"/>
+      <c r="M82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n"/>
@@ -13920,6 +15205,8 @@
       <c r="I83" s="14" t="n"/>
       <c r="J83" s="14" t="n"/>
       <c r="K83" s="14" t="n"/>
+      <c r="L83" s="14" t="n"/>
+      <c r="M83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n"/>
@@ -13933,6 +15220,8 @@
       <c r="I84" s="14" t="n"/>
       <c r="J84" s="14" t="n"/>
       <c r="K84" s="14" t="n"/>
+      <c r="L84" s="14" t="n"/>
+      <c r="M84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n"/>
@@ -13946,6 +15235,8 @@
       <c r="I85" s="14" t="n"/>
       <c r="J85" s="14" t="n"/>
       <c r="K85" s="14" t="n"/>
+      <c r="L85" s="14" t="n"/>
+      <c r="M85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n"/>
@@ -13959,6 +15250,8 @@
       <c r="I86" s="14" t="n"/>
       <c r="J86" s="14" t="n"/>
       <c r="K86" s="14" t="n"/>
+      <c r="L86" s="14" t="n"/>
+      <c r="M86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n"/>
@@ -13972,6 +15265,8 @@
       <c r="I87" s="14" t="n"/>
       <c r="J87" s="14" t="n"/>
       <c r="K87" s="14" t="n"/>
+      <c r="L87" s="14" t="n"/>
+      <c r="M87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n"/>
@@ -13985,6 +15280,8 @@
       <c r="I88" s="14" t="n"/>
       <c r="J88" s="14" t="n"/>
       <c r="K88" s="14" t="n"/>
+      <c r="L88" s="14" t="n"/>
+      <c r="M88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n"/>
@@ -13998,6 +15295,8 @@
       <c r="I89" s="14" t="n"/>
       <c r="J89" s="14" t="n"/>
       <c r="K89" s="14" t="n"/>
+      <c r="L89" s="14" t="n"/>
+      <c r="M89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n"/>
@@ -14011,6 +15310,8 @@
       <c r="I90" s="14" t="n"/>
       <c r="J90" s="14" t="n"/>
       <c r="K90" s="14" t="n"/>
+      <c r="L90" s="14" t="n"/>
+      <c r="M90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n"/>
@@ -14024,6 +15325,8 @@
       <c r="I91" s="14" t="n"/>
       <c r="J91" s="14" t="n"/>
       <c r="K91" s="14" t="n"/>
+      <c r="L91" s="14" t="n"/>
+      <c r="M91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n"/>
@@ -14037,6 +15340,8 @@
       <c r="I92" s="14" t="n"/>
       <c r="J92" s="14" t="n"/>
       <c r="K92" s="14" t="n"/>
+      <c r="L92" s="14" t="n"/>
+      <c r="M92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n"/>
@@ -14050,6 +15355,8 @@
       <c r="I93" s="14" t="n"/>
       <c r="J93" s="14" t="n"/>
       <c r="K93" s="14" t="n"/>
+      <c r="L93" s="14" t="n"/>
+      <c r="M93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n"/>
@@ -14063,6 +15370,8 @@
       <c r="I94" s="14" t="n"/>
       <c r="J94" s="14" t="n"/>
       <c r="K94" s="14" t="n"/>
+      <c r="L94" s="14" t="n"/>
+      <c r="M94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n"/>
@@ -14076,6 +15385,8 @@
       <c r="I95" s="14" t="n"/>
       <c r="J95" s="14" t="n"/>
       <c r="K95" s="14" t="n"/>
+      <c r="L95" s="14" t="n"/>
+      <c r="M95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n"/>
@@ -14089,6 +15400,8 @@
       <c r="I96" s="14" t="n"/>
       <c r="J96" s="14" t="n"/>
       <c r="K96" s="14" t="n"/>
+      <c r="L96" s="14" t="n"/>
+      <c r="M96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n"/>
@@ -14102,6 +15415,8 @@
       <c r="I97" s="14" t="n"/>
       <c r="J97" s="14" t="n"/>
       <c r="K97" s="14" t="n"/>
+      <c r="L97" s="14" t="n"/>
+      <c r="M97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n"/>
@@ -14115,6 +15430,8 @@
       <c r="I98" s="14" t="n"/>
       <c r="J98" s="14" t="n"/>
       <c r="K98" s="14" t="n"/>
+      <c r="L98" s="14" t="n"/>
+      <c r="M98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n"/>
@@ -14128,6 +15445,8 @@
       <c r="I99" s="14" t="n"/>
       <c r="J99" s="14" t="n"/>
       <c r="K99" s="14" t="n"/>
+      <c r="L99" s="14" t="n"/>
+      <c r="M99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n"/>
@@ -14141,6 +15460,8 @@
       <c r="I100" s="14" t="n"/>
       <c r="J100" s="14" t="n"/>
       <c r="K100" s="14" t="n"/>
+      <c r="L100" s="14" t="n"/>
+      <c r="M100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n"/>
@@ -14154,6 +15475,8 @@
       <c r="I101" s="14" t="n"/>
       <c r="J101" s="14" t="n"/>
       <c r="K101" s="14" t="n"/>
+      <c r="L101" s="14" t="n"/>
+      <c r="M101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n"/>
@@ -14167,6 +15490,8 @@
       <c r="I102" s="14" t="n"/>
       <c r="J102" s="14" t="n"/>
       <c r="K102" s="14" t="n"/>
+      <c r="L102" s="14" t="n"/>
+      <c r="M102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n"/>
@@ -14180,6 +15505,8 @@
       <c r="I103" s="14" t="n"/>
       <c r="J103" s="14" t="n"/>
       <c r="K103" s="14" t="n"/>
+      <c r="L103" s="14" t="n"/>
+      <c r="M103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n"/>
@@ -14193,6 +15520,8 @@
       <c r="I104" s="14" t="n"/>
       <c r="J104" s="14" t="n"/>
       <c r="K104" s="14" t="n"/>
+      <c r="L104" s="14" t="n"/>
+      <c r="M104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n"/>
@@ -14206,6 +15535,8 @@
       <c r="I105" s="14" t="n"/>
       <c r="J105" s="14" t="n"/>
       <c r="K105" s="14" t="n"/>
+      <c r="L105" s="14" t="n"/>
+      <c r="M105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n"/>
@@ -14219,6 +15550,8 @@
       <c r="I106" s="14" t="n"/>
       <c r="J106" s="14" t="n"/>
       <c r="K106" s="14" t="n"/>
+      <c r="L106" s="14" t="n"/>
+      <c r="M106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n"/>
@@ -14232,6 +15565,8 @@
       <c r="I107" s="14" t="n"/>
       <c r="J107" s="14" t="n"/>
       <c r="K107" s="14" t="n"/>
+      <c r="L107" s="14" t="n"/>
+      <c r="M107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n"/>
@@ -14245,6 +15580,8 @@
       <c r="I108" s="14" t="n"/>
       <c r="J108" s="14" t="n"/>
       <c r="K108" s="14" t="n"/>
+      <c r="L108" s="14" t="n"/>
+      <c r="M108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n"/>
@@ -14258,6 +15595,8 @@
       <c r="I109" s="14" t="n"/>
       <c r="J109" s="14" t="n"/>
       <c r="K109" s="14" t="n"/>
+      <c r="L109" s="14" t="n"/>
+      <c r="M109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n"/>
@@ -14271,6 +15610,8 @@
       <c r="I110" s="14" t="n"/>
       <c r="J110" s="14" t="n"/>
       <c r="K110" s="14" t="n"/>
+      <c r="L110" s="14" t="n"/>
+      <c r="M110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n"/>
@@ -14284,6 +15625,8 @@
       <c r="I111" s="14" t="n"/>
       <c r="J111" s="14" t="n"/>
       <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n"/>
+      <c r="M111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n"/>
@@ -14297,6 +15640,8 @@
       <c r="I112" s="14" t="n"/>
       <c r="J112" s="14" t="n"/>
       <c r="K112" s="14" t="n"/>
+      <c r="L112" s="14" t="n"/>
+      <c r="M112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n"/>
@@ -14310,6 +15655,8 @@
       <c r="I113" s="14" t="n"/>
       <c r="J113" s="14" t="n"/>
       <c r="K113" s="14" t="n"/>
+      <c r="L113" s="14" t="n"/>
+      <c r="M113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n"/>
@@ -14323,6 +15670,8 @@
       <c r="I114" s="14" t="n"/>
       <c r="J114" s="14" t="n"/>
       <c r="K114" s="14" t="n"/>
+      <c r="L114" s="14" t="n"/>
+      <c r="M114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n"/>
@@ -14336,6 +15685,8 @@
       <c r="I115" s="14" t="n"/>
       <c r="J115" s="14" t="n"/>
       <c r="K115" s="14" t="n"/>
+      <c r="L115" s="14" t="n"/>
+      <c r="M115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n"/>
@@ -14349,6 +15700,8 @@
       <c r="I116" s="14" t="n"/>
       <c r="J116" s="14" t="n"/>
       <c r="K116" s="14" t="n"/>
+      <c r="L116" s="14" t="n"/>
+      <c r="M116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n"/>
@@ -14362,6 +15715,8 @@
       <c r="I117" s="14" t="n"/>
       <c r="J117" s="14" t="n"/>
       <c r="K117" s="14" t="n"/>
+      <c r="L117" s="14" t="n"/>
+      <c r="M117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n"/>
@@ -14375,6 +15730,8 @@
       <c r="I118" s="14" t="n"/>
       <c r="J118" s="14" t="n"/>
       <c r="K118" s="14" t="n"/>
+      <c r="L118" s="14" t="n"/>
+      <c r="M118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n"/>
@@ -14388,6 +15745,8 @@
       <c r="I119" s="14" t="n"/>
       <c r="J119" s="14" t="n"/>
       <c r="K119" s="14" t="n"/>
+      <c r="L119" s="14" t="n"/>
+      <c r="M119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n"/>
@@ -14401,6 +15760,8 @@
       <c r="I120" s="14" t="n"/>
       <c r="J120" s="14" t="n"/>
       <c r="K120" s="14" t="n"/>
+      <c r="L120" s="14" t="n"/>
+      <c r="M120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n"/>
@@ -14414,6 +15775,8 @@
       <c r="I121" s="14" t="n"/>
       <c r="J121" s="14" t="n"/>
       <c r="K121" s="14" t="n"/>
+      <c r="L121" s="14" t="n"/>
+      <c r="M121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n"/>
@@ -14427,6 +15790,8 @@
       <c r="I122" s="14" t="n"/>
       <c r="J122" s="14" t="n"/>
       <c r="K122" s="14" t="n"/>
+      <c r="L122" s="14" t="n"/>
+      <c r="M122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n"/>
@@ -14440,6 +15805,8 @@
       <c r="I123" s="14" t="n"/>
       <c r="J123" s="14" t="n"/>
       <c r="K123" s="14" t="n"/>
+      <c r="L123" s="14" t="n"/>
+      <c r="M123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n"/>
@@ -14453,6 +15820,8 @@
       <c r="I124" s="14" t="n"/>
       <c r="J124" s="14" t="n"/>
       <c r="K124" s="14" t="n"/>
+      <c r="L124" s="14" t="n"/>
+      <c r="M124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n"/>
@@ -14466,6 +15835,8 @@
       <c r="I125" s="14" t="n"/>
       <c r="J125" s="14" t="n"/>
       <c r="K125" s="14" t="n"/>
+      <c r="L125" s="14" t="n"/>
+      <c r="M125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n"/>
@@ -14479,6 +15850,8 @@
       <c r="I126" s="14" t="n"/>
       <c r="J126" s="14" t="n"/>
       <c r="K126" s="14" t="n"/>
+      <c r="L126" s="14" t="n"/>
+      <c r="M126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n"/>
@@ -14492,6 +15865,8 @@
       <c r="I127" s="14" t="n"/>
       <c r="J127" s="14" t="n"/>
       <c r="K127" s="14" t="n"/>
+      <c r="L127" s="14" t="n"/>
+      <c r="M127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n"/>
@@ -14505,6 +15880,8 @@
       <c r="I128" s="14" t="n"/>
       <c r="J128" s="14" t="n"/>
       <c r="K128" s="14" t="n"/>
+      <c r="L128" s="14" t="n"/>
+      <c r="M128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n"/>
@@ -14518,6 +15895,8 @@
       <c r="I129" s="14" t="n"/>
       <c r="J129" s="14" t="n"/>
       <c r="K129" s="14" t="n"/>
+      <c r="L129" s="14" t="n"/>
+      <c r="M129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n"/>
@@ -14531,6 +15910,8 @@
       <c r="I130" s="14" t="n"/>
       <c r="J130" s="14" t="n"/>
       <c r="K130" s="14" t="n"/>
+      <c r="L130" s="14" t="n"/>
+      <c r="M130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n"/>
@@ -14544,6 +15925,8 @@
       <c r="I131" s="14" t="n"/>
       <c r="J131" s="14" t="n"/>
       <c r="K131" s="14" t="n"/>
+      <c r="L131" s="14" t="n"/>
+      <c r="M131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="14" t="n"/>
@@ -14557,6 +15940,8 @@
       <c r="I132" s="14" t="n"/>
       <c r="J132" s="14" t="n"/>
       <c r="K132" s="14" t="n"/>
+      <c r="L132" s="14" t="n"/>
+      <c r="M132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n"/>
@@ -14570,6 +15955,8 @@
       <c r="I133" s="14" t="n"/>
       <c r="J133" s="14" t="n"/>
       <c r="K133" s="14" t="n"/>
+      <c r="L133" s="14" t="n"/>
+      <c r="M133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="14" t="n"/>
@@ -14583,6 +15970,8 @@
       <c r="I134" s="14" t="n"/>
       <c r="J134" s="14" t="n"/>
       <c r="K134" s="14" t="n"/>
+      <c r="L134" s="14" t="n"/>
+      <c r="M134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n"/>
@@ -14596,6 +15985,8 @@
       <c r="I135" s="14" t="n"/>
       <c r="J135" s="14" t="n"/>
       <c r="K135" s="14" t="n"/>
+      <c r="L135" s="14" t="n"/>
+      <c r="M135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="14" t="n"/>
@@ -14609,6 +16000,8 @@
       <c r="I136" s="14" t="n"/>
       <c r="J136" s="14" t="n"/>
       <c r="K136" s="14" t="n"/>
+      <c r="L136" s="14" t="n"/>
+      <c r="M136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n"/>
@@ -14622,6 +16015,8 @@
       <c r="I137" s="14" t="n"/>
       <c r="J137" s="14" t="n"/>
       <c r="K137" s="14" t="n"/>
+      <c r="L137" s="14" t="n"/>
+      <c r="M137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="14" t="n"/>
@@ -14635,6 +16030,8 @@
       <c r="I138" s="14" t="n"/>
       <c r="J138" s="14" t="n"/>
       <c r="K138" s="14" t="n"/>
+      <c r="L138" s="14" t="n"/>
+      <c r="M138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n"/>
@@ -14648,6 +16045,8 @@
       <c r="I139" s="14" t="n"/>
       <c r="J139" s="14" t="n"/>
       <c r="K139" s="14" t="n"/>
+      <c r="L139" s="14" t="n"/>
+      <c r="M139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="14" t="n"/>
@@ -14661,6 +16060,8 @@
       <c r="I140" s="14" t="n"/>
       <c r="J140" s="14" t="n"/>
       <c r="K140" s="14" t="n"/>
+      <c r="L140" s="14" t="n"/>
+      <c r="M140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n"/>
@@ -14674,6 +16075,8 @@
       <c r="I141" s="14" t="n"/>
       <c r="J141" s="14" t="n"/>
       <c r="K141" s="14" t="n"/>
+      <c r="L141" s="14" t="n"/>
+      <c r="M141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="14" t="n"/>
@@ -14687,6 +16090,8 @@
       <c r="I142" s="14" t="n"/>
       <c r="J142" s="14" t="n"/>
       <c r="K142" s="14" t="n"/>
+      <c r="L142" s="14" t="n"/>
+      <c r="M142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n"/>
@@ -14700,6 +16105,8 @@
       <c r="I143" s="14" t="n"/>
       <c r="J143" s="14" t="n"/>
       <c r="K143" s="14" t="n"/>
+      <c r="L143" s="14" t="n"/>
+      <c r="M143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n"/>
@@ -14713,6 +16120,8 @@
       <c r="I144" s="14" t="n"/>
       <c r="J144" s="14" t="n"/>
       <c r="K144" s="14" t="n"/>
+      <c r="L144" s="14" t="n"/>
+      <c r="M144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n"/>
@@ -14726,6 +16135,8 @@
       <c r="I145" s="14" t="n"/>
       <c r="J145" s="14" t="n"/>
       <c r="K145" s="14" t="n"/>
+      <c r="L145" s="14" t="n"/>
+      <c r="M145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="14" t="n"/>
@@ -14739,6 +16150,8 @@
       <c r="I146" s="14" t="n"/>
       <c r="J146" s="14" t="n"/>
       <c r="K146" s="14" t="n"/>
+      <c r="L146" s="14" t="n"/>
+      <c r="M146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n"/>
@@ -14752,6 +16165,8 @@
       <c r="I147" s="14" t="n"/>
       <c r="J147" s="14" t="n"/>
       <c r="K147" s="14" t="n"/>
+      <c r="L147" s="14" t="n"/>
+      <c r="M147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="14" t="n"/>
@@ -14765,6 +16180,8 @@
       <c r="I148" s="14" t="n"/>
       <c r="J148" s="14" t="n"/>
       <c r="K148" s="14" t="n"/>
+      <c r="L148" s="14" t="n"/>
+      <c r="M148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n"/>
@@ -14778,6 +16195,8 @@
       <c r="I149" s="14" t="n"/>
       <c r="J149" s="14" t="n"/>
       <c r="K149" s="14" t="n"/>
+      <c r="L149" s="14" t="n"/>
+      <c r="M149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="14" t="n"/>
@@ -14791,6 +16210,8 @@
       <c r="I150" s="14" t="n"/>
       <c r="J150" s="14" t="n"/>
       <c r="K150" s="14" t="n"/>
+      <c r="L150" s="14" t="n"/>
+      <c r="M150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n"/>
@@ -14804,6 +16225,8 @@
       <c r="I151" s="14" t="n"/>
       <c r="J151" s="14" t="n"/>
       <c r="K151" s="14" t="n"/>
+      <c r="L151" s="14" t="n"/>
+      <c r="M151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="14" t="n"/>
@@ -14817,6 +16240,8 @@
       <c r="I152" s="14" t="n"/>
       <c r="J152" s="14" t="n"/>
       <c r="K152" s="14" t="n"/>
+      <c r="L152" s="14" t="n"/>
+      <c r="M152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n"/>
@@ -14830,6 +16255,8 @@
       <c r="I153" s="14" t="n"/>
       <c r="J153" s="14" t="n"/>
       <c r="K153" s="14" t="n"/>
+      <c r="L153" s="14" t="n"/>
+      <c r="M153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="14" t="n"/>
@@ -14843,6 +16270,8 @@
       <c r="I154" s="14" t="n"/>
       <c r="J154" s="14" t="n"/>
       <c r="K154" s="14" t="n"/>
+      <c r="L154" s="14" t="n"/>
+      <c r="M154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n"/>
@@ -14856,6 +16285,8 @@
       <c r="I155" s="14" t="n"/>
       <c r="J155" s="14" t="n"/>
       <c r="K155" s="14" t="n"/>
+      <c r="L155" s="14" t="n"/>
+      <c r="M155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n"/>
@@ -14869,6 +16300,8 @@
       <c r="I156" s="14" t="n"/>
       <c r="J156" s="14" t="n"/>
       <c r="K156" s="14" t="n"/>
+      <c r="L156" s="14" t="n"/>
+      <c r="M156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n"/>
@@ -14882,6 +16315,8 @@
       <c r="I157" s="14" t="n"/>
       <c r="J157" s="14" t="n"/>
       <c r="K157" s="14" t="n"/>
+      <c r="L157" s="14" t="n"/>
+      <c r="M157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="14" t="n"/>
@@ -14895,6 +16330,8 @@
       <c r="I158" s="14" t="n"/>
       <c r="J158" s="14" t="n"/>
       <c r="K158" s="14" t="n"/>
+      <c r="L158" s="14" t="n"/>
+      <c r="M158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n"/>
@@ -14908,6 +16345,8 @@
       <c r="I159" s="14" t="n"/>
       <c r="J159" s="14" t="n"/>
       <c r="K159" s="14" t="n"/>
+      <c r="L159" s="14" t="n"/>
+      <c r="M159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="14" t="n"/>
@@ -14921,6 +16360,8 @@
       <c r="I160" s="14" t="n"/>
       <c r="J160" s="14" t="n"/>
       <c r="K160" s="14" t="n"/>
+      <c r="L160" s="14" t="n"/>
+      <c r="M160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n"/>
@@ -14934,6 +16375,8 @@
       <c r="I161" s="14" t="n"/>
       <c r="J161" s="14" t="n"/>
       <c r="K161" s="14" t="n"/>
+      <c r="L161" s="14" t="n"/>
+      <c r="M161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="14" t="n"/>
@@ -14947,6 +16390,8 @@
       <c r="I162" s="14" t="n"/>
       <c r="J162" s="14" t="n"/>
       <c r="K162" s="14" t="n"/>
+      <c r="L162" s="14" t="n"/>
+      <c r="M162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n"/>
@@ -14960,6 +16405,8 @@
       <c r="I163" s="14" t="n"/>
       <c r="J163" s="14" t="n"/>
       <c r="K163" s="14" t="n"/>
+      <c r="L163" s="14" t="n"/>
+      <c r="M163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n"/>
@@ -14973,6 +16420,8 @@
       <c r="I164" s="14" t="n"/>
       <c r="J164" s="14" t="n"/>
       <c r="K164" s="14" t="n"/>
+      <c r="L164" s="14" t="n"/>
+      <c r="M164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n"/>
@@ -14986,6 +16435,8 @@
       <c r="I165" s="14" t="n"/>
       <c r="J165" s="14" t="n"/>
       <c r="K165" s="14" t="n"/>
+      <c r="L165" s="14" t="n"/>
+      <c r="M165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n"/>
@@ -14999,6 +16450,8 @@
       <c r="I166" s="14" t="n"/>
       <c r="J166" s="14" t="n"/>
       <c r="K166" s="14" t="n"/>
+      <c r="L166" s="14" t="n"/>
+      <c r="M166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n"/>
@@ -15012,6 +16465,8 @@
       <c r="I167" s="14" t="n"/>
       <c r="J167" s="14" t="n"/>
       <c r="K167" s="14" t="n"/>
+      <c r="L167" s="14" t="n"/>
+      <c r="M167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="14" t="n"/>
@@ -15025,6 +16480,8 @@
       <c r="I168" s="14" t="n"/>
       <c r="J168" s="14" t="n"/>
       <c r="K168" s="14" t="n"/>
+      <c r="L168" s="14" t="n"/>
+      <c r="M168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n"/>
@@ -15038,6 +16495,8 @@
       <c r="I169" s="14" t="n"/>
       <c r="J169" s="14" t="n"/>
       <c r="K169" s="14" t="n"/>
+      <c r="L169" s="14" t="n"/>
+      <c r="M169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="14" t="n"/>
@@ -15051,6 +16510,8 @@
       <c r="I170" s="14" t="n"/>
       <c r="J170" s="14" t="n"/>
       <c r="K170" s="14" t="n"/>
+      <c r="L170" s="14" t="n"/>
+      <c r="M170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n"/>
@@ -15064,6 +16525,8 @@
       <c r="I171" s="14" t="n"/>
       <c r="J171" s="14" t="n"/>
       <c r="K171" s="14" t="n"/>
+      <c r="L171" s="14" t="n"/>
+      <c r="M171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n"/>
@@ -15077,6 +16540,8 @@
       <c r="I172" s="14" t="n"/>
       <c r="J172" s="14" t="n"/>
       <c r="K172" s="14" t="n"/>
+      <c r="L172" s="14" t="n"/>
+      <c r="M172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n"/>
@@ -15090,6 +16555,8 @@
       <c r="I173" s="14" t="n"/>
       <c r="J173" s="14" t="n"/>
       <c r="K173" s="14" t="n"/>
+      <c r="L173" s="14" t="n"/>
+      <c r="M173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n"/>
@@ -15103,6 +16570,8 @@
       <c r="I174" s="14" t="n"/>
       <c r="J174" s="14" t="n"/>
       <c r="K174" s="14" t="n"/>
+      <c r="L174" s="14" t="n"/>
+      <c r="M174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n"/>
@@ -15116,6 +16585,8 @@
       <c r="I175" s="14" t="n"/>
       <c r="J175" s="14" t="n"/>
       <c r="K175" s="14" t="n"/>
+      <c r="L175" s="14" t="n"/>
+      <c r="M175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n"/>
@@ -15129,6 +16600,8 @@
       <c r="I176" s="14" t="n"/>
       <c r="J176" s="14" t="n"/>
       <c r="K176" s="14" t="n"/>
+      <c r="L176" s="14" t="n"/>
+      <c r="M176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n"/>
@@ -15142,6 +16615,8 @@
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="14" t="n"/>
       <c r="K177" s="14" t="n"/>
+      <c r="L177" s="14" t="n"/>
+      <c r="M177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n"/>
@@ -15155,6 +16630,8 @@
       <c r="I178" s="14" t="n"/>
       <c r="J178" s="14" t="n"/>
       <c r="K178" s="14" t="n"/>
+      <c r="L178" s="14" t="n"/>
+      <c r="M178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n"/>
@@ -15168,6 +16645,8 @@
       <c r="I179" s="14" t="n"/>
       <c r="J179" s="14" t="n"/>
       <c r="K179" s="14" t="n"/>
+      <c r="L179" s="14" t="n"/>
+      <c r="M179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n"/>
@@ -15181,6 +16660,8 @@
       <c r="I180" s="14" t="n"/>
       <c r="J180" s="14" t="n"/>
       <c r="K180" s="14" t="n"/>
+      <c r="L180" s="14" t="n"/>
+      <c r="M180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n"/>
@@ -15194,6 +16675,8 @@
       <c r="I181" s="14" t="n"/>
       <c r="J181" s="14" t="n"/>
       <c r="K181" s="14" t="n"/>
+      <c r="L181" s="14" t="n"/>
+      <c r="M181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n"/>
@@ -15207,6 +16690,8 @@
       <c r="I182" s="14" t="n"/>
       <c r="J182" s="14" t="n"/>
       <c r="K182" s="14" t="n"/>
+      <c r="L182" s="14" t="n"/>
+      <c r="M182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n"/>
@@ -15220,6 +16705,8 @@
       <c r="I183" s="14" t="n"/>
       <c r="J183" s="14" t="n"/>
       <c r="K183" s="14" t="n"/>
+      <c r="L183" s="14" t="n"/>
+      <c r="M183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n"/>
@@ -15233,6 +16720,8 @@
       <c r="I184" s="14" t="n"/>
       <c r="J184" s="14" t="n"/>
       <c r="K184" s="14" t="n"/>
+      <c r="L184" s="14" t="n"/>
+      <c r="M184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n"/>
@@ -15246,6 +16735,8 @@
       <c r="I185" s="14" t="n"/>
       <c r="J185" s="14" t="n"/>
       <c r="K185" s="14" t="n"/>
+      <c r="L185" s="14" t="n"/>
+      <c r="M185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n"/>
@@ -15259,6 +16750,8 @@
       <c r="I186" s="14" t="n"/>
       <c r="J186" s="14" t="n"/>
       <c r="K186" s="14" t="n"/>
+      <c r="L186" s="14" t="n"/>
+      <c r="M186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n"/>
@@ -15272,6 +16765,8 @@
       <c r="I187" s="14" t="n"/>
       <c r="J187" s="14" t="n"/>
       <c r="K187" s="14" t="n"/>
+      <c r="L187" s="14" t="n"/>
+      <c r="M187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n"/>
@@ -15285,6 +16780,8 @@
       <c r="I188" s="14" t="n"/>
       <c r="J188" s="14" t="n"/>
       <c r="K188" s="14" t="n"/>
+      <c r="L188" s="14" t="n"/>
+      <c r="M188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n"/>
@@ -15298,6 +16795,8 @@
       <c r="I189" s="14" t="n"/>
       <c r="J189" s="14" t="n"/>
       <c r="K189" s="14" t="n"/>
+      <c r="L189" s="14" t="n"/>
+      <c r="M189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n"/>
@@ -15311,6 +16810,8 @@
       <c r="I190" s="14" t="n"/>
       <c r="J190" s="14" t="n"/>
       <c r="K190" s="14" t="n"/>
+      <c r="L190" s="14" t="n"/>
+      <c r="M190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n"/>
@@ -15324,6 +16825,8 @@
       <c r="I191" s="14" t="n"/>
       <c r="J191" s="14" t="n"/>
       <c r="K191" s="14" t="n"/>
+      <c r="L191" s="14" t="n"/>
+      <c r="M191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n"/>
@@ -15337,6 +16840,8 @@
       <c r="I192" s="14" t="n"/>
       <c r="J192" s="14" t="n"/>
       <c r="K192" s="14" t="n"/>
+      <c r="L192" s="14" t="n"/>
+      <c r="M192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n"/>
@@ -15350,6 +16855,8 @@
       <c r="I193" s="14" t="n"/>
       <c r="J193" s="14" t="n"/>
       <c r="K193" s="14" t="n"/>
+      <c r="L193" s="14" t="n"/>
+      <c r="M193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n"/>
@@ -15363,6 +16870,8 @@
       <c r="I194" s="14" t="n"/>
       <c r="J194" s="14" t="n"/>
       <c r="K194" s="14" t="n"/>
+      <c r="L194" s="14" t="n"/>
+      <c r="M194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n"/>
@@ -15376,6 +16885,8 @@
       <c r="I195" s="14" t="n"/>
       <c r="J195" s="14" t="n"/>
       <c r="K195" s="14" t="n"/>
+      <c r="L195" s="14" t="n"/>
+      <c r="M195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n"/>
@@ -15389,6 +16900,8 @@
       <c r="I196" s="14" t="n"/>
       <c r="J196" s="14" t="n"/>
       <c r="K196" s="14" t="n"/>
+      <c r="L196" s="14" t="n"/>
+      <c r="M196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n"/>
@@ -15402,6 +16915,8 @@
       <c r="I197" s="14" t="n"/>
       <c r="J197" s="14" t="n"/>
       <c r="K197" s="14" t="n"/>
+      <c r="L197" s="14" t="n"/>
+      <c r="M197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n"/>
@@ -15415,6 +16930,8 @@
       <c r="I198" s="14" t="n"/>
       <c r="J198" s="14" t="n"/>
       <c r="K198" s="14" t="n"/>
+      <c r="L198" s="14" t="n"/>
+      <c r="M198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n"/>
@@ -15428,6 +16945,8 @@
       <c r="I199" s="14" t="n"/>
       <c r="J199" s="14" t="n"/>
       <c r="K199" s="14" t="n"/>
+      <c r="L199" s="14" t="n"/>
+      <c r="M199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n"/>
@@ -15441,6 +16960,8 @@
       <c r="I200" s="14" t="n"/>
       <c r="J200" s="14" t="n"/>
       <c r="K200" s="14" t="n"/>
+      <c r="L200" s="14" t="n"/>
+      <c r="M200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n"/>
@@ -15454,6 +16975,8 @@
       <c r="I201" s="14" t="n"/>
       <c r="J201" s="14" t="n"/>
       <c r="K201" s="14" t="n"/>
+      <c r="L201" s="14" t="n"/>
+      <c r="M201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n"/>
@@ -15467,6 +16990,8 @@
       <c r="I202" s="14" t="n"/>
       <c r="J202" s="14" t="n"/>
       <c r="K202" s="14" t="n"/>
+      <c r="L202" s="14" t="n"/>
+      <c r="M202" s="14" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15480,7 +17005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16353,9 +17878,50 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>inbound</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Balkans road</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>250</v>
+      </c>
+      <c r="G22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="16" t="inlineStr">
+        <is>
+          <t>Albania / Serbia groupage truck to Helmond. Replace with the forwarder's quote</t>
+        </is>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I2:I81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"placeholder,real"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16369,7 +17935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P202"/>
+  <dimension ref="A1:R202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16387,6 +17953,8 @@
     <col width="32" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16461,6 +18029,16 @@
         </is>
       </c>
       <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -16513,12 +18091,14 @@
       <c r="L2" s="12" t="n"/>
       <c r="M2" s="12" t="n"/>
       <c r="N2" s="12" t="n"/>
-      <c r="O2" s="12" t="inlineStr">
+      <c r="O2" s="12" t="n"/>
+      <c r="P2" s="12" t="n"/>
+      <c r="Q2" s="12" t="inlineStr">
         <is>
           <t>Origin of every flow in this tool</t>
         </is>
       </c>
-      <c r="P2" s="13" t="inlineStr">
+      <c r="R2" s="13" t="inlineStr">
         <is>
           <t>EXAMPLE ROW: delete before upload</t>
         </is>
@@ -16540,6 +18120,8 @@
       <c r="M3" s="14" t="n"/>
       <c r="N3" s="14" t="n"/>
       <c r="O3" s="14" t="n"/>
+      <c r="P3" s="14" t="n"/>
+      <c r="Q3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n"/>
@@ -16557,6 +18139,8 @@
       <c r="M4" s="14" t="n"/>
       <c r="N4" s="14" t="n"/>
       <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n"/>
@@ -16574,6 +18158,8 @@
       <c r="M5" s="14" t="n"/>
       <c r="N5" s="14" t="n"/>
       <c r="O5" s="14" t="n"/>
+      <c r="P5" s="14" t="n"/>
+      <c r="Q5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n"/>
@@ -16591,6 +18177,8 @@
       <c r="M6" s="14" t="n"/>
       <c r="N6" s="14" t="n"/>
       <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n"/>
@@ -16608,6 +18196,8 @@
       <c r="M7" s="14" t="n"/>
       <c r="N7" s="14" t="n"/>
       <c r="O7" s="14" t="n"/>
+      <c r="P7" s="14" t="n"/>
+      <c r="Q7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
@@ -16625,6 +18215,8 @@
       <c r="M8" s="14" t="n"/>
       <c r="N8" s="14" t="n"/>
       <c r="O8" s="14" t="n"/>
+      <c r="P8" s="14" t="n"/>
+      <c r="Q8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n"/>
@@ -16642,6 +18234,8 @@
       <c r="M9" s="14" t="n"/>
       <c r="N9" s="14" t="n"/>
       <c r="O9" s="14" t="n"/>
+      <c r="P9" s="14" t="n"/>
+      <c r="Q9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n"/>
@@ -16659,6 +18253,8 @@
       <c r="M10" s="14" t="n"/>
       <c r="N10" s="14" t="n"/>
       <c r="O10" s="14" t="n"/>
+      <c r="P10" s="14" t="n"/>
+      <c r="Q10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n"/>
@@ -16676,6 +18272,8 @@
       <c r="M11" s="14" t="n"/>
       <c r="N11" s="14" t="n"/>
       <c r="O11" s="14" t="n"/>
+      <c r="P11" s="14" t="n"/>
+      <c r="Q11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n"/>
@@ -16693,6 +18291,8 @@
       <c r="M12" s="14" t="n"/>
       <c r="N12" s="14" t="n"/>
       <c r="O12" s="14" t="n"/>
+      <c r="P12" s="14" t="n"/>
+      <c r="Q12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n"/>
@@ -16710,6 +18310,8 @@
       <c r="M13" s="14" t="n"/>
       <c r="N13" s="14" t="n"/>
       <c r="O13" s="14" t="n"/>
+      <c r="P13" s="14" t="n"/>
+      <c r="Q13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n"/>
@@ -16727,6 +18329,8 @@
       <c r="M14" s="14" t="n"/>
       <c r="N14" s="14" t="n"/>
       <c r="O14" s="14" t="n"/>
+      <c r="P14" s="14" t="n"/>
+      <c r="Q14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n"/>
@@ -16744,6 +18348,8 @@
       <c r="M15" s="14" t="n"/>
       <c r="N15" s="14" t="n"/>
       <c r="O15" s="14" t="n"/>
+      <c r="P15" s="14" t="n"/>
+      <c r="Q15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n"/>
@@ -16761,6 +18367,8 @@
       <c r="M16" s="14" t="n"/>
       <c r="N16" s="14" t="n"/>
       <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n"/>
@@ -16778,6 +18386,8 @@
       <c r="M17" s="14" t="n"/>
       <c r="N17" s="14" t="n"/>
       <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n"/>
@@ -16795,6 +18405,8 @@
       <c r="M18" s="14" t="n"/>
       <c r="N18" s="14" t="n"/>
       <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n"/>
@@ -16812,6 +18424,8 @@
       <c r="M19" s="14" t="n"/>
       <c r="N19" s="14" t="n"/>
       <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n"/>
@@ -16829,6 +18443,8 @@
       <c r="M20" s="14" t="n"/>
       <c r="N20" s="14" t="n"/>
       <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
@@ -16846,6 +18462,8 @@
       <c r="M21" s="14" t="n"/>
       <c r="N21" s="14" t="n"/>
       <c r="O21" s="14" t="n"/>
+      <c r="P21" s="14" t="n"/>
+      <c r="Q21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n"/>
@@ -16863,6 +18481,8 @@
       <c r="M22" s="14" t="n"/>
       <c r="N22" s="14" t="n"/>
       <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n"/>
@@ -16880,6 +18500,8 @@
       <c r="M23" s="14" t="n"/>
       <c r="N23" s="14" t="n"/>
       <c r="O23" s="14" t="n"/>
+      <c r="P23" s="14" t="n"/>
+      <c r="Q23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n"/>
@@ -16897,6 +18519,8 @@
       <c r="M24" s="14" t="n"/>
       <c r="N24" s="14" t="n"/>
       <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n"/>
@@ -16914,6 +18538,8 @@
       <c r="M25" s="14" t="n"/>
       <c r="N25" s="14" t="n"/>
       <c r="O25" s="14" t="n"/>
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n"/>
@@ -16931,6 +18557,8 @@
       <c r="M26" s="14" t="n"/>
       <c r="N26" s="14" t="n"/>
       <c r="O26" s="14" t="n"/>
+      <c r="P26" s="14" t="n"/>
+      <c r="Q26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n"/>
@@ -16948,6 +18576,8 @@
       <c r="M27" s="14" t="n"/>
       <c r="N27" s="14" t="n"/>
       <c r="O27" s="14" t="n"/>
+      <c r="P27" s="14" t="n"/>
+      <c r="Q27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n"/>
@@ -16965,6 +18595,8 @@
       <c r="M28" s="14" t="n"/>
       <c r="N28" s="14" t="n"/>
       <c r="O28" s="14" t="n"/>
+      <c r="P28" s="14" t="n"/>
+      <c r="Q28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n"/>
@@ -16982,6 +18614,8 @@
       <c r="M29" s="14" t="n"/>
       <c r="N29" s="14" t="n"/>
       <c r="O29" s="14" t="n"/>
+      <c r="P29" s="14" t="n"/>
+      <c r="Q29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n"/>
@@ -16999,6 +18633,8 @@
       <c r="M30" s="14" t="n"/>
       <c r="N30" s="14" t="n"/>
       <c r="O30" s="14" t="n"/>
+      <c r="P30" s="14" t="n"/>
+      <c r="Q30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n"/>
@@ -17016,6 +18652,8 @@
       <c r="M31" s="14" t="n"/>
       <c r="N31" s="14" t="n"/>
       <c r="O31" s="14" t="n"/>
+      <c r="P31" s="14" t="n"/>
+      <c r="Q31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n"/>
@@ -17033,6 +18671,8 @@
       <c r="M32" s="14" t="n"/>
       <c r="N32" s="14" t="n"/>
       <c r="O32" s="14" t="n"/>
+      <c r="P32" s="14" t="n"/>
+      <c r="Q32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n"/>
@@ -17050,6 +18690,8 @@
       <c r="M33" s="14" t="n"/>
       <c r="N33" s="14" t="n"/>
       <c r="O33" s="14" t="n"/>
+      <c r="P33" s="14" t="n"/>
+      <c r="Q33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n"/>
@@ -17067,6 +18709,8 @@
       <c r="M34" s="14" t="n"/>
       <c r="N34" s="14" t="n"/>
       <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="n"/>
+      <c r="Q34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n"/>
@@ -17084,6 +18728,8 @@
       <c r="M35" s="14" t="n"/>
       <c r="N35" s="14" t="n"/>
       <c r="O35" s="14" t="n"/>
+      <c r="P35" s="14" t="n"/>
+      <c r="Q35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n"/>
@@ -17101,6 +18747,8 @@
       <c r="M36" s="14" t="n"/>
       <c r="N36" s="14" t="n"/>
       <c r="O36" s="14" t="n"/>
+      <c r="P36" s="14" t="n"/>
+      <c r="Q36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n"/>
@@ -17118,6 +18766,8 @@
       <c r="M37" s="14" t="n"/>
       <c r="N37" s="14" t="n"/>
       <c r="O37" s="14" t="n"/>
+      <c r="P37" s="14" t="n"/>
+      <c r="Q37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n"/>
@@ -17135,6 +18785,8 @@
       <c r="M38" s="14" t="n"/>
       <c r="N38" s="14" t="n"/>
       <c r="O38" s="14" t="n"/>
+      <c r="P38" s="14" t="n"/>
+      <c r="Q38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n"/>
@@ -17152,6 +18804,8 @@
       <c r="M39" s="14" t="n"/>
       <c r="N39" s="14" t="n"/>
       <c r="O39" s="14" t="n"/>
+      <c r="P39" s="14" t="n"/>
+      <c r="Q39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n"/>
@@ -17169,6 +18823,8 @@
       <c r="M40" s="14" t="n"/>
       <c r="N40" s="14" t="n"/>
       <c r="O40" s="14" t="n"/>
+      <c r="P40" s="14" t="n"/>
+      <c r="Q40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n"/>
@@ -17186,6 +18842,8 @@
       <c r="M41" s="14" t="n"/>
       <c r="N41" s="14" t="n"/>
       <c r="O41" s="14" t="n"/>
+      <c r="P41" s="14" t="n"/>
+      <c r="Q41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n"/>
@@ -17203,6 +18861,8 @@
       <c r="M42" s="14" t="n"/>
       <c r="N42" s="14" t="n"/>
       <c r="O42" s="14" t="n"/>
+      <c r="P42" s="14" t="n"/>
+      <c r="Q42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n"/>
@@ -17220,6 +18880,8 @@
       <c r="M43" s="14" t="n"/>
       <c r="N43" s="14" t="n"/>
       <c r="O43" s="14" t="n"/>
+      <c r="P43" s="14" t="n"/>
+      <c r="Q43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n"/>
@@ -17237,6 +18899,8 @@
       <c r="M44" s="14" t="n"/>
       <c r="N44" s="14" t="n"/>
       <c r="O44" s="14" t="n"/>
+      <c r="P44" s="14" t="n"/>
+      <c r="Q44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n"/>
@@ -17254,6 +18918,8 @@
       <c r="M45" s="14" t="n"/>
       <c r="N45" s="14" t="n"/>
       <c r="O45" s="14" t="n"/>
+      <c r="P45" s="14" t="n"/>
+      <c r="Q45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n"/>
@@ -17271,6 +18937,8 @@
       <c r="M46" s="14" t="n"/>
       <c r="N46" s="14" t="n"/>
       <c r="O46" s="14" t="n"/>
+      <c r="P46" s="14" t="n"/>
+      <c r="Q46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n"/>
@@ -17288,6 +18956,8 @@
       <c r="M47" s="14" t="n"/>
       <c r="N47" s="14" t="n"/>
       <c r="O47" s="14" t="n"/>
+      <c r="P47" s="14" t="n"/>
+      <c r="Q47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n"/>
@@ -17305,6 +18975,8 @@
       <c r="M48" s="14" t="n"/>
       <c r="N48" s="14" t="n"/>
       <c r="O48" s="14" t="n"/>
+      <c r="P48" s="14" t="n"/>
+      <c r="Q48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n"/>
@@ -17322,6 +18994,8 @@
       <c r="M49" s="14" t="n"/>
       <c r="N49" s="14" t="n"/>
       <c r="O49" s="14" t="n"/>
+      <c r="P49" s="14" t="n"/>
+      <c r="Q49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n"/>
@@ -17339,6 +19013,8 @@
       <c r="M50" s="14" t="n"/>
       <c r="N50" s="14" t="n"/>
       <c r="O50" s="14" t="n"/>
+      <c r="P50" s="14" t="n"/>
+      <c r="Q50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n"/>
@@ -17356,6 +19032,8 @@
       <c r="M51" s="14" t="n"/>
       <c r="N51" s="14" t="n"/>
       <c r="O51" s="14" t="n"/>
+      <c r="P51" s="14" t="n"/>
+      <c r="Q51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n"/>
@@ -17373,6 +19051,8 @@
       <c r="M52" s="14" t="n"/>
       <c r="N52" s="14" t="n"/>
       <c r="O52" s="14" t="n"/>
+      <c r="P52" s="14" t="n"/>
+      <c r="Q52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n"/>
@@ -17390,6 +19070,8 @@
       <c r="M53" s="14" t="n"/>
       <c r="N53" s="14" t="n"/>
       <c r="O53" s="14" t="n"/>
+      <c r="P53" s="14" t="n"/>
+      <c r="Q53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n"/>
@@ -17407,6 +19089,8 @@
       <c r="M54" s="14" t="n"/>
       <c r="N54" s="14" t="n"/>
       <c r="O54" s="14" t="n"/>
+      <c r="P54" s="14" t="n"/>
+      <c r="Q54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n"/>
@@ -17424,6 +19108,8 @@
       <c r="M55" s="14" t="n"/>
       <c r="N55" s="14" t="n"/>
       <c r="O55" s="14" t="n"/>
+      <c r="P55" s="14" t="n"/>
+      <c r="Q55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n"/>
@@ -17441,6 +19127,8 @@
       <c r="M56" s="14" t="n"/>
       <c r="N56" s="14" t="n"/>
       <c r="O56" s="14" t="n"/>
+      <c r="P56" s="14" t="n"/>
+      <c r="Q56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n"/>
@@ -17458,6 +19146,8 @@
       <c r="M57" s="14" t="n"/>
       <c r="N57" s="14" t="n"/>
       <c r="O57" s="14" t="n"/>
+      <c r="P57" s="14" t="n"/>
+      <c r="Q57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n"/>
@@ -17475,6 +19165,8 @@
       <c r="M58" s="14" t="n"/>
       <c r="N58" s="14" t="n"/>
       <c r="O58" s="14" t="n"/>
+      <c r="P58" s="14" t="n"/>
+      <c r="Q58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n"/>
@@ -17492,6 +19184,8 @@
       <c r="M59" s="14" t="n"/>
       <c r="N59" s="14" t="n"/>
       <c r="O59" s="14" t="n"/>
+      <c r="P59" s="14" t="n"/>
+      <c r="Q59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n"/>
@@ -17509,6 +19203,8 @@
       <c r="M60" s="14" t="n"/>
       <c r="N60" s="14" t="n"/>
       <c r="O60" s="14" t="n"/>
+      <c r="P60" s="14" t="n"/>
+      <c r="Q60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n"/>
@@ -17526,6 +19222,8 @@
       <c r="M61" s="14" t="n"/>
       <c r="N61" s="14" t="n"/>
       <c r="O61" s="14" t="n"/>
+      <c r="P61" s="14" t="n"/>
+      <c r="Q61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n"/>
@@ -17543,6 +19241,8 @@
       <c r="M62" s="14" t="n"/>
       <c r="N62" s="14" t="n"/>
       <c r="O62" s="14" t="n"/>
+      <c r="P62" s="14" t="n"/>
+      <c r="Q62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n"/>
@@ -17560,6 +19260,8 @@
       <c r="M63" s="14" t="n"/>
       <c r="N63" s="14" t="n"/>
       <c r="O63" s="14" t="n"/>
+      <c r="P63" s="14" t="n"/>
+      <c r="Q63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n"/>
@@ -17577,6 +19279,8 @@
       <c r="M64" s="14" t="n"/>
       <c r="N64" s="14" t="n"/>
       <c r="O64" s="14" t="n"/>
+      <c r="P64" s="14" t="n"/>
+      <c r="Q64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n"/>
@@ -17594,6 +19298,8 @@
       <c r="M65" s="14" t="n"/>
       <c r="N65" s="14" t="n"/>
       <c r="O65" s="14" t="n"/>
+      <c r="P65" s="14" t="n"/>
+      <c r="Q65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n"/>
@@ -17611,6 +19317,8 @@
       <c r="M66" s="14" t="n"/>
       <c r="N66" s="14" t="n"/>
       <c r="O66" s="14" t="n"/>
+      <c r="P66" s="14" t="n"/>
+      <c r="Q66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n"/>
@@ -17628,6 +19336,8 @@
       <c r="M67" s="14" t="n"/>
       <c r="N67" s="14" t="n"/>
       <c r="O67" s="14" t="n"/>
+      <c r="P67" s="14" t="n"/>
+      <c r="Q67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n"/>
@@ -17645,6 +19355,8 @@
       <c r="M68" s="14" t="n"/>
       <c r="N68" s="14" t="n"/>
       <c r="O68" s="14" t="n"/>
+      <c r="P68" s="14" t="n"/>
+      <c r="Q68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n"/>
@@ -17662,6 +19374,8 @@
       <c r="M69" s="14" t="n"/>
       <c r="N69" s="14" t="n"/>
       <c r="O69" s="14" t="n"/>
+      <c r="P69" s="14" t="n"/>
+      <c r="Q69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n"/>
@@ -17679,6 +19393,8 @@
       <c r="M70" s="14" t="n"/>
       <c r="N70" s="14" t="n"/>
       <c r="O70" s="14" t="n"/>
+      <c r="P70" s="14" t="n"/>
+      <c r="Q70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n"/>
@@ -17696,6 +19412,8 @@
       <c r="M71" s="14" t="n"/>
       <c r="N71" s="14" t="n"/>
       <c r="O71" s="14" t="n"/>
+      <c r="P71" s="14" t="n"/>
+      <c r="Q71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n"/>
@@ -17713,6 +19431,8 @@
       <c r="M72" s="14" t="n"/>
       <c r="N72" s="14" t="n"/>
       <c r="O72" s="14" t="n"/>
+      <c r="P72" s="14" t="n"/>
+      <c r="Q72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n"/>
@@ -17730,6 +19450,8 @@
       <c r="M73" s="14" t="n"/>
       <c r="N73" s="14" t="n"/>
       <c r="O73" s="14" t="n"/>
+      <c r="P73" s="14" t="n"/>
+      <c r="Q73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n"/>
@@ -17747,6 +19469,8 @@
       <c r="M74" s="14" t="n"/>
       <c r="N74" s="14" t="n"/>
       <c r="O74" s="14" t="n"/>
+      <c r="P74" s="14" t="n"/>
+      <c r="Q74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n"/>
@@ -17764,6 +19488,8 @@
       <c r="M75" s="14" t="n"/>
       <c r="N75" s="14" t="n"/>
       <c r="O75" s="14" t="n"/>
+      <c r="P75" s="14" t="n"/>
+      <c r="Q75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n"/>
@@ -17781,6 +19507,8 @@
       <c r="M76" s="14" t="n"/>
       <c r="N76" s="14" t="n"/>
       <c r="O76" s="14" t="n"/>
+      <c r="P76" s="14" t="n"/>
+      <c r="Q76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n"/>
@@ -17798,6 +19526,8 @@
       <c r="M77" s="14" t="n"/>
       <c r="N77" s="14" t="n"/>
       <c r="O77" s="14" t="n"/>
+      <c r="P77" s="14" t="n"/>
+      <c r="Q77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n"/>
@@ -17815,6 +19545,8 @@
       <c r="M78" s="14" t="n"/>
       <c r="N78" s="14" t="n"/>
       <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
+      <c r="Q78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n"/>
@@ -17832,6 +19564,8 @@
       <c r="M79" s="14" t="n"/>
       <c r="N79" s="14" t="n"/>
       <c r="O79" s="14" t="n"/>
+      <c r="P79" s="14" t="n"/>
+      <c r="Q79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n"/>
@@ -17849,6 +19583,8 @@
       <c r="M80" s="14" t="n"/>
       <c r="N80" s="14" t="n"/>
       <c r="O80" s="14" t="n"/>
+      <c r="P80" s="14" t="n"/>
+      <c r="Q80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n"/>
@@ -17866,6 +19602,8 @@
       <c r="M81" s="14" t="n"/>
       <c r="N81" s="14" t="n"/>
       <c r="O81" s="14" t="n"/>
+      <c r="P81" s="14" t="n"/>
+      <c r="Q81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n"/>
@@ -17883,6 +19621,8 @@
       <c r="M82" s="14" t="n"/>
       <c r="N82" s="14" t="n"/>
       <c r="O82" s="14" t="n"/>
+      <c r="P82" s="14" t="n"/>
+      <c r="Q82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n"/>
@@ -17900,6 +19640,8 @@
       <c r="M83" s="14" t="n"/>
       <c r="N83" s="14" t="n"/>
       <c r="O83" s="14" t="n"/>
+      <c r="P83" s="14" t="n"/>
+      <c r="Q83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n"/>
@@ -17917,6 +19659,8 @@
       <c r="M84" s="14" t="n"/>
       <c r="N84" s="14" t="n"/>
       <c r="O84" s="14" t="n"/>
+      <c r="P84" s="14" t="n"/>
+      <c r="Q84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n"/>
@@ -17934,6 +19678,8 @@
       <c r="M85" s="14" t="n"/>
       <c r="N85" s="14" t="n"/>
       <c r="O85" s="14" t="n"/>
+      <c r="P85" s="14" t="n"/>
+      <c r="Q85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n"/>
@@ -17951,6 +19697,8 @@
       <c r="M86" s="14" t="n"/>
       <c r="N86" s="14" t="n"/>
       <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
+      <c r="Q86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n"/>
@@ -17968,6 +19716,8 @@
       <c r="M87" s="14" t="n"/>
       <c r="N87" s="14" t="n"/>
       <c r="O87" s="14" t="n"/>
+      <c r="P87" s="14" t="n"/>
+      <c r="Q87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n"/>
@@ -17985,6 +19735,8 @@
       <c r="M88" s="14" t="n"/>
       <c r="N88" s="14" t="n"/>
       <c r="O88" s="14" t="n"/>
+      <c r="P88" s="14" t="n"/>
+      <c r="Q88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n"/>
@@ -18002,6 +19754,8 @@
       <c r="M89" s="14" t="n"/>
       <c r="N89" s="14" t="n"/>
       <c r="O89" s="14" t="n"/>
+      <c r="P89" s="14" t="n"/>
+      <c r="Q89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n"/>
@@ -18019,6 +19773,8 @@
       <c r="M90" s="14" t="n"/>
       <c r="N90" s="14" t="n"/>
       <c r="O90" s="14" t="n"/>
+      <c r="P90" s="14" t="n"/>
+      <c r="Q90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n"/>
@@ -18036,6 +19792,8 @@
       <c r="M91" s="14" t="n"/>
       <c r="N91" s="14" t="n"/>
       <c r="O91" s="14" t="n"/>
+      <c r="P91" s="14" t="n"/>
+      <c r="Q91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n"/>
@@ -18053,6 +19811,8 @@
       <c r="M92" s="14" t="n"/>
       <c r="N92" s="14" t="n"/>
       <c r="O92" s="14" t="n"/>
+      <c r="P92" s="14" t="n"/>
+      <c r="Q92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n"/>
@@ -18070,6 +19830,8 @@
       <c r="M93" s="14" t="n"/>
       <c r="N93" s="14" t="n"/>
       <c r="O93" s="14" t="n"/>
+      <c r="P93" s="14" t="n"/>
+      <c r="Q93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n"/>
@@ -18087,6 +19849,8 @@
       <c r="M94" s="14" t="n"/>
       <c r="N94" s="14" t="n"/>
       <c r="O94" s="14" t="n"/>
+      <c r="P94" s="14" t="n"/>
+      <c r="Q94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n"/>
@@ -18104,6 +19868,8 @@
       <c r="M95" s="14" t="n"/>
       <c r="N95" s="14" t="n"/>
       <c r="O95" s="14" t="n"/>
+      <c r="P95" s="14" t="n"/>
+      <c r="Q95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n"/>
@@ -18121,6 +19887,8 @@
       <c r="M96" s="14" t="n"/>
       <c r="N96" s="14" t="n"/>
       <c r="O96" s="14" t="n"/>
+      <c r="P96" s="14" t="n"/>
+      <c r="Q96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n"/>
@@ -18138,6 +19906,8 @@
       <c r="M97" s="14" t="n"/>
       <c r="N97" s="14" t="n"/>
       <c r="O97" s="14" t="n"/>
+      <c r="P97" s="14" t="n"/>
+      <c r="Q97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n"/>
@@ -18155,6 +19925,8 @@
       <c r="M98" s="14" t="n"/>
       <c r="N98" s="14" t="n"/>
       <c r="O98" s="14" t="n"/>
+      <c r="P98" s="14" t="n"/>
+      <c r="Q98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n"/>
@@ -18172,6 +19944,8 @@
       <c r="M99" s="14" t="n"/>
       <c r="N99" s="14" t="n"/>
       <c r="O99" s="14" t="n"/>
+      <c r="P99" s="14" t="n"/>
+      <c r="Q99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n"/>
@@ -18189,6 +19963,8 @@
       <c r="M100" s="14" t="n"/>
       <c r="N100" s="14" t="n"/>
       <c r="O100" s="14" t="n"/>
+      <c r="P100" s="14" t="n"/>
+      <c r="Q100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n"/>
@@ -18206,6 +19982,8 @@
       <c r="M101" s="14" t="n"/>
       <c r="N101" s="14" t="n"/>
       <c r="O101" s="14" t="n"/>
+      <c r="P101" s="14" t="n"/>
+      <c r="Q101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n"/>
@@ -18223,6 +20001,8 @@
       <c r="M102" s="14" t="n"/>
       <c r="N102" s="14" t="n"/>
       <c r="O102" s="14" t="n"/>
+      <c r="P102" s="14" t="n"/>
+      <c r="Q102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n"/>
@@ -18240,6 +20020,8 @@
       <c r="M103" s="14" t="n"/>
       <c r="N103" s="14" t="n"/>
       <c r="O103" s="14" t="n"/>
+      <c r="P103" s="14" t="n"/>
+      <c r="Q103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n"/>
@@ -18257,6 +20039,8 @@
       <c r="M104" s="14" t="n"/>
       <c r="N104" s="14" t="n"/>
       <c r="O104" s="14" t="n"/>
+      <c r="P104" s="14" t="n"/>
+      <c r="Q104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n"/>
@@ -18274,6 +20058,8 @@
       <c r="M105" s="14" t="n"/>
       <c r="N105" s="14" t="n"/>
       <c r="O105" s="14" t="n"/>
+      <c r="P105" s="14" t="n"/>
+      <c r="Q105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n"/>
@@ -18291,6 +20077,8 @@
       <c r="M106" s="14" t="n"/>
       <c r="N106" s="14" t="n"/>
       <c r="O106" s="14" t="n"/>
+      <c r="P106" s="14" t="n"/>
+      <c r="Q106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n"/>
@@ -18308,6 +20096,8 @@
       <c r="M107" s="14" t="n"/>
       <c r="N107" s="14" t="n"/>
       <c r="O107" s="14" t="n"/>
+      <c r="P107" s="14" t="n"/>
+      <c r="Q107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n"/>
@@ -18325,6 +20115,8 @@
       <c r="M108" s="14" t="n"/>
       <c r="N108" s="14" t="n"/>
       <c r="O108" s="14" t="n"/>
+      <c r="P108" s="14" t="n"/>
+      <c r="Q108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n"/>
@@ -18342,6 +20134,8 @@
       <c r="M109" s="14" t="n"/>
       <c r="N109" s="14" t="n"/>
       <c r="O109" s="14" t="n"/>
+      <c r="P109" s="14" t="n"/>
+      <c r="Q109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n"/>
@@ -18359,6 +20153,8 @@
       <c r="M110" s="14" t="n"/>
       <c r="N110" s="14" t="n"/>
       <c r="O110" s="14" t="n"/>
+      <c r="P110" s="14" t="n"/>
+      <c r="Q110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n"/>
@@ -18376,6 +20172,8 @@
       <c r="M111" s="14" t="n"/>
       <c r="N111" s="14" t="n"/>
       <c r="O111" s="14" t="n"/>
+      <c r="P111" s="14" t="n"/>
+      <c r="Q111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n"/>
@@ -18393,6 +20191,8 @@
       <c r="M112" s="14" t="n"/>
       <c r="N112" s="14" t="n"/>
       <c r="O112" s="14" t="n"/>
+      <c r="P112" s="14" t="n"/>
+      <c r="Q112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n"/>
@@ -18410,6 +20210,8 @@
       <c r="M113" s="14" t="n"/>
       <c r="N113" s="14" t="n"/>
       <c r="O113" s="14" t="n"/>
+      <c r="P113" s="14" t="n"/>
+      <c r="Q113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n"/>
@@ -18427,6 +20229,8 @@
       <c r="M114" s="14" t="n"/>
       <c r="N114" s="14" t="n"/>
       <c r="O114" s="14" t="n"/>
+      <c r="P114" s="14" t="n"/>
+      <c r="Q114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n"/>
@@ -18444,6 +20248,8 @@
       <c r="M115" s="14" t="n"/>
       <c r="N115" s="14" t="n"/>
       <c r="O115" s="14" t="n"/>
+      <c r="P115" s="14" t="n"/>
+      <c r="Q115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n"/>
@@ -18461,6 +20267,8 @@
       <c r="M116" s="14" t="n"/>
       <c r="N116" s="14" t="n"/>
       <c r="O116" s="14" t="n"/>
+      <c r="P116" s="14" t="n"/>
+      <c r="Q116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n"/>
@@ -18478,6 +20286,8 @@
       <c r="M117" s="14" t="n"/>
       <c r="N117" s="14" t="n"/>
       <c r="O117" s="14" t="n"/>
+      <c r="P117" s="14" t="n"/>
+      <c r="Q117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n"/>
@@ -18495,6 +20305,8 @@
       <c r="M118" s="14" t="n"/>
       <c r="N118" s="14" t="n"/>
       <c r="O118" s="14" t="n"/>
+      <c r="P118" s="14" t="n"/>
+      <c r="Q118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n"/>
@@ -18512,6 +20324,8 @@
       <c r="M119" s="14" t="n"/>
       <c r="N119" s="14" t="n"/>
       <c r="O119" s="14" t="n"/>
+      <c r="P119" s="14" t="n"/>
+      <c r="Q119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n"/>
@@ -18529,6 +20343,8 @@
       <c r="M120" s="14" t="n"/>
       <c r="N120" s="14" t="n"/>
       <c r="O120" s="14" t="n"/>
+      <c r="P120" s="14" t="n"/>
+      <c r="Q120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n"/>
@@ -18546,6 +20362,8 @@
       <c r="M121" s="14" t="n"/>
       <c r="N121" s="14" t="n"/>
       <c r="O121" s="14" t="n"/>
+      <c r="P121" s="14" t="n"/>
+      <c r="Q121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n"/>
@@ -18563,6 +20381,8 @@
       <c r="M122" s="14" t="n"/>
       <c r="N122" s="14" t="n"/>
       <c r="O122" s="14" t="n"/>
+      <c r="P122" s="14" t="n"/>
+      <c r="Q122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n"/>
@@ -18580,6 +20400,8 @@
       <c r="M123" s="14" t="n"/>
       <c r="N123" s="14" t="n"/>
       <c r="O123" s="14" t="n"/>
+      <c r="P123" s="14" t="n"/>
+      <c r="Q123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n"/>
@@ -18597,6 +20419,8 @@
       <c r="M124" s="14" t="n"/>
       <c r="N124" s="14" t="n"/>
       <c r="O124" s="14" t="n"/>
+      <c r="P124" s="14" t="n"/>
+      <c r="Q124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n"/>
@@ -18614,6 +20438,8 @@
       <c r="M125" s="14" t="n"/>
       <c r="N125" s="14" t="n"/>
       <c r="O125" s="14" t="n"/>
+      <c r="P125" s="14" t="n"/>
+      <c r="Q125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n"/>
@@ -18631,6 +20457,8 @@
       <c r="M126" s="14" t="n"/>
       <c r="N126" s="14" t="n"/>
       <c r="O126" s="14" t="n"/>
+      <c r="P126" s="14" t="n"/>
+      <c r="Q126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n"/>
@@ -18648,6 +20476,8 @@
       <c r="M127" s="14" t="n"/>
       <c r="N127" s="14" t="n"/>
       <c r="O127" s="14" t="n"/>
+      <c r="P127" s="14" t="n"/>
+      <c r="Q127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n"/>
@@ -18665,6 +20495,8 @@
       <c r="M128" s="14" t="n"/>
       <c r="N128" s="14" t="n"/>
       <c r="O128" s="14" t="n"/>
+      <c r="P128" s="14" t="n"/>
+      <c r="Q128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n"/>
@@ -18682,6 +20514,8 @@
       <c r="M129" s="14" t="n"/>
       <c r="N129" s="14" t="n"/>
       <c r="O129" s="14" t="n"/>
+      <c r="P129" s="14" t="n"/>
+      <c r="Q129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n"/>
@@ -18699,6 +20533,8 @@
       <c r="M130" s="14" t="n"/>
       <c r="N130" s="14" t="n"/>
       <c r="O130" s="14" t="n"/>
+      <c r="P130" s="14" t="n"/>
+      <c r="Q130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n"/>
@@ -18716,6 +20552,8 @@
       <c r="M131" s="14" t="n"/>
       <c r="N131" s="14" t="n"/>
       <c r="O131" s="14" t="n"/>
+      <c r="P131" s="14" t="n"/>
+      <c r="Q131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="14" t="n"/>
@@ -18733,6 +20571,8 @@
       <c r="M132" s="14" t="n"/>
       <c r="N132" s="14" t="n"/>
       <c r="O132" s="14" t="n"/>
+      <c r="P132" s="14" t="n"/>
+      <c r="Q132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n"/>
@@ -18750,6 +20590,8 @@
       <c r="M133" s="14" t="n"/>
       <c r="N133" s="14" t="n"/>
       <c r="O133" s="14" t="n"/>
+      <c r="P133" s="14" t="n"/>
+      <c r="Q133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="14" t="n"/>
@@ -18767,6 +20609,8 @@
       <c r="M134" s="14" t="n"/>
       <c r="N134" s="14" t="n"/>
       <c r="O134" s="14" t="n"/>
+      <c r="P134" s="14" t="n"/>
+      <c r="Q134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n"/>
@@ -18784,6 +20628,8 @@
       <c r="M135" s="14" t="n"/>
       <c r="N135" s="14" t="n"/>
       <c r="O135" s="14" t="n"/>
+      <c r="P135" s="14" t="n"/>
+      <c r="Q135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="14" t="n"/>
@@ -18801,6 +20647,8 @@
       <c r="M136" s="14" t="n"/>
       <c r="N136" s="14" t="n"/>
       <c r="O136" s="14" t="n"/>
+      <c r="P136" s="14" t="n"/>
+      <c r="Q136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n"/>
@@ -18818,6 +20666,8 @@
       <c r="M137" s="14" t="n"/>
       <c r="N137" s="14" t="n"/>
       <c r="O137" s="14" t="n"/>
+      <c r="P137" s="14" t="n"/>
+      <c r="Q137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="14" t="n"/>
@@ -18835,6 +20685,8 @@
       <c r="M138" s="14" t="n"/>
       <c r="N138" s="14" t="n"/>
       <c r="O138" s="14" t="n"/>
+      <c r="P138" s="14" t="n"/>
+      <c r="Q138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n"/>
@@ -18852,6 +20704,8 @@
       <c r="M139" s="14" t="n"/>
       <c r="N139" s="14" t="n"/>
       <c r="O139" s="14" t="n"/>
+      <c r="P139" s="14" t="n"/>
+      <c r="Q139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="14" t="n"/>
@@ -18869,6 +20723,8 @@
       <c r="M140" s="14" t="n"/>
       <c r="N140" s="14" t="n"/>
       <c r="O140" s="14" t="n"/>
+      <c r="P140" s="14" t="n"/>
+      <c r="Q140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n"/>
@@ -18886,6 +20742,8 @@
       <c r="M141" s="14" t="n"/>
       <c r="N141" s="14" t="n"/>
       <c r="O141" s="14" t="n"/>
+      <c r="P141" s="14" t="n"/>
+      <c r="Q141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="14" t="n"/>
@@ -18903,6 +20761,8 @@
       <c r="M142" s="14" t="n"/>
       <c r="N142" s="14" t="n"/>
       <c r="O142" s="14" t="n"/>
+      <c r="P142" s="14" t="n"/>
+      <c r="Q142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n"/>
@@ -18920,6 +20780,8 @@
       <c r="M143" s="14" t="n"/>
       <c r="N143" s="14" t="n"/>
       <c r="O143" s="14" t="n"/>
+      <c r="P143" s="14" t="n"/>
+      <c r="Q143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n"/>
@@ -18937,6 +20799,8 @@
       <c r="M144" s="14" t="n"/>
       <c r="N144" s="14" t="n"/>
       <c r="O144" s="14" t="n"/>
+      <c r="P144" s="14" t="n"/>
+      <c r="Q144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n"/>
@@ -18954,6 +20818,8 @@
       <c r="M145" s="14" t="n"/>
       <c r="N145" s="14" t="n"/>
       <c r="O145" s="14" t="n"/>
+      <c r="P145" s="14" t="n"/>
+      <c r="Q145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="14" t="n"/>
@@ -18971,6 +20837,8 @@
       <c r="M146" s="14" t="n"/>
       <c r="N146" s="14" t="n"/>
       <c r="O146" s="14" t="n"/>
+      <c r="P146" s="14" t="n"/>
+      <c r="Q146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n"/>
@@ -18988,6 +20856,8 @@
       <c r="M147" s="14" t="n"/>
       <c r="N147" s="14" t="n"/>
       <c r="O147" s="14" t="n"/>
+      <c r="P147" s="14" t="n"/>
+      <c r="Q147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="14" t="n"/>
@@ -19005,6 +20875,8 @@
       <c r="M148" s="14" t="n"/>
       <c r="N148" s="14" t="n"/>
       <c r="O148" s="14" t="n"/>
+      <c r="P148" s="14" t="n"/>
+      <c r="Q148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n"/>
@@ -19022,6 +20894,8 @@
       <c r="M149" s="14" t="n"/>
       <c r="N149" s="14" t="n"/>
       <c r="O149" s="14" t="n"/>
+      <c r="P149" s="14" t="n"/>
+      <c r="Q149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="14" t="n"/>
@@ -19039,6 +20913,8 @@
       <c r="M150" s="14" t="n"/>
       <c r="N150" s="14" t="n"/>
       <c r="O150" s="14" t="n"/>
+      <c r="P150" s="14" t="n"/>
+      <c r="Q150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n"/>
@@ -19056,6 +20932,8 @@
       <c r="M151" s="14" t="n"/>
       <c r="N151" s="14" t="n"/>
       <c r="O151" s="14" t="n"/>
+      <c r="P151" s="14" t="n"/>
+      <c r="Q151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="14" t="n"/>
@@ -19073,6 +20951,8 @@
       <c r="M152" s="14" t="n"/>
       <c r="N152" s="14" t="n"/>
       <c r="O152" s="14" t="n"/>
+      <c r="P152" s="14" t="n"/>
+      <c r="Q152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n"/>
@@ -19090,6 +20970,8 @@
       <c r="M153" s="14" t="n"/>
       <c r="N153" s="14" t="n"/>
       <c r="O153" s="14" t="n"/>
+      <c r="P153" s="14" t="n"/>
+      <c r="Q153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="14" t="n"/>
@@ -19107,6 +20989,8 @@
       <c r="M154" s="14" t="n"/>
       <c r="N154" s="14" t="n"/>
       <c r="O154" s="14" t="n"/>
+      <c r="P154" s="14" t="n"/>
+      <c r="Q154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n"/>
@@ -19124,6 +21008,8 @@
       <c r="M155" s="14" t="n"/>
       <c r="N155" s="14" t="n"/>
       <c r="O155" s="14" t="n"/>
+      <c r="P155" s="14" t="n"/>
+      <c r="Q155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n"/>
@@ -19141,6 +21027,8 @@
       <c r="M156" s="14" t="n"/>
       <c r="N156" s="14" t="n"/>
       <c r="O156" s="14" t="n"/>
+      <c r="P156" s="14" t="n"/>
+      <c r="Q156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n"/>
@@ -19158,6 +21046,8 @@
       <c r="M157" s="14" t="n"/>
       <c r="N157" s="14" t="n"/>
       <c r="O157" s="14" t="n"/>
+      <c r="P157" s="14" t="n"/>
+      <c r="Q157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="14" t="n"/>
@@ -19175,6 +21065,8 @@
       <c r="M158" s="14" t="n"/>
       <c r="N158" s="14" t="n"/>
       <c r="O158" s="14" t="n"/>
+      <c r="P158" s="14" t="n"/>
+      <c r="Q158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n"/>
@@ -19192,6 +21084,8 @@
       <c r="M159" s="14" t="n"/>
       <c r="N159" s="14" t="n"/>
       <c r="O159" s="14" t="n"/>
+      <c r="P159" s="14" t="n"/>
+      <c r="Q159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="14" t="n"/>
@@ -19209,6 +21103,8 @@
       <c r="M160" s="14" t="n"/>
       <c r="N160" s="14" t="n"/>
       <c r="O160" s="14" t="n"/>
+      <c r="P160" s="14" t="n"/>
+      <c r="Q160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n"/>
@@ -19226,6 +21122,8 @@
       <c r="M161" s="14" t="n"/>
       <c r="N161" s="14" t="n"/>
       <c r="O161" s="14" t="n"/>
+      <c r="P161" s="14" t="n"/>
+      <c r="Q161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="14" t="n"/>
@@ -19243,6 +21141,8 @@
       <c r="M162" s="14" t="n"/>
       <c r="N162" s="14" t="n"/>
       <c r="O162" s="14" t="n"/>
+      <c r="P162" s="14" t="n"/>
+      <c r="Q162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n"/>
@@ -19260,6 +21160,8 @@
       <c r="M163" s="14" t="n"/>
       <c r="N163" s="14" t="n"/>
       <c r="O163" s="14" t="n"/>
+      <c r="P163" s="14" t="n"/>
+      <c r="Q163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n"/>
@@ -19277,6 +21179,8 @@
       <c r="M164" s="14" t="n"/>
       <c r="N164" s="14" t="n"/>
       <c r="O164" s="14" t="n"/>
+      <c r="P164" s="14" t="n"/>
+      <c r="Q164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n"/>
@@ -19294,6 +21198,8 @@
       <c r="M165" s="14" t="n"/>
       <c r="N165" s="14" t="n"/>
       <c r="O165" s="14" t="n"/>
+      <c r="P165" s="14" t="n"/>
+      <c r="Q165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n"/>
@@ -19311,6 +21217,8 @@
       <c r="M166" s="14" t="n"/>
       <c r="N166" s="14" t="n"/>
       <c r="O166" s="14" t="n"/>
+      <c r="P166" s="14" t="n"/>
+      <c r="Q166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n"/>
@@ -19328,6 +21236,8 @@
       <c r="M167" s="14" t="n"/>
       <c r="N167" s="14" t="n"/>
       <c r="O167" s="14" t="n"/>
+      <c r="P167" s="14" t="n"/>
+      <c r="Q167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="14" t="n"/>
@@ -19345,6 +21255,8 @@
       <c r="M168" s="14" t="n"/>
       <c r="N168" s="14" t="n"/>
       <c r="O168" s="14" t="n"/>
+      <c r="P168" s="14" t="n"/>
+      <c r="Q168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n"/>
@@ -19362,6 +21274,8 @@
       <c r="M169" s="14" t="n"/>
       <c r="N169" s="14" t="n"/>
       <c r="O169" s="14" t="n"/>
+      <c r="P169" s="14" t="n"/>
+      <c r="Q169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="14" t="n"/>
@@ -19379,6 +21293,8 @@
       <c r="M170" s="14" t="n"/>
       <c r="N170" s="14" t="n"/>
       <c r="O170" s="14" t="n"/>
+      <c r="P170" s="14" t="n"/>
+      <c r="Q170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n"/>
@@ -19396,6 +21312,8 @@
       <c r="M171" s="14" t="n"/>
       <c r="N171" s="14" t="n"/>
       <c r="O171" s="14" t="n"/>
+      <c r="P171" s="14" t="n"/>
+      <c r="Q171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n"/>
@@ -19413,6 +21331,8 @@
       <c r="M172" s="14" t="n"/>
       <c r="N172" s="14" t="n"/>
       <c r="O172" s="14" t="n"/>
+      <c r="P172" s="14" t="n"/>
+      <c r="Q172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n"/>
@@ -19430,6 +21350,8 @@
       <c r="M173" s="14" t="n"/>
       <c r="N173" s="14" t="n"/>
       <c r="O173" s="14" t="n"/>
+      <c r="P173" s="14" t="n"/>
+      <c r="Q173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n"/>
@@ -19447,6 +21369,8 @@
       <c r="M174" s="14" t="n"/>
       <c r="N174" s="14" t="n"/>
       <c r="O174" s="14" t="n"/>
+      <c r="P174" s="14" t="n"/>
+      <c r="Q174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n"/>
@@ -19464,6 +21388,8 @@
       <c r="M175" s="14" t="n"/>
       <c r="N175" s="14" t="n"/>
       <c r="O175" s="14" t="n"/>
+      <c r="P175" s="14" t="n"/>
+      <c r="Q175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n"/>
@@ -19481,6 +21407,8 @@
       <c r="M176" s="14" t="n"/>
       <c r="N176" s="14" t="n"/>
       <c r="O176" s="14" t="n"/>
+      <c r="P176" s="14" t="n"/>
+      <c r="Q176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n"/>
@@ -19498,6 +21426,8 @@
       <c r="M177" s="14" t="n"/>
       <c r="N177" s="14" t="n"/>
       <c r="O177" s="14" t="n"/>
+      <c r="P177" s="14" t="n"/>
+      <c r="Q177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n"/>
@@ -19515,6 +21445,8 @@
       <c r="M178" s="14" t="n"/>
       <c r="N178" s="14" t="n"/>
       <c r="O178" s="14" t="n"/>
+      <c r="P178" s="14" t="n"/>
+      <c r="Q178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n"/>
@@ -19532,6 +21464,8 @@
       <c r="M179" s="14" t="n"/>
       <c r="N179" s="14" t="n"/>
       <c r="O179" s="14" t="n"/>
+      <c r="P179" s="14" t="n"/>
+      <c r="Q179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n"/>
@@ -19549,6 +21483,8 @@
       <c r="M180" s="14" t="n"/>
       <c r="N180" s="14" t="n"/>
       <c r="O180" s="14" t="n"/>
+      <c r="P180" s="14" t="n"/>
+      <c r="Q180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n"/>
@@ -19566,6 +21502,8 @@
       <c r="M181" s="14" t="n"/>
       <c r="N181" s="14" t="n"/>
       <c r="O181" s="14" t="n"/>
+      <c r="P181" s="14" t="n"/>
+      <c r="Q181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n"/>
@@ -19583,6 +21521,8 @@
       <c r="M182" s="14" t="n"/>
       <c r="N182" s="14" t="n"/>
       <c r="O182" s="14" t="n"/>
+      <c r="P182" s="14" t="n"/>
+      <c r="Q182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n"/>
@@ -19600,6 +21540,8 @@
       <c r="M183" s="14" t="n"/>
       <c r="N183" s="14" t="n"/>
       <c r="O183" s="14" t="n"/>
+      <c r="P183" s="14" t="n"/>
+      <c r="Q183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n"/>
@@ -19617,6 +21559,8 @@
       <c r="M184" s="14" t="n"/>
       <c r="N184" s="14" t="n"/>
       <c r="O184" s="14" t="n"/>
+      <c r="P184" s="14" t="n"/>
+      <c r="Q184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n"/>
@@ -19634,6 +21578,8 @@
       <c r="M185" s="14" t="n"/>
       <c r="N185" s="14" t="n"/>
       <c r="O185" s="14" t="n"/>
+      <c r="P185" s="14" t="n"/>
+      <c r="Q185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n"/>
@@ -19651,6 +21597,8 @@
       <c r="M186" s="14" t="n"/>
       <c r="N186" s="14" t="n"/>
       <c r="O186" s="14" t="n"/>
+      <c r="P186" s="14" t="n"/>
+      <c r="Q186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n"/>
@@ -19668,6 +21616,8 @@
       <c r="M187" s="14" t="n"/>
       <c r="N187" s="14" t="n"/>
       <c r="O187" s="14" t="n"/>
+      <c r="P187" s="14" t="n"/>
+      <c r="Q187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n"/>
@@ -19685,6 +21635,8 @@
       <c r="M188" s="14" t="n"/>
       <c r="N188" s="14" t="n"/>
       <c r="O188" s="14" t="n"/>
+      <c r="P188" s="14" t="n"/>
+      <c r="Q188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n"/>
@@ -19702,6 +21654,8 @@
       <c r="M189" s="14" t="n"/>
       <c r="N189" s="14" t="n"/>
       <c r="O189" s="14" t="n"/>
+      <c r="P189" s="14" t="n"/>
+      <c r="Q189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n"/>
@@ -19719,6 +21673,8 @@
       <c r="M190" s="14" t="n"/>
       <c r="N190" s="14" t="n"/>
       <c r="O190" s="14" t="n"/>
+      <c r="P190" s="14" t="n"/>
+      <c r="Q190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n"/>
@@ -19736,6 +21692,8 @@
       <c r="M191" s="14" t="n"/>
       <c r="N191" s="14" t="n"/>
       <c r="O191" s="14" t="n"/>
+      <c r="P191" s="14" t="n"/>
+      <c r="Q191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n"/>
@@ -19753,6 +21711,8 @@
       <c r="M192" s="14" t="n"/>
       <c r="N192" s="14" t="n"/>
       <c r="O192" s="14" t="n"/>
+      <c r="P192" s="14" t="n"/>
+      <c r="Q192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n"/>
@@ -19770,6 +21730,8 @@
       <c r="M193" s="14" t="n"/>
       <c r="N193" s="14" t="n"/>
       <c r="O193" s="14" t="n"/>
+      <c r="P193" s="14" t="n"/>
+      <c r="Q193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n"/>
@@ -19787,6 +21749,8 @@
       <c r="M194" s="14" t="n"/>
       <c r="N194" s="14" t="n"/>
       <c r="O194" s="14" t="n"/>
+      <c r="P194" s="14" t="n"/>
+      <c r="Q194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n"/>
@@ -19804,6 +21768,8 @@
       <c r="M195" s="14" t="n"/>
       <c r="N195" s="14" t="n"/>
       <c r="O195" s="14" t="n"/>
+      <c r="P195" s="14" t="n"/>
+      <c r="Q195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n"/>
@@ -19821,6 +21787,8 @@
       <c r="M196" s="14" t="n"/>
       <c r="N196" s="14" t="n"/>
       <c r="O196" s="14" t="n"/>
+      <c r="P196" s="14" t="n"/>
+      <c r="Q196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n"/>
@@ -19838,6 +21806,8 @@
       <c r="M197" s="14" t="n"/>
       <c r="N197" s="14" t="n"/>
       <c r="O197" s="14" t="n"/>
+      <c r="P197" s="14" t="n"/>
+      <c r="Q197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n"/>
@@ -19855,6 +21825,8 @@
       <c r="M198" s="14" t="n"/>
       <c r="N198" s="14" t="n"/>
       <c r="O198" s="14" t="n"/>
+      <c r="P198" s="14" t="n"/>
+      <c r="Q198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n"/>
@@ -19872,6 +21844,8 @@
       <c r="M199" s="14" t="n"/>
       <c r="N199" s="14" t="n"/>
       <c r="O199" s="14" t="n"/>
+      <c r="P199" s="14" t="n"/>
+      <c r="Q199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n"/>
@@ -19889,6 +21863,8 @@
       <c r="M200" s="14" t="n"/>
       <c r="N200" s="14" t="n"/>
       <c r="O200" s="14" t="n"/>
+      <c r="P200" s="14" t="n"/>
+      <c r="Q200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n"/>
@@ -19906,6 +21882,8 @@
       <c r="M201" s="14" t="n"/>
       <c r="N201" s="14" t="n"/>
       <c r="O201" s="14" t="n"/>
+      <c r="P201" s="14" t="n"/>
+      <c r="Q201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n"/>
@@ -19923,6 +21901,8 @@
       <c r="M202" s="14" t="n"/>
       <c r="N202" s="14" t="n"/>
       <c r="O202" s="14" t="n"/>
+      <c r="P202" s="14" t="n"/>
+      <c r="Q202" s="14" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">

--- a/templates/FlexiTog_data_request_pack.xlsx
+++ b/templates/FlexiTog_data_request_pack.xlsx
@@ -783,8 +783,8 @@
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Optional. For the dashboard map. Blank = city lookup
-Type: float</t>
+        <t>Can ship straight to a distributor, 3PL or owned warehouse. Blank = yes
+Type: bool</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
@@ -794,6 +794,12 @@
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. For the dashboard map. Blank = city lookup
+Type: float</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>notes
 Type: str</t>
@@ -1450,12 +1456,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Largest cost line in every scenario. Need single-shipment (groupage/LCL) and consolidated (FTL/FCL) rates, minimum charges and transit days.</t>
+          <t>Largest cost line in every scenario. Need single-shipment (groupage/LCL) and consolidated (FTL/FCL) rates, minimum charges and transit days, for supplier to Helmond, Helmond to each market, and supplier straight to each partner country (direct refill).</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Forwarder quotes and invoices of the last 12 months. Logistics team.</t>
+          <t>Forwarder quotes and invoices of the last 12 months. Supplier and forwarder quotes for direct delivery to partners. Logistics team.</t>
         </is>
       </c>
       <c r="F15" s="8" t="n"/>
@@ -1471,11 +1477,11 @@
         </is>
       </c>
       <c r="J15" s="5">
-        <f>COUNTA('Freight rates'!A2:A81)</f>
+        <f>COUNTA('Freight rates'!A2:A101)</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>COUNTIF('Freight rates'!I2:I81,"real")</f>
+        <f>COUNTIF('Freight rates'!J2:J101,"real")</f>
         <v/>
       </c>
     </row>
@@ -1743,11 +1749,11 @@
         </is>
       </c>
       <c r="J21" s="5">
-        <f>COUNTA('Helmond costs'!A2:A77)</f>
+        <f>COUNTA('Helmond costs'!A2:A81)</f>
         <v/>
       </c>
       <c r="K21" s="5">
-        <f>COUNTIF('Helmond costs'!E2:E77,"real")</f>
+        <f>COUNTIF('Helmond costs'!E2:E81,"real")</f>
         <v/>
       </c>
     </row>
@@ -2255,7 +2261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2717,9 +2723,109 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>direct_sourcing_mode</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>0 never / 1 when cheaper / 2 always</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Stocked scenarios only. 1 = per supplier, ship direct to the node when that costs less per pallet than going through Helmond. 2 = direct whenever a direct rate exists</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>direct_replenishment_pallets_per_shipment</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t>pallets</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>One 40 ft container or one truck per supplier per refill. Spreads origin export fees</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>origin_export_docs_eur_per_shipment</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>EUR/shipment</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Export declaration and certificate of origin in the supplier country, via its forwarder</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>risk_premium_direct_sourcing_pct</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>% of cost</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Routing score penalty, scaled by the share of pallets sourced direct: new lanes, no quality check or relabelling at Helmond</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"placeholder,real"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3138,7 +3244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N202"/>
+  <dimension ref="A1:O202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3151,9 +3257,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3209,15 +3316,20 @@
       </c>
       <c r="K1" s="4" t="inlineStr">
         <is>
+          <t>direct_to_partners</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
           <t>latitude</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>longitude</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -3272,14 +3384,17 @@
           <t>road</t>
         </is>
       </c>
-      <c r="K2" s="12" t="n"/>
+      <c r="K2" s="12" t="b">
+        <v>1</v>
+      </c>
       <c r="L2" s="12" t="n"/>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="M2" s="12" t="n"/>
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>Cut-make-trim for the FlexiTog line. Road via Montenegro and Croatia, or ferry to Bari</t>
         </is>
       </c>
-      <c r="N2" s="13" t="inlineStr">
+      <c r="O2" s="13" t="inlineStr">
         <is>
           <t>EXAMPLE ROW: delete before upload</t>
         </is>
@@ -3299,6 +3414,7 @@
       <c r="K3" s="14" t="n"/>
       <c r="L3" s="14" t="n"/>
       <c r="M3" s="14" t="n"/>
+      <c r="N3" s="14" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="n"/>
@@ -3314,6 +3430,7 @@
       <c r="K4" s="14" t="n"/>
       <c r="L4" s="14" t="n"/>
       <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="n"/>
@@ -3329,6 +3446,7 @@
       <c r="K5" s="14" t="n"/>
       <c r="L5" s="14" t="n"/>
       <c r="M5" s="14" t="n"/>
+      <c r="N5" s="14" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="n"/>
@@ -3344,6 +3462,7 @@
       <c r="K6" s="14" t="n"/>
       <c r="L6" s="14" t="n"/>
       <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="14" t="n"/>
@@ -3359,6 +3478,7 @@
       <c r="K7" s="14" t="n"/>
       <c r="L7" s="14" t="n"/>
       <c r="M7" s="14" t="n"/>
+      <c r="N7" s="14" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="n"/>
@@ -3374,6 +3494,7 @@
       <c r="K8" s="14" t="n"/>
       <c r="L8" s="14" t="n"/>
       <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="14" t="n"/>
@@ -3389,6 +3510,7 @@
       <c r="K9" s="14" t="n"/>
       <c r="L9" s="14" t="n"/>
       <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="n"/>
@@ -3404,6 +3526,7 @@
       <c r="K10" s="14" t="n"/>
       <c r="L10" s="14" t="n"/>
       <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="n"/>
@@ -3419,6 +3542,7 @@
       <c r="K11" s="14" t="n"/>
       <c r="L11" s="14" t="n"/>
       <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="n"/>
@@ -3434,6 +3558,7 @@
       <c r="K12" s="14" t="n"/>
       <c r="L12" s="14" t="n"/>
       <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="n"/>
@@ -3449,6 +3574,7 @@
       <c r="K13" s="14" t="n"/>
       <c r="L13" s="14" t="n"/>
       <c r="M13" s="14" t="n"/>
+      <c r="N13" s="14" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="n"/>
@@ -3464,6 +3590,7 @@
       <c r="K14" s="14" t="n"/>
       <c r="L14" s="14" t="n"/>
       <c r="M14" s="14" t="n"/>
+      <c r="N14" s="14" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n"/>
@@ -3479,6 +3606,7 @@
       <c r="K15" s="14" t="n"/>
       <c r="L15" s="14" t="n"/>
       <c r="M15" s="14" t="n"/>
+      <c r="N15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="n"/>
@@ -3494,6 +3622,7 @@
       <c r="K16" s="14" t="n"/>
       <c r="L16" s="14" t="n"/>
       <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="n"/>
@@ -3509,6 +3638,7 @@
       <c r="K17" s="14" t="n"/>
       <c r="L17" s="14" t="n"/>
       <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="n"/>
@@ -3524,6 +3654,7 @@
       <c r="K18" s="14" t="n"/>
       <c r="L18" s="14" t="n"/>
       <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="n"/>
@@ -3539,6 +3670,7 @@
       <c r="K19" s="14" t="n"/>
       <c r="L19" s="14" t="n"/>
       <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="n"/>
@@ -3554,6 +3686,7 @@
       <c r="K20" s="14" t="n"/>
       <c r="L20" s="14" t="n"/>
       <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="n"/>
@@ -3569,6 +3702,7 @@
       <c r="K21" s="14" t="n"/>
       <c r="L21" s="14" t="n"/>
       <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="n"/>
@@ -3584,6 +3718,7 @@
       <c r="K22" s="14" t="n"/>
       <c r="L22" s="14" t="n"/>
       <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="n"/>
@@ -3599,6 +3734,7 @@
       <c r="K23" s="14" t="n"/>
       <c r="L23" s="14" t="n"/>
       <c r="M23" s="14" t="n"/>
+      <c r="N23" s="14" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="n"/>
@@ -3614,6 +3750,7 @@
       <c r="K24" s="14" t="n"/>
       <c r="L24" s="14" t="n"/>
       <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="n"/>
@@ -3629,6 +3766,7 @@
       <c r="K25" s="14" t="n"/>
       <c r="L25" s="14" t="n"/>
       <c r="M25" s="14" t="n"/>
+      <c r="N25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="n"/>
@@ -3644,6 +3782,7 @@
       <c r="K26" s="14" t="n"/>
       <c r="L26" s="14" t="n"/>
       <c r="M26" s="14" t="n"/>
+      <c r="N26" s="14" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="n"/>
@@ -3659,6 +3798,7 @@
       <c r="K27" s="14" t="n"/>
       <c r="L27" s="14" t="n"/>
       <c r="M27" s="14" t="n"/>
+      <c r="N27" s="14" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="n"/>
@@ -3674,6 +3814,7 @@
       <c r="K28" s="14" t="n"/>
       <c r="L28" s="14" t="n"/>
       <c r="M28" s="14" t="n"/>
+      <c r="N28" s="14" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n"/>
@@ -3689,6 +3830,7 @@
       <c r="K29" s="14" t="n"/>
       <c r="L29" s="14" t="n"/>
       <c r="M29" s="14" t="n"/>
+      <c r="N29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="n"/>
@@ -3704,6 +3846,7 @@
       <c r="K30" s="14" t="n"/>
       <c r="L30" s="14" t="n"/>
       <c r="M30" s="14" t="n"/>
+      <c r="N30" s="14" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="n"/>
@@ -3719,6 +3862,7 @@
       <c r="K31" s="14" t="n"/>
       <c r="L31" s="14" t="n"/>
       <c r="M31" s="14" t="n"/>
+      <c r="N31" s="14" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="n"/>
@@ -3734,6 +3878,7 @@
       <c r="K32" s="14" t="n"/>
       <c r="L32" s="14" t="n"/>
       <c r="M32" s="14" t="n"/>
+      <c r="N32" s="14" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="n"/>
@@ -3749,6 +3894,7 @@
       <c r="K33" s="14" t="n"/>
       <c r="L33" s="14" t="n"/>
       <c r="M33" s="14" t="n"/>
+      <c r="N33" s="14" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="n"/>
@@ -3764,6 +3910,7 @@
       <c r="K34" s="14" t="n"/>
       <c r="L34" s="14" t="n"/>
       <c r="M34" s="14" t="n"/>
+      <c r="N34" s="14" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="n"/>
@@ -3779,6 +3926,7 @@
       <c r="K35" s="14" t="n"/>
       <c r="L35" s="14" t="n"/>
       <c r="M35" s="14" t="n"/>
+      <c r="N35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="n"/>
@@ -3794,6 +3942,7 @@
       <c r="K36" s="14" t="n"/>
       <c r="L36" s="14" t="n"/>
       <c r="M36" s="14" t="n"/>
+      <c r="N36" s="14" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="n"/>
@@ -3809,6 +3958,7 @@
       <c r="K37" s="14" t="n"/>
       <c r="L37" s="14" t="n"/>
       <c r="M37" s="14" t="n"/>
+      <c r="N37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="n"/>
@@ -3824,6 +3974,7 @@
       <c r="K38" s="14" t="n"/>
       <c r="L38" s="14" t="n"/>
       <c r="M38" s="14" t="n"/>
+      <c r="N38" s="14" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="n"/>
@@ -3839,6 +3990,7 @@
       <c r="K39" s="14" t="n"/>
       <c r="L39" s="14" t="n"/>
       <c r="M39" s="14" t="n"/>
+      <c r="N39" s="14" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n"/>
@@ -3854,6 +4006,7 @@
       <c r="K40" s="14" t="n"/>
       <c r="L40" s="14" t="n"/>
       <c r="M40" s="14" t="n"/>
+      <c r="N40" s="14" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n"/>
@@ -3869,6 +4022,7 @@
       <c r="K41" s="14" t="n"/>
       <c r="L41" s="14" t="n"/>
       <c r="M41" s="14" t="n"/>
+      <c r="N41" s="14" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n"/>
@@ -3884,6 +4038,7 @@
       <c r="K42" s="14" t="n"/>
       <c r="L42" s="14" t="n"/>
       <c r="M42" s="14" t="n"/>
+      <c r="N42" s="14" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n"/>
@@ -3899,6 +4054,7 @@
       <c r="K43" s="14" t="n"/>
       <c r="L43" s="14" t="n"/>
       <c r="M43" s="14" t="n"/>
+      <c r="N43" s="14" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="14" t="n"/>
@@ -3914,6 +4070,7 @@
       <c r="K44" s="14" t="n"/>
       <c r="L44" s="14" t="n"/>
       <c r="M44" s="14" t="n"/>
+      <c r="N44" s="14" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="14" t="n"/>
@@ -3929,6 +4086,7 @@
       <c r="K45" s="14" t="n"/>
       <c r="L45" s="14" t="n"/>
       <c r="M45" s="14" t="n"/>
+      <c r="N45" s="14" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="14" t="n"/>
@@ -3944,6 +4102,7 @@
       <c r="K46" s="14" t="n"/>
       <c r="L46" s="14" t="n"/>
       <c r="M46" s="14" t="n"/>
+      <c r="N46" s="14" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="14" t="n"/>
@@ -3959,6 +4118,7 @@
       <c r="K47" s="14" t="n"/>
       <c r="L47" s="14" t="n"/>
       <c r="M47" s="14" t="n"/>
+      <c r="N47" s="14" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="n"/>
@@ -3974,6 +4134,7 @@
       <c r="K48" s="14" t="n"/>
       <c r="L48" s="14" t="n"/>
       <c r="M48" s="14" t="n"/>
+      <c r="N48" s="14" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="14" t="n"/>
@@ -3989,6 +4150,7 @@
       <c r="K49" s="14" t="n"/>
       <c r="L49" s="14" t="n"/>
       <c r="M49" s="14" t="n"/>
+      <c r="N49" s="14" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="14" t="n"/>
@@ -4004,6 +4166,7 @@
       <c r="K50" s="14" t="n"/>
       <c r="L50" s="14" t="n"/>
       <c r="M50" s="14" t="n"/>
+      <c r="N50" s="14" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="14" t="n"/>
@@ -4019,6 +4182,7 @@
       <c r="K51" s="14" t="n"/>
       <c r="L51" s="14" t="n"/>
       <c r="M51" s="14" t="n"/>
+      <c r="N51" s="14" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="14" t="n"/>
@@ -4034,6 +4198,7 @@
       <c r="K52" s="14" t="n"/>
       <c r="L52" s="14" t="n"/>
       <c r="M52" s="14" t="n"/>
+      <c r="N52" s="14" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="14" t="n"/>
@@ -4049,6 +4214,7 @@
       <c r="K53" s="14" t="n"/>
       <c r="L53" s="14" t="n"/>
       <c r="M53" s="14" t="n"/>
+      <c r="N53" s="14" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="n"/>
@@ -4064,6 +4230,7 @@
       <c r="K54" s="14" t="n"/>
       <c r="L54" s="14" t="n"/>
       <c r="M54" s="14" t="n"/>
+      <c r="N54" s="14" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n"/>
@@ -4079,6 +4246,7 @@
       <c r="K55" s="14" t="n"/>
       <c r="L55" s="14" t="n"/>
       <c r="M55" s="14" t="n"/>
+      <c r="N55" s="14" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="14" t="n"/>
@@ -4094,6 +4262,7 @@
       <c r="K56" s="14" t="n"/>
       <c r="L56" s="14" t="n"/>
       <c r="M56" s="14" t="n"/>
+      <c r="N56" s="14" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="14" t="n"/>
@@ -4109,6 +4278,7 @@
       <c r="K57" s="14" t="n"/>
       <c r="L57" s="14" t="n"/>
       <c r="M57" s="14" t="n"/>
+      <c r="N57" s="14" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n"/>
@@ -4124,6 +4294,7 @@
       <c r="K58" s="14" t="n"/>
       <c r="L58" s="14" t="n"/>
       <c r="M58" s="14" t="n"/>
+      <c r="N58" s="14" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n"/>
@@ -4139,6 +4310,7 @@
       <c r="K59" s="14" t="n"/>
       <c r="L59" s="14" t="n"/>
       <c r="M59" s="14" t="n"/>
+      <c r="N59" s="14" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="14" t="n"/>
@@ -4154,6 +4326,7 @@
       <c r="K60" s="14" t="n"/>
       <c r="L60" s="14" t="n"/>
       <c r="M60" s="14" t="n"/>
+      <c r="N60" s="14" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="14" t="n"/>
@@ -4169,6 +4342,7 @@
       <c r="K61" s="14" t="n"/>
       <c r="L61" s="14" t="n"/>
       <c r="M61" s="14" t="n"/>
+      <c r="N61" s="14" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="14" t="n"/>
@@ -4184,6 +4358,7 @@
       <c r="K62" s="14" t="n"/>
       <c r="L62" s="14" t="n"/>
       <c r="M62" s="14" t="n"/>
+      <c r="N62" s="14" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="14" t="n"/>
@@ -4199,6 +4374,7 @@
       <c r="K63" s="14" t="n"/>
       <c r="L63" s="14" t="n"/>
       <c r="M63" s="14" t="n"/>
+      <c r="N63" s="14" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="14" t="n"/>
@@ -4214,6 +4390,7 @@
       <c r="K64" s="14" t="n"/>
       <c r="L64" s="14" t="n"/>
       <c r="M64" s="14" t="n"/>
+      <c r="N64" s="14" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="14" t="n"/>
@@ -4229,6 +4406,7 @@
       <c r="K65" s="14" t="n"/>
       <c r="L65" s="14" t="n"/>
       <c r="M65" s="14" t="n"/>
+      <c r="N65" s="14" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="14" t="n"/>
@@ -4244,6 +4422,7 @@
       <c r="K66" s="14" t="n"/>
       <c r="L66" s="14" t="n"/>
       <c r="M66" s="14" t="n"/>
+      <c r="N66" s="14" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="14" t="n"/>
@@ -4259,6 +4438,7 @@
       <c r="K67" s="14" t="n"/>
       <c r="L67" s="14" t="n"/>
       <c r="M67" s="14" t="n"/>
+      <c r="N67" s="14" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="14" t="n"/>
@@ -4274,6 +4454,7 @@
       <c r="K68" s="14" t="n"/>
       <c r="L68" s="14" t="n"/>
       <c r="M68" s="14" t="n"/>
+      <c r="N68" s="14" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="14" t="n"/>
@@ -4289,6 +4470,7 @@
       <c r="K69" s="14" t="n"/>
       <c r="L69" s="14" t="n"/>
       <c r="M69" s="14" t="n"/>
+      <c r="N69" s="14" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="14" t="n"/>
@@ -4304,6 +4486,7 @@
       <c r="K70" s="14" t="n"/>
       <c r="L70" s="14" t="n"/>
       <c r="M70" s="14" t="n"/>
+      <c r="N70" s="14" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="14" t="n"/>
@@ -4319,6 +4502,7 @@
       <c r="K71" s="14" t="n"/>
       <c r="L71" s="14" t="n"/>
       <c r="M71" s="14" t="n"/>
+      <c r="N71" s="14" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="14" t="n"/>
@@ -4334,6 +4518,7 @@
       <c r="K72" s="14" t="n"/>
       <c r="L72" s="14" t="n"/>
       <c r="M72" s="14" t="n"/>
+      <c r="N72" s="14" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="14" t="n"/>
@@ -4349,6 +4534,7 @@
       <c r="K73" s="14" t="n"/>
       <c r="L73" s="14" t="n"/>
       <c r="M73" s="14" t="n"/>
+      <c r="N73" s="14" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="14" t="n"/>
@@ -4364,6 +4550,7 @@
       <c r="K74" s="14" t="n"/>
       <c r="L74" s="14" t="n"/>
       <c r="M74" s="14" t="n"/>
+      <c r="N74" s="14" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n"/>
@@ -4379,6 +4566,7 @@
       <c r="K75" s="14" t="n"/>
       <c r="L75" s="14" t="n"/>
       <c r="M75" s="14" t="n"/>
+      <c r="N75" s="14" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="14" t="n"/>
@@ -4394,6 +4582,7 @@
       <c r="K76" s="14" t="n"/>
       <c r="L76" s="14" t="n"/>
       <c r="M76" s="14" t="n"/>
+      <c r="N76" s="14" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n"/>
@@ -4409,6 +4598,7 @@
       <c r="K77" s="14" t="n"/>
       <c r="L77" s="14" t="n"/>
       <c r="M77" s="14" t="n"/>
+      <c r="N77" s="14" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="14" t="n"/>
@@ -4424,6 +4614,7 @@
       <c r="K78" s="14" t="n"/>
       <c r="L78" s="14" t="n"/>
       <c r="M78" s="14" t="n"/>
+      <c r="N78" s="14" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="14" t="n"/>
@@ -4439,6 +4630,7 @@
       <c r="K79" s="14" t="n"/>
       <c r="L79" s="14" t="n"/>
       <c r="M79" s="14" t="n"/>
+      <c r="N79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="14" t="n"/>
@@ -4454,6 +4646,7 @@
       <c r="K80" s="14" t="n"/>
       <c r="L80" s="14" t="n"/>
       <c r="M80" s="14" t="n"/>
+      <c r="N80" s="14" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="14" t="n"/>
@@ -4469,6 +4662,7 @@
       <c r="K81" s="14" t="n"/>
       <c r="L81" s="14" t="n"/>
       <c r="M81" s="14" t="n"/>
+      <c r="N81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="n"/>
@@ -4484,6 +4678,7 @@
       <c r="K82" s="14" t="n"/>
       <c r="L82" s="14" t="n"/>
       <c r="M82" s="14" t="n"/>
+      <c r="N82" s="14" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="14" t="n"/>
@@ -4499,6 +4694,7 @@
       <c r="K83" s="14" t="n"/>
       <c r="L83" s="14" t="n"/>
       <c r="M83" s="14" t="n"/>
+      <c r="N83" s="14" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n"/>
@@ -4514,6 +4710,7 @@
       <c r="K84" s="14" t="n"/>
       <c r="L84" s="14" t="n"/>
       <c r="M84" s="14" t="n"/>
+      <c r="N84" s="14" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="14" t="n"/>
@@ -4529,6 +4726,7 @@
       <c r="K85" s="14" t="n"/>
       <c r="L85" s="14" t="n"/>
       <c r="M85" s="14" t="n"/>
+      <c r="N85" s="14" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="14" t="n"/>
@@ -4544,6 +4742,7 @@
       <c r="K86" s="14" t="n"/>
       <c r="L86" s="14" t="n"/>
       <c r="M86" s="14" t="n"/>
+      <c r="N86" s="14" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="14" t="n"/>
@@ -4559,6 +4758,7 @@
       <c r="K87" s="14" t="n"/>
       <c r="L87" s="14" t="n"/>
       <c r="M87" s="14" t="n"/>
+      <c r="N87" s="14" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n"/>
@@ -4574,6 +4774,7 @@
       <c r="K88" s="14" t="n"/>
       <c r="L88" s="14" t="n"/>
       <c r="M88" s="14" t="n"/>
+      <c r="N88" s="14" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n"/>
@@ -4589,6 +4790,7 @@
       <c r="K89" s="14" t="n"/>
       <c r="L89" s="14" t="n"/>
       <c r="M89" s="14" t="n"/>
+      <c r="N89" s="14" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="14" t="n"/>
@@ -4604,6 +4806,7 @@
       <c r="K90" s="14" t="n"/>
       <c r="L90" s="14" t="n"/>
       <c r="M90" s="14" t="n"/>
+      <c r="N90" s="14" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="14" t="n"/>
@@ -4619,6 +4822,7 @@
       <c r="K91" s="14" t="n"/>
       <c r="L91" s="14" t="n"/>
       <c r="M91" s="14" t="n"/>
+      <c r="N91" s="14" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="14" t="n"/>
@@ -4634,6 +4838,7 @@
       <c r="K92" s="14" t="n"/>
       <c r="L92" s="14" t="n"/>
       <c r="M92" s="14" t="n"/>
+      <c r="N92" s="14" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="14" t="n"/>
@@ -4649,6 +4854,7 @@
       <c r="K93" s="14" t="n"/>
       <c r="L93" s="14" t="n"/>
       <c r="M93" s="14" t="n"/>
+      <c r="N93" s="14" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="14" t="n"/>
@@ -4664,6 +4870,7 @@
       <c r="K94" s="14" t="n"/>
       <c r="L94" s="14" t="n"/>
       <c r="M94" s="14" t="n"/>
+      <c r="N94" s="14" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="14" t="n"/>
@@ -4679,6 +4886,7 @@
       <c r="K95" s="14" t="n"/>
       <c r="L95" s="14" t="n"/>
       <c r="M95" s="14" t="n"/>
+      <c r="N95" s="14" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="14" t="n"/>
@@ -4694,6 +4902,7 @@
       <c r="K96" s="14" t="n"/>
       <c r="L96" s="14" t="n"/>
       <c r="M96" s="14" t="n"/>
+      <c r="N96" s="14" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n"/>
@@ -4709,6 +4918,7 @@
       <c r="K97" s="14" t="n"/>
       <c r="L97" s="14" t="n"/>
       <c r="M97" s="14" t="n"/>
+      <c r="N97" s="14" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n"/>
@@ -4724,6 +4934,7 @@
       <c r="K98" s="14" t="n"/>
       <c r="L98" s="14" t="n"/>
       <c r="M98" s="14" t="n"/>
+      <c r="N98" s="14" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="14" t="n"/>
@@ -4739,6 +4950,7 @@
       <c r="K99" s="14" t="n"/>
       <c r="L99" s="14" t="n"/>
       <c r="M99" s="14" t="n"/>
+      <c r="N99" s="14" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="14" t="n"/>
@@ -4754,6 +4966,7 @@
       <c r="K100" s="14" t="n"/>
       <c r="L100" s="14" t="n"/>
       <c r="M100" s="14" t="n"/>
+      <c r="N100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="14" t="n"/>
@@ -4769,6 +4982,7 @@
       <c r="K101" s="14" t="n"/>
       <c r="L101" s="14" t="n"/>
       <c r="M101" s="14" t="n"/>
+      <c r="N101" s="14" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="14" t="n"/>
@@ -4784,6 +4998,7 @@
       <c r="K102" s="14" t="n"/>
       <c r="L102" s="14" t="n"/>
       <c r="M102" s="14" t="n"/>
+      <c r="N102" s="14" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="14" t="n"/>
@@ -4799,6 +5014,7 @@
       <c r="K103" s="14" t="n"/>
       <c r="L103" s="14" t="n"/>
       <c r="M103" s="14" t="n"/>
+      <c r="N103" s="14" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="14" t="n"/>
@@ -4814,6 +5030,7 @@
       <c r="K104" s="14" t="n"/>
       <c r="L104" s="14" t="n"/>
       <c r="M104" s="14" t="n"/>
+      <c r="N104" s="14" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n"/>
@@ -4829,6 +5046,7 @@
       <c r="K105" s="14" t="n"/>
       <c r="L105" s="14" t="n"/>
       <c r="M105" s="14" t="n"/>
+      <c r="N105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="14" t="n"/>
@@ -4844,6 +5062,7 @@
       <c r="K106" s="14" t="n"/>
       <c r="L106" s="14" t="n"/>
       <c r="M106" s="14" t="n"/>
+      <c r="N106" s="14" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="14" t="n"/>
@@ -4859,6 +5078,7 @@
       <c r="K107" s="14" t="n"/>
       <c r="L107" s="14" t="n"/>
       <c r="M107" s="14" t="n"/>
+      <c r="N107" s="14" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="14" t="n"/>
@@ -4874,6 +5094,7 @@
       <c r="K108" s="14" t="n"/>
       <c r="L108" s="14" t="n"/>
       <c r="M108" s="14" t="n"/>
+      <c r="N108" s="14" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="14" t="n"/>
@@ -4889,6 +5110,7 @@
       <c r="K109" s="14" t="n"/>
       <c r="L109" s="14" t="n"/>
       <c r="M109" s="14" t="n"/>
+      <c r="N109" s="14" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="14" t="n"/>
@@ -4904,6 +5126,7 @@
       <c r="K110" s="14" t="n"/>
       <c r="L110" s="14" t="n"/>
       <c r="M110" s="14" t="n"/>
+      <c r="N110" s="14" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="14" t="n"/>
@@ -4919,6 +5142,7 @@
       <c r="K111" s="14" t="n"/>
       <c r="L111" s="14" t="n"/>
       <c r="M111" s="14" t="n"/>
+      <c r="N111" s="14" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="14" t="n"/>
@@ -4934,6 +5158,7 @@
       <c r="K112" s="14" t="n"/>
       <c r="L112" s="14" t="n"/>
       <c r="M112" s="14" t="n"/>
+      <c r="N112" s="14" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="14" t="n"/>
@@ -4949,6 +5174,7 @@
       <c r="K113" s="14" t="n"/>
       <c r="L113" s="14" t="n"/>
       <c r="M113" s="14" t="n"/>
+      <c r="N113" s="14" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="14" t="n"/>
@@ -4964,6 +5190,7 @@
       <c r="K114" s="14" t="n"/>
       <c r="L114" s="14" t="n"/>
       <c r="M114" s="14" t="n"/>
+      <c r="N114" s="14" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="14" t="n"/>
@@ -4979,6 +5206,7 @@
       <c r="K115" s="14" t="n"/>
       <c r="L115" s="14" t="n"/>
       <c r="M115" s="14" t="n"/>
+      <c r="N115" s="14" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="14" t="n"/>
@@ -4994,6 +5222,7 @@
       <c r="K116" s="14" t="n"/>
       <c r="L116" s="14" t="n"/>
       <c r="M116" s="14" t="n"/>
+      <c r="N116" s="14" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="14" t="n"/>
@@ -5009,6 +5238,7 @@
       <c r="K117" s="14" t="n"/>
       <c r="L117" s="14" t="n"/>
       <c r="M117" s="14" t="n"/>
+      <c r="N117" s="14" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="14" t="n"/>
@@ -5024,6 +5254,7 @@
       <c r="K118" s="14" t="n"/>
       <c r="L118" s="14" t="n"/>
       <c r="M118" s="14" t="n"/>
+      <c r="N118" s="14" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="14" t="n"/>
@@ -5039,6 +5270,7 @@
       <c r="K119" s="14" t="n"/>
       <c r="L119" s="14" t="n"/>
       <c r="M119" s="14" t="n"/>
+      <c r="N119" s="14" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="14" t="n"/>
@@ -5054,6 +5286,7 @@
       <c r="K120" s="14" t="n"/>
       <c r="L120" s="14" t="n"/>
       <c r="M120" s="14" t="n"/>
+      <c r="N120" s="14" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="14" t="n"/>
@@ -5069,6 +5302,7 @@
       <c r="K121" s="14" t="n"/>
       <c r="L121" s="14" t="n"/>
       <c r="M121" s="14" t="n"/>
+      <c r="N121" s="14" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="14" t="n"/>
@@ -5084,6 +5318,7 @@
       <c r="K122" s="14" t="n"/>
       <c r="L122" s="14" t="n"/>
       <c r="M122" s="14" t="n"/>
+      <c r="N122" s="14" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="14" t="n"/>
@@ -5099,6 +5334,7 @@
       <c r="K123" s="14" t="n"/>
       <c r="L123" s="14" t="n"/>
       <c r="M123" s="14" t="n"/>
+      <c r="N123" s="14" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="14" t="n"/>
@@ -5114,6 +5350,7 @@
       <c r="K124" s="14" t="n"/>
       <c r="L124" s="14" t="n"/>
       <c r="M124" s="14" t="n"/>
+      <c r="N124" s="14" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="14" t="n"/>
@@ -5129,6 +5366,7 @@
       <c r="K125" s="14" t="n"/>
       <c r="L125" s="14" t="n"/>
       <c r="M125" s="14" t="n"/>
+      <c r="N125" s="14" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="14" t="n"/>
@@ -5144,6 +5382,7 @@
       <c r="K126" s="14" t="n"/>
       <c r="L126" s="14" t="n"/>
       <c r="M126" s="14" t="n"/>
+      <c r="N126" s="14" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="14" t="n"/>
@@ -5159,6 +5398,7 @@
       <c r="K127" s="14" t="n"/>
       <c r="L127" s="14" t="n"/>
       <c r="M127" s="14" t="n"/>
+      <c r="N127" s="14" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="14" t="n"/>
@@ -5174,6 +5414,7 @@
       <c r="K128" s="14" t="n"/>
       <c r="L128" s="14" t="n"/>
       <c r="M128" s="14" t="n"/>
+      <c r="N128" s="14" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="14" t="n"/>
@@ -5189,6 +5430,7 @@
       <c r="K129" s="14" t="n"/>
       <c r="L129" s="14" t="n"/>
       <c r="M129" s="14" t="n"/>
+      <c r="N129" s="14" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="14" t="n"/>
@@ -5204,6 +5446,7 @@
       <c r="K130" s="14" t="n"/>
       <c r="L130" s="14" t="n"/>
       <c r="M130" s="14" t="n"/>
+      <c r="N130" s="14" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="14" t="n"/>
@@ -5219,6 +5462,7 @@
       <c r="K131" s="14" t="n"/>
       <c r="L131" s="14" t="n"/>
       <c r="M131" s="14" t="n"/>
+      <c r="N131" s="14" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="14" t="n"/>
@@ -5234,6 +5478,7 @@
       <c r="K132" s="14" t="n"/>
       <c r="L132" s="14" t="n"/>
       <c r="M132" s="14" t="n"/>
+      <c r="N132" s="14" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="14" t="n"/>
@@ -5249,6 +5494,7 @@
       <c r="K133" s="14" t="n"/>
       <c r="L133" s="14" t="n"/>
       <c r="M133" s="14" t="n"/>
+      <c r="N133" s="14" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="14" t="n"/>
@@ -5264,6 +5510,7 @@
       <c r="K134" s="14" t="n"/>
       <c r="L134" s="14" t="n"/>
       <c r="M134" s="14" t="n"/>
+      <c r="N134" s="14" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="14" t="n"/>
@@ -5279,6 +5526,7 @@
       <c r="K135" s="14" t="n"/>
       <c r="L135" s="14" t="n"/>
       <c r="M135" s="14" t="n"/>
+      <c r="N135" s="14" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="14" t="n"/>
@@ -5294,6 +5542,7 @@
       <c r="K136" s="14" t="n"/>
       <c r="L136" s="14" t="n"/>
       <c r="M136" s="14" t="n"/>
+      <c r="N136" s="14" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="14" t="n"/>
@@ -5309,6 +5558,7 @@
       <c r="K137" s="14" t="n"/>
       <c r="L137" s="14" t="n"/>
       <c r="M137" s="14" t="n"/>
+      <c r="N137" s="14" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="14" t="n"/>
@@ -5324,6 +5574,7 @@
       <c r="K138" s="14" t="n"/>
       <c r="L138" s="14" t="n"/>
       <c r="M138" s="14" t="n"/>
+      <c r="N138" s="14" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="14" t="n"/>
@@ -5339,6 +5590,7 @@
       <c r="K139" s="14" t="n"/>
       <c r="L139" s="14" t="n"/>
       <c r="M139" s="14" t="n"/>
+      <c r="N139" s="14" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="14" t="n"/>
@@ -5354,6 +5606,7 @@
       <c r="K140" s="14" t="n"/>
       <c r="L140" s="14" t="n"/>
       <c r="M140" s="14" t="n"/>
+      <c r="N140" s="14" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="14" t="n"/>
@@ -5369,6 +5622,7 @@
       <c r="K141" s="14" t="n"/>
       <c r="L141" s="14" t="n"/>
       <c r="M141" s="14" t="n"/>
+      <c r="N141" s="14" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="14" t="n"/>
@@ -5384,6 +5638,7 @@
       <c r="K142" s="14" t="n"/>
       <c r="L142" s="14" t="n"/>
       <c r="M142" s="14" t="n"/>
+      <c r="N142" s="14" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="14" t="n"/>
@@ -5399,6 +5654,7 @@
       <c r="K143" s="14" t="n"/>
       <c r="L143" s="14" t="n"/>
       <c r="M143" s="14" t="n"/>
+      <c r="N143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="14" t="n"/>
@@ -5414,6 +5670,7 @@
       <c r="K144" s="14" t="n"/>
       <c r="L144" s="14" t="n"/>
       <c r="M144" s="14" t="n"/>
+      <c r="N144" s="14" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="14" t="n"/>
@@ -5429,6 +5686,7 @@
       <c r="K145" s="14" t="n"/>
       <c r="L145" s="14" t="n"/>
       <c r="M145" s="14" t="n"/>
+      <c r="N145" s="14" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="14" t="n"/>
@@ -5444,6 +5702,7 @@
       <c r="K146" s="14" t="n"/>
       <c r="L146" s="14" t="n"/>
       <c r="M146" s="14" t="n"/>
+      <c r="N146" s="14" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="14" t="n"/>
@@ -5459,6 +5718,7 @@
       <c r="K147" s="14" t="n"/>
       <c r="L147" s="14" t="n"/>
       <c r="M147" s="14" t="n"/>
+      <c r="N147" s="14" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="14" t="n"/>
@@ -5474,6 +5734,7 @@
       <c r="K148" s="14" t="n"/>
       <c r="L148" s="14" t="n"/>
       <c r="M148" s="14" t="n"/>
+      <c r="N148" s="14" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="14" t="n"/>
@@ -5489,6 +5750,7 @@
       <c r="K149" s="14" t="n"/>
       <c r="L149" s="14" t="n"/>
       <c r="M149" s="14" t="n"/>
+      <c r="N149" s="14" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="14" t="n"/>
@@ -5504,6 +5766,7 @@
       <c r="K150" s="14" t="n"/>
       <c r="L150" s="14" t="n"/>
       <c r="M150" s="14" t="n"/>
+      <c r="N150" s="14" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="14" t="n"/>
@@ -5519,6 +5782,7 @@
       <c r="K151" s="14" t="n"/>
       <c r="L151" s="14" t="n"/>
       <c r="M151" s="14" t="n"/>
+      <c r="N151" s="14" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="14" t="n"/>
@@ -5534,6 +5798,7 @@
       <c r="K152" s="14" t="n"/>
       <c r="L152" s="14" t="n"/>
       <c r="M152" s="14" t="n"/>
+      <c r="N152" s="14" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="14" t="n"/>
@@ -5549,6 +5814,7 @@
       <c r="K153" s="14" t="n"/>
       <c r="L153" s="14" t="n"/>
       <c r="M153" s="14" t="n"/>
+      <c r="N153" s="14" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="14" t="n"/>
@@ -5564,6 +5830,7 @@
       <c r="K154" s="14" t="n"/>
       <c r="L154" s="14" t="n"/>
       <c r="M154" s="14" t="n"/>
+      <c r="N154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="14" t="n"/>
@@ -5579,6 +5846,7 @@
       <c r="K155" s="14" t="n"/>
       <c r="L155" s="14" t="n"/>
       <c r="M155" s="14" t="n"/>
+      <c r="N155" s="14" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="14" t="n"/>
@@ -5594,6 +5862,7 @@
       <c r="K156" s="14" t="n"/>
       <c r="L156" s="14" t="n"/>
       <c r="M156" s="14" t="n"/>
+      <c r="N156" s="14" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="14" t="n"/>
@@ -5609,6 +5878,7 @@
       <c r="K157" s="14" t="n"/>
       <c r="L157" s="14" t="n"/>
       <c r="M157" s="14" t="n"/>
+      <c r="N157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="14" t="n"/>
@@ -5624,6 +5894,7 @@
       <c r="K158" s="14" t="n"/>
       <c r="L158" s="14" t="n"/>
       <c r="M158" s="14" t="n"/>
+      <c r="N158" s="14" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="n"/>
@@ -5639,6 +5910,7 @@
       <c r="K159" s="14" t="n"/>
       <c r="L159" s="14" t="n"/>
       <c r="M159" s="14" t="n"/>
+      <c r="N159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="14" t="n"/>
@@ -5654,6 +5926,7 @@
       <c r="K160" s="14" t="n"/>
       <c r="L160" s="14" t="n"/>
       <c r="M160" s="14" t="n"/>
+      <c r="N160" s="14" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="14" t="n"/>
@@ -5669,6 +5942,7 @@
       <c r="K161" s="14" t="n"/>
       <c r="L161" s="14" t="n"/>
       <c r="M161" s="14" t="n"/>
+      <c r="N161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="14" t="n"/>
@@ -5684,6 +5958,7 @@
       <c r="K162" s="14" t="n"/>
       <c r="L162" s="14" t="n"/>
       <c r="M162" s="14" t="n"/>
+      <c r="N162" s="14" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="14" t="n"/>
@@ -5699,6 +5974,7 @@
       <c r="K163" s="14" t="n"/>
       <c r="L163" s="14" t="n"/>
       <c r="M163" s="14" t="n"/>
+      <c r="N163" s="14" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="14" t="n"/>
@@ -5714,6 +5990,7 @@
       <c r="K164" s="14" t="n"/>
       <c r="L164" s="14" t="n"/>
       <c r="M164" s="14" t="n"/>
+      <c r="N164" s="14" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="14" t="n"/>
@@ -5729,6 +6006,7 @@
       <c r="K165" s="14" t="n"/>
       <c r="L165" s="14" t="n"/>
       <c r="M165" s="14" t="n"/>
+      <c r="N165" s="14" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="14" t="n"/>
@@ -5744,6 +6022,7 @@
       <c r="K166" s="14" t="n"/>
       <c r="L166" s="14" t="n"/>
       <c r="M166" s="14" t="n"/>
+      <c r="N166" s="14" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="14" t="n"/>
@@ -5759,6 +6038,7 @@
       <c r="K167" s="14" t="n"/>
       <c r="L167" s="14" t="n"/>
       <c r="M167" s="14" t="n"/>
+      <c r="N167" s="14" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="14" t="n"/>
@@ -5774,6 +6054,7 @@
       <c r="K168" s="14" t="n"/>
       <c r="L168" s="14" t="n"/>
       <c r="M168" s="14" t="n"/>
+      <c r="N168" s="14" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="14" t="n"/>
@@ -5789,6 +6070,7 @@
       <c r="K169" s="14" t="n"/>
       <c r="L169" s="14" t="n"/>
       <c r="M169" s="14" t="n"/>
+      <c r="N169" s="14" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="14" t="n"/>
@@ -5804,6 +6086,7 @@
       <c r="K170" s="14" t="n"/>
       <c r="L170" s="14" t="n"/>
       <c r="M170" s="14" t="n"/>
+      <c r="N170" s="14" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="14" t="n"/>
@@ -5819,6 +6102,7 @@
       <c r="K171" s="14" t="n"/>
       <c r="L171" s="14" t="n"/>
       <c r="M171" s="14" t="n"/>
+      <c r="N171" s="14" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="14" t="n"/>
@@ -5834,6 +6118,7 @@
       <c r="K172" s="14" t="n"/>
       <c r="L172" s="14" t="n"/>
       <c r="M172" s="14" t="n"/>
+      <c r="N172" s="14" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="14" t="n"/>
@@ -5849,6 +6134,7 @@
       <c r="K173" s="14" t="n"/>
       <c r="L173" s="14" t="n"/>
       <c r="M173" s="14" t="n"/>
+      <c r="N173" s="14" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="14" t="n"/>
@@ -5864,6 +6150,7 @@
       <c r="K174" s="14" t="n"/>
       <c r="L174" s="14" t="n"/>
       <c r="M174" s="14" t="n"/>
+      <c r="N174" s="14" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="14" t="n"/>
@@ -5879,6 +6166,7 @@
       <c r="K175" s="14" t="n"/>
       <c r="L175" s="14" t="n"/>
       <c r="M175" s="14" t="n"/>
+      <c r="N175" s="14" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="14" t="n"/>
@@ -5894,6 +6182,7 @@
       <c r="K176" s="14" t="n"/>
       <c r="L176" s="14" t="n"/>
       <c r="M176" s="14" t="n"/>
+      <c r="N176" s="14" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="14" t="n"/>
@@ -5909,6 +6198,7 @@
       <c r="K177" s="14" t="n"/>
       <c r="L177" s="14" t="n"/>
       <c r="M177" s="14" t="n"/>
+      <c r="N177" s="14" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="14" t="n"/>
@@ -5924,6 +6214,7 @@
       <c r="K178" s="14" t="n"/>
       <c r="L178" s="14" t="n"/>
       <c r="M178" s="14" t="n"/>
+      <c r="N178" s="14" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="14" t="n"/>
@@ -5939,6 +6230,7 @@
       <c r="K179" s="14" t="n"/>
       <c r="L179" s="14" t="n"/>
       <c r="M179" s="14" t="n"/>
+      <c r="N179" s="14" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="14" t="n"/>
@@ -5954,6 +6246,7 @@
       <c r="K180" s="14" t="n"/>
       <c r="L180" s="14" t="n"/>
       <c r="M180" s="14" t="n"/>
+      <c r="N180" s="14" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="14" t="n"/>
@@ -5969,6 +6262,7 @@
       <c r="K181" s="14" t="n"/>
       <c r="L181" s="14" t="n"/>
       <c r="M181" s="14" t="n"/>
+      <c r="N181" s="14" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="14" t="n"/>
@@ -5984,6 +6278,7 @@
       <c r="K182" s="14" t="n"/>
       <c r="L182" s="14" t="n"/>
       <c r="M182" s="14" t="n"/>
+      <c r="N182" s="14" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="14" t="n"/>
@@ -5999,6 +6294,7 @@
       <c r="K183" s="14" t="n"/>
       <c r="L183" s="14" t="n"/>
       <c r="M183" s="14" t="n"/>
+      <c r="N183" s="14" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="14" t="n"/>
@@ -6014,6 +6310,7 @@
       <c r="K184" s="14" t="n"/>
       <c r="L184" s="14" t="n"/>
       <c r="M184" s="14" t="n"/>
+      <c r="N184" s="14" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="14" t="n"/>
@@ -6029,6 +6326,7 @@
       <c r="K185" s="14" t="n"/>
       <c r="L185" s="14" t="n"/>
       <c r="M185" s="14" t="n"/>
+      <c r="N185" s="14" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="14" t="n"/>
@@ -6044,6 +6342,7 @@
       <c r="K186" s="14" t="n"/>
       <c r="L186" s="14" t="n"/>
       <c r="M186" s="14" t="n"/>
+      <c r="N186" s="14" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="14" t="n"/>
@@ -6059,6 +6358,7 @@
       <c r="K187" s="14" t="n"/>
       <c r="L187" s="14" t="n"/>
       <c r="M187" s="14" t="n"/>
+      <c r="N187" s="14" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="14" t="n"/>
@@ -6074,6 +6374,7 @@
       <c r="K188" s="14" t="n"/>
       <c r="L188" s="14" t="n"/>
       <c r="M188" s="14" t="n"/>
+      <c r="N188" s="14" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="14" t="n"/>
@@ -6089,6 +6390,7 @@
       <c r="K189" s="14" t="n"/>
       <c r="L189" s="14" t="n"/>
       <c r="M189" s="14" t="n"/>
+      <c r="N189" s="14" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="14" t="n"/>
@@ -6104,6 +6406,7 @@
       <c r="K190" s="14" t="n"/>
       <c r="L190" s="14" t="n"/>
       <c r="M190" s="14" t="n"/>
+      <c r="N190" s="14" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="14" t="n"/>
@@ -6119,6 +6422,7 @@
       <c r="K191" s="14" t="n"/>
       <c r="L191" s="14" t="n"/>
       <c r="M191" s="14" t="n"/>
+      <c r="N191" s="14" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="14" t="n"/>
@@ -6134,6 +6438,7 @@
       <c r="K192" s="14" t="n"/>
       <c r="L192" s="14" t="n"/>
       <c r="M192" s="14" t="n"/>
+      <c r="N192" s="14" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="14" t="n"/>
@@ -6149,6 +6454,7 @@
       <c r="K193" s="14" t="n"/>
       <c r="L193" s="14" t="n"/>
       <c r="M193" s="14" t="n"/>
+      <c r="N193" s="14" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="14" t="n"/>
@@ -6164,6 +6470,7 @@
       <c r="K194" s="14" t="n"/>
       <c r="L194" s="14" t="n"/>
       <c r="M194" s="14" t="n"/>
+      <c r="N194" s="14" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="14" t="n"/>
@@ -6179,6 +6486,7 @@
       <c r="K195" s="14" t="n"/>
       <c r="L195" s="14" t="n"/>
       <c r="M195" s="14" t="n"/>
+      <c r="N195" s="14" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="14" t="n"/>
@@ -6194,6 +6502,7 @@
       <c r="K196" s="14" t="n"/>
       <c r="L196" s="14" t="n"/>
       <c r="M196" s="14" t="n"/>
+      <c r="N196" s="14" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="14" t="n"/>
@@ -6209,6 +6518,7 @@
       <c r="K197" s="14" t="n"/>
       <c r="L197" s="14" t="n"/>
       <c r="M197" s="14" t="n"/>
+      <c r="N197" s="14" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="14" t="n"/>
@@ -6224,6 +6534,7 @@
       <c r="K198" s="14" t="n"/>
       <c r="L198" s="14" t="n"/>
       <c r="M198" s="14" t="n"/>
+      <c r="N198" s="14" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="14" t="n"/>
@@ -6239,6 +6550,7 @@
       <c r="K199" s="14" t="n"/>
       <c r="L199" s="14" t="n"/>
       <c r="M199" s="14" t="n"/>
+      <c r="N199" s="14" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="14" t="n"/>
@@ -6254,6 +6566,7 @@
       <c r="K200" s="14" t="n"/>
       <c r="L200" s="14" t="n"/>
       <c r="M200" s="14" t="n"/>
+      <c r="N200" s="14" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="14" t="n"/>
@@ -6269,6 +6582,7 @@
       <c r="K201" s="14" t="n"/>
       <c r="L201" s="14" t="n"/>
       <c r="M201" s="14" t="n"/>
+      <c r="N201" s="14" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="14" t="n"/>
@@ -6284,6 +6598,7 @@
       <c r="K202" s="14" t="n"/>
       <c r="L202" s="14" t="n"/>
       <c r="M202" s="14" t="n"/>
+      <c r="N202" s="14" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -17005,7 +17320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17016,7 +17331,8 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17062,6 +17378,11 @@
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
+          <t>origin_country</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
@@ -17101,7 +17422,8 @@
           <t>Groupage NL-Istanbul, EUR 200-320/pallet. FTL approx. EUR 3.8-4.5k</t>
         </is>
       </c>
-      <c r="I2" s="16" t="inlineStr">
+      <c r="I2" s="15" t="n"/>
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17142,7 +17464,8 @@
           <t>LCL Rotterdam-Ambarlı incl. origin/destination THC</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="15" t="n"/>
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17183,7 +17506,8 @@
           <t>Groupage via Spain + Algeciras ferry</t>
         </is>
       </c>
-      <c r="I4" s="16" t="inlineStr">
+      <c r="I4" s="15" t="n"/>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17224,7 +17548,8 @@
           <t>LCL Rotterdam-Casablanca</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17265,7 +17590,8 @@
           <t>LCL Rotterdam-Alexandria</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17306,7 +17632,8 @@
           <t>LCL Rotterdam-Algiers, port congestion adds risk</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17347,7 +17674,8 @@
           <t>LCL Rotterdam-Radès</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17388,7 +17716,8 @@
           <t>LCL Rotterdam-Jebel Ali, Cape routing</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17429,7 +17758,8 @@
           <t>LCL Rotterdam-Dammam, Cape routing</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17470,7 +17800,8 @@
           <t>LCL Rotterdam-Jeddah. Red Sea risk surcharges volatile</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17511,7 +17842,8 @@
           <t>LCL Rotterdam-Hamad</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17552,7 +17884,8 @@
           <t>LCL Rotterdam-Shuwaikh</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17593,7 +17926,8 @@
           <t>LCL Rotterdam-Bahrain</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17634,7 +17968,8 @@
           <t>LCL Rotterdam-Sohar</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17675,7 +18010,8 @@
           <t>Approx. EUR 3-4/kg chargeable at 300 kg/pallet. Emergency use only</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17716,7 +18052,8 @@
           <t>Jebel Ali to other GCC by truck. Customs at each border</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17757,7 +18094,8 @@
           <t>Tanger Med to EG/TN/DZ. Poor intra-Maghreb connections</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17794,7 +18132,8 @@
           <t>Generic in-country LTL. Override per country</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17831,7 +18170,8 @@
           <t>Long distances Dammam-Riyadh-Jeddah</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17872,7 +18212,8 @@
           <t>Asia-Rotterdam LCL + drayage to Helmond. Replace per supplier</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17913,7 +18254,928 @@
           <t>Albania / Serbia groupage truck to Helmond. Replace with the forwarder's quote</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
+          <t>Jebel Ali</t>
+        </is>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>FCL share Ningbo/Qingdao-Jebel Ali. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>Dammam</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>FCL share China-Dammam. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>Ambarlı</t>
+        </is>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>China-Ambarlı, Cape routing while the Red Sea is disrupted. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>Tanger Med</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>China-Tanger Med (Asia-Europe main line call), Cape routing. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>China-Alexandria, Cape routing. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Jebel Ali</t>
+        </is>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="F28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>Chattogram-Jebel Ali via Colombo. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>Dammam</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>Chattogram-Dammam via Colombo. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>Ambarlı</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>Chattogram-Ambarlı, Cape routing. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>Tanger Med</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>120</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>Chattogram-Tanger Med, Cape routing. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>125</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>Chattogram-Alexandria, Cape routing. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>BD</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>Kapıkule</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Istanbul groupage via North Macedonia and Bulgaria. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>Tanger Med</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Tanger Med short sea with transhipment. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C35" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Alexandria short sea. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>Jebel Ali</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>190</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Jebel Ali, Cape routing while the Red Sea is disrupted (about 16 days via Suez). Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C37" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>165</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Jeddah via Suez (northern Red Sea), then truck to the node. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C38" s="15" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="inlineStr">
+        <is>
+          <t>Kapıkule</t>
+        </is>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F38" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>Leskovac-Istanbul truck via Bulgaria. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>Tanger Med</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, short sea to Tanger Med. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F40" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, short sea to Alexandria. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C41" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>Jebel Ali</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>195</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, sea via the Cape while the Red Sea is disrupted. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="F42" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, sea via Suez to Jeddah, then truck to the node. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -17921,7 +19183,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="J2:J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"placeholder,real"</formula1>
     </dataValidation>
   </dataValidations>

--- a/templates/FlexiTog_data_request_pack.xlsx
+++ b/templates/FlexiTog_data_request_pack.xlsx
@@ -1477,11 +1477,11 @@
         </is>
       </c>
       <c r="J15" s="5">
-        <f>COUNTA('Freight rates'!A2:A101)</f>
+        <f>COUNTA('Freight rates'!A2:A112)</f>
         <v/>
       </c>
       <c r="K15" s="5">
-        <f>COUNTIF('Freight rates'!J2:J101,"real")</f>
+        <f>COUNTIF('Freight rates'!J2:J112,"real")</f>
         <v/>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       </c>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>sea</t>
         </is>
       </c>
       <c r="K2" s="12" t="b">
@@ -3391,7 +3391,7 @@
       <c r="M2" s="12" t="n"/>
       <c r="N2" s="12" t="inlineStr">
         <is>
-          <t>Cut-make-trim for the FlexiTog line. Road via Montenegro and Croatia, or ferry to Bari</t>
+          <t>Cut-make-trim for the FlexiTog line. Sea from Durrës; road via Montenegro and Croatia is the alternative</t>
         </is>
       </c>
       <c r="O2" s="13" t="inlineStr">
@@ -17320,7 +17320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J42"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -18104,32 +18104,36 @@
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>regional</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>GCC</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>road</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr"/>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Dubai air cargo</t>
+        </is>
+      </c>
       <c r="E19" s="15" t="n">
-        <v>55</v>
+        <v>480</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="G19" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="16" t="inlineStr">
         <is>
-          <t>Generic in-country LTL. Override per country</t>
+          <t>Dubai to GCC capitals, about EUR 1.6/kg at 300 kg per pallet</t>
         </is>
       </c>
       <c r="I19" s="15" t="n"/>
@@ -18142,32 +18146,36 @@
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>domestic</t>
+          <t>regional</t>
         </is>
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>road</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="inlineStr"/>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Air cargo</t>
+        </is>
+      </c>
       <c r="E20" s="15" t="n">
-        <v>80</v>
+        <v>750</v>
       </c>
       <c r="F20" s="15" t="n">
-        <v>120</v>
+        <v>350</v>
       </c>
       <c r="G20" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="16" t="inlineStr">
         <is>
-          <t>Long distances Dammam-Riyadh-Jeddah</t>
+          <t>Tangier/Casablanca to Cairo, Tunis, Algiers. Morocco-Algeria land border is closed</t>
         </is>
       </c>
       <c r="I20" s="15" t="n"/>
@@ -18180,36 +18188,32 @@
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>inbound</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>sea</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Rotterdam</t>
-        </is>
-      </c>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr"/>
       <c r="E21" s="15" t="n">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>300</v>
+        <v>90</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="H21" s="16" t="inlineStr">
         <is>
-          <t>Asia-Rotterdam LCL + drayage to Helmond. Replace per supplier</t>
+          <t>Generic in-country LTL. Override per country</t>
         </is>
       </c>
       <c r="I21" s="15" t="n"/>
@@ -18222,12 +18226,12 @@
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>inbound</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -18235,23 +18239,19 @@
           <t>road</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>Balkans road</t>
-        </is>
-      </c>
+      <c r="D22" s="15" t="inlineStr"/>
       <c r="E22" s="15" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="F22" s="15" t="n">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="16" t="inlineStr">
         <is>
-          <t>Albania / Serbia groupage truck to Helmond. Replace with the forwarder's quote</t>
+          <t>Long distances Dammam-Riyadh-Jeddah</t>
         </is>
       </c>
       <c r="I22" s="15" t="n"/>
@@ -18264,43 +18264,39 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>*</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>air</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Jebel Ali</t>
+          <t>Domestic air cargo</t>
         </is>
       </c>
       <c r="E23" s="15" t="n">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H23" s="16" t="inlineStr">
         <is>
-          <t>FCL share Ningbo/Qingdao-Jebel Ali. Consolidated refill rate, replace with a quote</t>
-        </is>
-      </c>
-      <c r="I23" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>Domestic air cargo plus airport handling and delivery, about EUR 1.4/kg at 300 kg</t>
+        </is>
+      </c>
+      <c r="I23" s="15" t="n"/>
       <c r="J23" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
@@ -18310,7 +18306,7 @@
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>domestic</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -18320,33 +18316,29 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>air</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Dammam</t>
+          <t>Saudia Cargo</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
-        <v>95</v>
+        <v>380</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H24" s="16" t="inlineStr">
         <is>
-          <t>FCL share China-Dammam. Consolidated refill rate, replace with a quote</t>
-        </is>
-      </c>
-      <c r="I24" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>Dammam/Jeddah to Riyadh by air</t>
+        </is>
+      </c>
+      <c r="I24" s="15" t="n"/>
       <c r="J24" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
@@ -18356,12 +18348,12 @@
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -18371,28 +18363,24 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Ambarlı</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H25" s="16" t="inlineStr">
         <is>
-          <t>China-Ambarlı, Cape routing while the Red Sea is disrupted. Consolidated refill rate, replace with a quote</t>
-        </is>
-      </c>
-      <c r="I25" s="15" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
+          <t>Asia-Rotterdam LCL + drayage to Helmond. Replace per supplier</t>
+        </is>
+      </c>
+      <c r="I25" s="15" t="n"/>
       <c r="J25" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
@@ -18402,41 +18390,41 @@
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Tanger Med</t>
+          <t>Balkans road</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
         <v>110</v>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="H26" s="16" t="inlineStr">
         <is>
-          <t>China-Tanger Med (Asia-Europe main line call), Cape routing. Consolidated refill rate, replace with a quote</t>
+          <t>Albania groupage truck to Helmond via Montenegro and Croatia. Replace with the forwarder's quote</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
@@ -18448,41 +18436,41 @@
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Balkans road</t>
         </is>
       </c>
       <c r="E27" s="15" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H27" s="16" t="inlineStr">
         <is>
-          <t>China-Alexandria, Cape routing. Consolidated refill rate, replace with a quote</t>
+          <t>Serbia groupage truck to Helmond via Hungary and Austria. Replace with the forwarder's quote</t>
         </is>
       </c>
       <c r="I27" s="15" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr">
@@ -18494,12 +18482,12 @@
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -18509,26 +18497,26 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Jebel Ali</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E28" s="15" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H28" s="16" t="inlineStr">
         <is>
-          <t>Chattogram-Jebel Ali via Colombo. Consolidated refill rate, replace with a quote</t>
+          <t>Ningbo/Qingdao-Rotterdam FCL share + drayage, Cape routing</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
@@ -18540,12 +18528,12 @@
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -18555,21 +18543,21 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Dammam</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E29" s="15" t="n">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="H29" s="16" t="inlineStr">
         <is>
-          <t>Chattogram-Dammam via Colombo. Consolidated refill rate, replace with a quote</t>
+          <t>Chattogram-Rotterdam via Colombo + drayage, Cape routing</t>
         </is>
       </c>
       <c r="I29" s="15" t="inlineStr">
@@ -18586,12 +18574,12 @@
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -18601,26 +18589,26 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Ambarlı</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E30" s="15" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="H30" s="16" t="inlineStr">
         <is>
-          <t>Chattogram-Ambarlı, Cape routing. Consolidated refill rate, replace with a quote</t>
+          <t>Durrës-Rotterdam feeder via Gibraltar + drayage</t>
         </is>
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
@@ -18632,12 +18620,12 @@
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>inbound</t>
         </is>
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -18647,26 +18635,26 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Tanger Med</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E31" s="15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="H31" s="16" t="inlineStr">
         <is>
-          <t>Chattogram-Tanger Med, Cape routing. Consolidated refill rate, replace with a quote</t>
+          <t>Truck to Thessaloniki, feeder to Rotterdam + drayage</t>
         </is>
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
@@ -18683,7 +18671,7 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
@@ -18693,26 +18681,26 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Jebel Ali</t>
         </is>
       </c>
       <c r="E32" s="15" t="n">
-        <v>125</v>
+        <v>85</v>
       </c>
       <c r="F32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="15" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H32" s="16" t="inlineStr">
         <is>
-          <t>Chattogram-Alexandria, Cape routing. Consolidated refill rate, replace with a quote</t>
+          <t>FCL share Ningbo/Qingdao-Jebel Ali. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>BD</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J32" s="16" t="inlineStr">
@@ -18729,36 +18717,36 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>sea</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Kapıkule</t>
+          <t>Dammam</t>
         </is>
       </c>
       <c r="E33" s="15" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="F33" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G33" s="15" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>Durrës-Istanbul groupage via North Macedonia and Bulgaria. Consolidated refill rate, replace with a quote</t>
+          <t>FCL share China-Dammam. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
@@ -18775,7 +18763,7 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -18785,26 +18773,26 @@
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>Tanger Med</t>
+          <t>Ambarlı</t>
         </is>
       </c>
       <c r="E34" s="15" t="n">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="F34" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="15" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="H34" s="16" t="inlineStr">
         <is>
-          <t>Durrës-Tanger Med short sea with transhipment. Consolidated refill rate, replace with a quote</t>
+          <t>China-Ambarlı, Cape routing while the Red Sea is disrupted. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
@@ -18821,7 +18809,7 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -18831,26 +18819,26 @@
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Tanger Med</t>
         </is>
       </c>
       <c r="E35" s="15" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="F35" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="15" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H35" s="16" t="inlineStr">
         <is>
-          <t>Durrës-Alexandria short sea. Consolidated refill rate, replace with a quote</t>
+          <t>China-Tanger Med (Asia-Europe main line call), Cape routing. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
@@ -18867,7 +18855,7 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -18877,11 +18865,11 @@
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Jebel Ali</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="E36" s="15" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="F36" s="15" t="n">
         <v>0</v>
@@ -18891,12 +18879,12 @@
       </c>
       <c r="H36" s="16" t="inlineStr">
         <is>
-          <t>Durrës-Jebel Ali, Cape routing while the Red Sea is disrupted (about 16 days via Suez). Consolidated refill rate, replace with a quote</t>
+          <t>China-Alexandria, Cape routing. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="J36" s="16" t="inlineStr">
@@ -18913,7 +18901,7 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
@@ -18923,26 +18911,26 @@
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Jebel Ali</t>
         </is>
       </c>
       <c r="E37" s="15" t="n">
-        <v>165</v>
+        <v>80</v>
       </c>
       <c r="F37" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H37" s="16" t="inlineStr">
         <is>
-          <t>Durrës-Jeddah via Suez (northern Red Sea), then truck to the node. Consolidated refill rate, replace with a quote</t>
+          <t>Chattogram-Jebel Ali via Colombo. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
@@ -18959,17 +18947,17 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>TR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>road</t>
+          <t>sea</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Kapıkule</t>
+          <t>Dammam</t>
         </is>
       </c>
       <c r="E38" s="15" t="n">
@@ -18979,16 +18967,16 @@
         <v>0</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H38" s="16" t="inlineStr">
         <is>
-          <t>Leskovac-Istanbul truck via Bulgaria. Consolidated refill rate, replace with a quote</t>
+          <t>Chattogram-Dammam via Colombo. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="J38" s="16" t="inlineStr">
@@ -19005,7 +18993,7 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
@@ -19015,26 +19003,26 @@
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Tanger Med</t>
+          <t>Ambarlı</t>
         </is>
       </c>
       <c r="E39" s="15" t="n">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="F39" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="15" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H39" s="16" t="inlineStr">
         <is>
-          <t>Truck to Thessaloniki, short sea to Tanger Med. Consolidated refill rate, replace with a quote</t>
+          <t>Chattogram-Ambarlı, Cape routing. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
@@ -19051,7 +19039,7 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -19061,26 +19049,26 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Alexandria</t>
+          <t>Tanger Med</t>
         </is>
       </c>
       <c r="E40" s="15" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F40" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="H40" s="16" t="inlineStr">
         <is>
-          <t>Truck to Thessaloniki, short sea to Alexandria. Consolidated refill rate, replace with a quote</t>
+          <t>Chattogram-Tanger Med, Cape routing. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
@@ -19097,7 +19085,7 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>AE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -19107,26 +19095,26 @@
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>Jebel Ali</t>
+          <t>Alexandria</t>
         </is>
       </c>
       <c r="E41" s="15" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="F41" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H41" s="16" t="inlineStr">
         <is>
-          <t>Truck to Thessaloniki, sea via the Cape while the Red Sea is disrupted. Consolidated refill rate, replace with a quote</t>
+          <t>Chattogram-Alexandria, Cape routing. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
@@ -19143,39 +19131,545 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
         <is>
-          <t>sea</t>
+          <t>road</t>
         </is>
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Jeddah</t>
+          <t>Kapıkule</t>
         </is>
       </c>
       <c r="E42" s="15" t="n">
-        <v>170</v>
+        <v>105</v>
       </c>
       <c r="F42" s="15" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Istanbul groupage via North Macedonia and Bulgaria. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C43" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>Ambarlı</t>
+        </is>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Ambarlı short sea. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>Ambarlı</t>
+        </is>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, short sea to Ambarlı. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>Tanger Med</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Tanger Med short sea with transhipment. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C46" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F46" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Alexandria short sea. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>Jebel Ali</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>190</v>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="15" t="n">
+        <v>38</v>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Jebel Ali, Cape routing while the Red Sea is disrupted (about 16 days via Suez). Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C48" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>165</v>
+      </c>
+      <c r="F48" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="H42" s="16" t="inlineStr">
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>Durrës-Jeddah via Suez (northern Red Sea), then truck to the node. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>TR</t>
+        </is>
+      </c>
+      <c r="C49" s="15" t="inlineStr">
+        <is>
+          <t>road</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>Kapıkule</t>
+        </is>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>Leskovac-Istanbul truck via Bulgaria. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="inlineStr">
+        <is>
+          <t>Tanger Med</t>
+        </is>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>160</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, short sea to Tanger Med. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="C51" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, short sea to Alexandria. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="inlineStr">
+        <is>
+          <t>Jebel Ali</t>
+        </is>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>195</v>
+      </c>
+      <c r="F52" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>Truck to Thessaloniki, sea via the Cape while the Red Sea is disrupted. Consolidated refill rate, replace with a quote</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>placeholder</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
+          <t>Jeddah</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="F53" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="15" t="n">
+        <v>18</v>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
         <is>
           <t>Truck to Thessaloniki, sea via Suez to Jeddah, then truck to the node. Consolidated refill rate, replace with a quote</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="J42" s="16" t="inlineStr">
+      <c r="J53" s="16" t="inlineStr">
         <is>
           <t>placeholder</t>
         </is>
@@ -19183,7 +19677,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="J2:J101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="J2:J112" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"placeholder,real"</formula1>
     </dataValidation>
   </dataValidations>
